--- a/eplab_website_content.xlsx
+++ b/eplab_website_content.xlsx
@@ -415,17 +415,6 @@
       <c r="A1" t="str">
         <v>eP Lab Website — Content CMS (Google Sheet)</v>
       </c>
-      <c r="B1" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v/>
-      </c>
-      <c r="B2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -467,14 +456,6 @@
         <v>셀엔 URL만. 사진·로고·PDF는 Google Drive/저장소에 두고 photo_url·logo_url·image_url 참조.</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v/>
-      </c>
-      <c r="B8" t="str">
-        <v/>
-      </c>
-    </row>
     <row r="9">
       <c r="A9" t="str">
         <v>탭 구성</v>
@@ -516,7 +497,6 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:B13"/>
   </ignoredErrors>
@@ -548,7 +528,7 @@
       <c r="A2" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B2">
+      <c r="B2" t="str">
         <v>10</v>
       </c>
       <c r="C2" t="str">
@@ -565,7 +545,7 @@
       <c r="A3" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B3">
+      <c r="B3" t="str">
         <v>20</v>
       </c>
       <c r="C3" t="str">
@@ -582,7 +562,7 @@
       <c r="A4" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B4">
+      <c r="B4" t="str">
         <v>30</v>
       </c>
       <c r="C4" t="str">
@@ -599,7 +579,7 @@
       <c r="A5" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B5">
+      <c r="B5" t="str">
         <v>40</v>
       </c>
       <c r="C5" t="str">
@@ -616,7 +596,7 @@
       <c r="A6" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B6">
+      <c r="B6" t="str">
         <v>50</v>
       </c>
       <c r="C6" t="str">
@@ -633,7 +613,7 @@
       <c r="A7" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B7">
+      <c r="B7" t="str">
         <v>60</v>
       </c>
       <c r="C7" t="str">
@@ -650,7 +630,7 @@
       <c r="A8" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B8">
+      <c r="B8" t="str">
         <v>70</v>
       </c>
       <c r="C8" t="str">
@@ -667,7 +647,7 @@
       <c r="A9" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B9">
+      <c r="B9" t="str">
         <v>80</v>
       </c>
       <c r="C9" t="str">
@@ -684,7 +664,7 @@
       <c r="A10" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B10">
+      <c r="B10" t="str">
         <v>90</v>
       </c>
       <c r="C10" t="str">
@@ -701,7 +681,7 @@
       <c r="A11" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B11">
+      <c r="B11" t="str">
         <v>100</v>
       </c>
       <c r="C11" t="str">
@@ -718,7 +698,7 @@
       <c r="A12" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B12">
+      <c r="B12" t="str">
         <v>110</v>
       </c>
       <c r="C12" t="str">
@@ -735,7 +715,7 @@
       <c r="A13" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B13">
+      <c r="B13" t="str">
         <v>120</v>
       </c>
       <c r="C13" t="str">
@@ -752,7 +732,7 @@
       <c r="A14" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B14">
+      <c r="B14" t="str">
         <v>130</v>
       </c>
       <c r="C14" t="str">
@@ -769,7 +749,7 @@
       <c r="A15" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B15">
+      <c r="B15" t="str">
         <v>140</v>
       </c>
       <c r="C15" t="str">
@@ -786,7 +766,7 @@
       <c r="A16" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B16">
+      <c r="B16" t="str">
         <v>150</v>
       </c>
       <c r="C16" t="str">
@@ -803,7 +783,7 @@
       <c r="A17" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B17">
+      <c r="B17" t="str">
         <v>160</v>
       </c>
       <c r="C17" t="str">
@@ -820,7 +800,7 @@
       <c r="A18" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B18">
+      <c r="B18" t="str">
         <v>170</v>
       </c>
       <c r="C18" t="str">
@@ -837,7 +817,7 @@
       <c r="A19" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B19">
+      <c r="B19" t="str">
         <v>180</v>
       </c>
       <c r="C19" t="str">
@@ -854,7 +834,7 @@
       <c r="A20" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B20">
+      <c r="B20" t="str">
         <v>190</v>
       </c>
       <c r="C20" t="str">
@@ -871,7 +851,7 @@
       <c r="A21" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B21">
+      <c r="B21" t="str">
         <v>200</v>
       </c>
       <c r="C21" t="str">
@@ -888,7 +868,7 @@
       <c r="A22" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B22">
+      <c r="B22" t="str">
         <v>210</v>
       </c>
       <c r="C22" t="str">
@@ -905,7 +885,7 @@
       <c r="A23" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B23">
+      <c r="B23" t="str">
         <v>220</v>
       </c>
       <c r="C23" t="str">
@@ -922,7 +902,7 @@
       <c r="A24" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B24">
+      <c r="B24" t="str">
         <v>230</v>
       </c>
       <c r="C24" t="str">
@@ -939,7 +919,7 @@
       <c r="A25" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B25">
+      <c r="B25" t="str">
         <v>240</v>
       </c>
       <c r="C25" t="str">
@@ -953,7 +933,6 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:E25"/>
   </ignoredErrors>
@@ -997,7 +976,7 @@
       <c r="A2" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B2">
+      <c r="B2" t="str">
         <v>10</v>
       </c>
       <c r="C2" t="str">
@@ -1012,21 +991,12 @@
       <c r="F2" t="str">
         <v>MEC2036</v>
       </c>
-      <c r="G2" t="str">
-        <v/>
-      </c>
-      <c r="H2" t="str">
-        <v/>
-      </c>
-      <c r="I2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B3">
+      <c r="B3" t="str">
         <v>20</v>
       </c>
       <c r="C3" t="str">
@@ -1041,21 +1011,12 @@
       <c r="F3" t="str">
         <v>MEC2011</v>
       </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v/>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B4">
+      <c r="B4" t="str">
         <v>30</v>
       </c>
       <c r="C4" t="str">
@@ -1070,21 +1031,12 @@
       <c r="F4" t="str">
         <v>MEC4038</v>
       </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v/>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B5">
+      <c r="B5" t="str">
         <v>40</v>
       </c>
       <c r="C5" t="str">
@@ -1111,9 +1063,9 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="B6">
+        <v>FALSE</v>
+      </c>
+      <c r="B6" t="str">
         <v>50</v>
       </c>
       <c r="C6" t="str">
@@ -1140,9 +1092,9 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="B7">
+        <v>FALSE</v>
+      </c>
+      <c r="B7" t="str">
         <v>60</v>
       </c>
       <c r="C7" t="str">
@@ -1171,7 +1123,7 @@
       <c r="A8" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B8">
+      <c r="B8" t="str">
         <v>70</v>
       </c>
       <c r="C8" t="str">
@@ -1197,7 +1149,6 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:I8"/>
   </ignoredErrors>
@@ -1235,7 +1186,7 @@
       <c r="A2" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B2">
+      <c r="B2" t="str">
         <v>10</v>
       </c>
       <c r="C2" t="str">
@@ -1247,18 +1198,12 @@
       <c r="E2" t="str">
         <v>유재경 석사과정이 제1저자로 작성한 "Efficient multi-objective design optimization of axial-flux permanent magnet machines for drone propulsion system using multi-fidelity gaussian process" 논문이 Structural and Multidisciplinary Optimization 저널에 Accept 되었습니다. 축하합니다!</v>
       </c>
-      <c r="F2" t="str">
-        <v/>
-      </c>
-      <c r="G2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B3">
+      <c r="B3" t="str">
         <v>20</v>
       </c>
       <c r="C3" t="str">
@@ -1270,18 +1215,12 @@
       <c r="E3" t="str">
         <v>현대자동차와 함께 "모터시스템 효율 향상을 위한 실측데이터 기반 전류지령맵 추출 기술 개발" 연구과제를 수행합니다.</v>
       </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B4">
+      <c r="B4" t="str">
         <v>30</v>
       </c>
       <c r="C4" t="str">
@@ -1293,18 +1232,12 @@
       <c r="E4" t="str">
         <v>현대자동차와 함께 "PE 비효율 제어 시, 차량 열관리 시스템 성능 검토를 위한 해석 모델 개발" 연구과제를 수행합니다.</v>
       </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B5">
+      <c r="B5" t="str">
         <v>40</v>
       </c>
       <c r="C5" t="str">
@@ -1316,18 +1249,12 @@
       <c r="E5" t="str">
         <v>현대자동차와 함께 "저가형 모터를 위한 PE 시스템 최적화 기술 개발" 연구과제를 수행합니다.</v>
       </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B6">
+      <c r="B6" t="str">
         <v>50</v>
       </c>
       <c r="C6" t="str">
@@ -1339,18 +1266,12 @@
       <c r="E6" t="str">
         <v>HD현대중공업과 함께 "친환경연료 힘센엔진 솔레노이드 밸브 LECM Fault 분석 및 설계 기술 개발" 연구과제를 수행합니다.</v>
       </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B7">
+      <c r="B7" t="str">
         <v>60</v>
       </c>
       <c r="C7" t="str">
@@ -1362,18 +1283,12 @@
       <c r="E7" t="str">
         <v>우리 연구실에 유나경 학생이 학부연구생으로 합류하였습니다. 환영합니다!</v>
       </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B8">
+      <c r="B8" t="str">
         <v>70</v>
       </c>
       <c r="C8" t="str">
@@ -1385,18 +1300,12 @@
       <c r="E8" t="str">
         <v>학부연구생 김하린 학생이 볼보그룹코리아에 입사했습니다. 건설기계 고전압시스템 엔지니어로 근무할 예정입니다. 축하합니다!</v>
       </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B9">
+      <c r="B9" t="str">
         <v>80</v>
       </c>
       <c r="C9" t="str">
@@ -1408,18 +1317,12 @@
       <c r="E9" t="str">
         <v>HD현대중공업과 함께 "친환경연료 힘센엔진 연료분사펌프(e-FIP)용 솔레노이드 밸브 해석 및 시험평가 기술 개발" 연구과제를 수행합니다.</v>
       </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B10">
+      <c r="B10" t="str">
         <v>90</v>
       </c>
       <c r="C10" t="str">
@@ -1431,18 +1334,12 @@
       <c r="E10" t="str">
         <v>장민우, 정성원 석사과정이 한국연구재단 석사과정생연구장려금지원사업에 선정되었습니다. 축하합니다!</v>
       </c>
-      <c r="F10" t="str">
-        <v/>
-      </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B11">
+      <c r="B11" t="str">
         <v>100</v>
       </c>
       <c r="C11" t="str">
@@ -1454,18 +1351,12 @@
       <c r="E11" t="str">
         <v>우리 연구실에 노진태, 조혜찬, 홍서현 학생이 학부연구생으로 합류하였습니다. 환영합니다!</v>
       </c>
-      <c r="F11" t="str">
-        <v/>
-      </c>
-      <c r="G11" t="str">
-        <v/>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B12">
+      <c r="B12" t="str">
         <v>110</v>
       </c>
       <c r="C12" t="str">
@@ -1477,18 +1368,12 @@
       <c r="E12" t="str">
         <v>우리 연구실에 정채영 학생이 학부연구생으로 합류하였습니다. 환영합니다!</v>
       </c>
-      <c r="F12" t="str">
-        <v/>
-      </c>
-      <c r="G12" t="str">
-        <v/>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B13">
+      <c r="B13" t="str">
         <v>120</v>
       </c>
       <c r="C13" t="str">
@@ -1500,18 +1385,12 @@
       <c r="E13" t="str">
         <v>우리 연구실에 서영주, 김재윤, 유재경 학생이 석사과정으로 합류하였습니다. 환영합니다!</v>
       </c>
-      <c r="F13" t="str">
-        <v/>
-      </c>
-      <c r="G13" t="str">
-        <v/>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B14">
+      <c r="B14" t="str">
         <v>130</v>
       </c>
       <c r="C14" t="str">
@@ -1523,18 +1402,12 @@
       <c r="E14" t="str">
         <v>효성전기, 한국자동차연구원, 대구대학교와 함께 "평각동선 분포권 기술 적용 축방향자속 전동기 개발" 연구과제를 수행합니다.</v>
       </c>
-      <c r="F14" t="str">
-        <v/>
-      </c>
-      <c r="G14" t="str">
-        <v/>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B15">
+      <c r="B15" t="str">
         <v>140</v>
       </c>
       <c r="C15" t="str">
@@ -1546,18 +1419,12 @@
       <c r="E15" t="str">
         <v>현대트랜시스와 함께 "e2DT 구동모터 가진력 최적 설계 개발" 연구과제를 수행합니다.</v>
       </c>
-      <c r="F15" t="str">
-        <v/>
-      </c>
-      <c r="G15" t="str">
-        <v/>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B16">
+      <c r="B16" t="str">
         <v>150</v>
       </c>
       <c r="C16" t="str">
@@ -1569,18 +1436,12 @@
       <c r="E16" t="str">
         <v>현대자동차와 함께 "고전압 파워넷 네트워크의 공진 해석을 위한 시스템 해석 기법 및 모델링, 검증, 시뮬레이션 툴 개발" 연구과제를 수행합니다.</v>
       </c>
-      <c r="F16" t="str">
-        <v/>
-      </c>
-      <c r="G16" t="str">
-        <v/>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B17">
+      <c r="B17" t="str">
         <v>160</v>
       </c>
       <c r="C17" t="str">
@@ -1592,18 +1453,12 @@
       <c r="E17" t="str">
         <v>우리 연구실에 장민우, 정성원 학생이 석사과정으로 합류하였습니다. 환영합니다!</v>
       </c>
-      <c r="F17" t="str">
-        <v/>
-      </c>
-      <c r="G17" t="str">
-        <v/>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B18">
+      <c r="B18" t="str">
         <v>170</v>
       </c>
       <c r="C18" t="str">
@@ -1615,18 +1470,12 @@
       <c r="E18" t="str">
         <v>현대자동차와 함께 "VTM 기반기술 확보 및 데이터 구축을 위한 전력 모델 구축 및 PE시스템 Scaling 기법 개발" 연구과제를 수행합니다.</v>
       </c>
-      <c r="F18" t="str">
-        <v/>
-      </c>
-      <c r="G18" t="str">
-        <v/>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B19">
+      <c r="B19" t="str">
         <v>180</v>
       </c>
       <c r="C19" t="str">
@@ -1638,18 +1487,12 @@
       <c r="E19" t="str">
         <v>학부연구생 엄기웅 학생이 현대제철에 입사했습니다. 설비 엔지니어로 근무할 예정입니다. 축하합니다!</v>
       </c>
-      <c r="F19" t="str">
-        <v/>
-      </c>
-      <c r="G19" t="str">
-        <v/>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B20">
+      <c r="B20" t="str">
         <v>190</v>
       </c>
       <c r="C20" t="str">
@@ -1661,18 +1504,12 @@
       <c r="E20" t="str">
         <v>학부연구생 한진성 학생이 KAIST 석사과정에 진학했습니다. 훌륭한 연구자로 성장하시기 바랍니다. 축하합니다!</v>
       </c>
-      <c r="F20" t="str">
-        <v/>
-      </c>
-      <c r="G20" t="str">
-        <v/>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B21">
+      <c r="B21" t="str">
         <v>200</v>
       </c>
       <c r="C21" t="str">
@@ -1684,18 +1521,12 @@
       <c r="E21" t="str">
         <v>학부연구생 허태혁 학생이 현대자동차에 입사했습니다. 하이브리드 전기자동차 성능 개발 업무를 담당할 예정입니다. 축하합니다!</v>
       </c>
-      <c r="F21" t="str">
-        <v/>
-      </c>
-      <c r="G21" t="str">
-        <v/>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B22">
+      <c r="B22" t="str">
         <v>210</v>
       </c>
       <c r="C22" t="str">
@@ -1707,18 +1538,12 @@
       <c r="E22" t="str">
         <v>한국생산기술연구원과 함께 "회전자 관성을 이용한 토크 산정 알고리즘 개선" 연구과제를 수행합니다.</v>
       </c>
-      <c r="F22" t="str">
-        <v/>
-      </c>
-      <c r="G22" t="str">
-        <v/>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B23">
+      <c r="B23" t="str">
         <v>220</v>
       </c>
       <c r="C23" t="str">
@@ -1730,18 +1555,12 @@
       <c r="E23" t="str">
         <v>김찬우 석사과정이 한국연구재단 석사과정생연구장려금지원사업에 선정되었습니다. 축하합니다!</v>
       </c>
-      <c r="F23" t="str">
-        <v/>
-      </c>
-      <c r="G23" t="str">
-        <v/>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B24">
+      <c r="B24" t="str">
         <v>230</v>
       </c>
       <c r="C24" t="str">
@@ -1753,18 +1572,12 @@
       <c r="E24" t="str">
         <v>김찬우 학생이 우리 연구실 1호 석사과정으로 진학하였습니다. 환영합니다!</v>
       </c>
-      <c r="F24" t="str">
-        <v/>
-      </c>
-      <c r="G24" t="str">
-        <v/>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B25">
+      <c r="B25" t="str">
         <v>240</v>
       </c>
       <c r="C25" t="str">
@@ -1776,18 +1589,12 @@
       <c r="E25" t="str">
         <v>우리 연구실에 서영주, 김재윤 학생이 학부연구생으로 합류하였습니다. 환영합니다!</v>
       </c>
-      <c r="F25" t="str">
-        <v/>
-      </c>
-      <c r="G25" t="str">
-        <v/>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B26">
+      <c r="B26" t="str">
         <v>250</v>
       </c>
       <c r="C26" t="str">
@@ -1799,18 +1606,12 @@
       <c r="E26" t="str">
         <v>WESPION과 함께 "스마트 헬스케어 머신의 감성품질 향상을 위한 부하정밀제어 캘리브레이션 기술개발 및 출고 검사 장비 개발" 연구과제를 수행합니다.</v>
       </c>
-      <c r="F26" t="str">
-        <v/>
-      </c>
-      <c r="G26" t="str">
-        <v/>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B27">
+      <c r="B27" t="str">
         <v>260</v>
       </c>
       <c r="C27" t="str">
@@ -1822,18 +1623,12 @@
       <c r="E27" t="str">
         <v>현대트랜시스와 함께 "구동모터 특성해석 시간 단축을 위한 프로그램 개발" 연구과제를 수행합니다.</v>
       </c>
-      <c r="F27" t="str">
-        <v/>
-      </c>
-      <c r="G27" t="str">
-        <v/>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B28">
+      <c r="B28" t="str">
         <v>270</v>
       </c>
       <c r="C28" t="str">
@@ -1845,18 +1640,12 @@
       <c r="E28" t="str">
         <v>동국대학교 전동화 추진시스템 연구실 홈페이지 오픈!</v>
       </c>
-      <c r="F28" t="str">
-        <v/>
-      </c>
-      <c r="G28" t="str">
-        <v/>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B29">
+      <c r="B29" t="str">
         <v>280</v>
       </c>
       <c r="C29" t="str">
@@ -1868,18 +1657,12 @@
       <c r="E29" t="str">
         <v>1호 학부연구생 박태호 학생이 현대자동차에 입사했습니다. 상용차 연비/전비 계측 및 개발 업무를 담당할 예정입니다. 축하합니다!</v>
       </c>
-      <c r="F29" t="str">
-        <v/>
-      </c>
-      <c r="G29" t="str">
-        <v/>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B30">
+      <c r="B30" t="str">
         <v>290</v>
       </c>
       <c r="C30" t="str">
@@ -1891,18 +1674,12 @@
       <c r="E30" t="str">
         <v>학부연구생 허태혁 학생이 삼성SDI 인턴에 합격하였습니다. 축하합니다!</v>
       </c>
-      <c r="F30" t="str">
-        <v/>
-      </c>
-      <c r="G30" t="str">
-        <v/>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B31">
+      <c r="B31" t="str">
         <v>300</v>
       </c>
       <c r="C31" t="str">
@@ -1914,18 +1691,12 @@
       <c r="E31" t="str">
         <v>우리 연구실에 이준범, 엄기웅 학생이 학부연구생으로 합류하였습니다. 환영합니다!</v>
       </c>
-      <c r="F31" t="str">
-        <v/>
-      </c>
-      <c r="G31" t="str">
-        <v/>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B32">
+      <c r="B32" t="str">
         <v>310</v>
       </c>
       <c r="C32" t="str">
@@ -1937,18 +1708,12 @@
       <c r="E32" t="str">
         <v>현대자동차와 함께 "VTM 모델의 전비 예측 정확도 향상을 위한 2-Stage PE 시스템 손실맵 확장 프로세스 개발" 연구과제를 수행합니다.</v>
       </c>
-      <c r="F32" t="str">
-        <v/>
-      </c>
-      <c r="G32" t="str">
-        <v/>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B33">
+      <c r="B33" t="str">
         <v>320</v>
       </c>
       <c r="C33" t="str">
@@ -1960,18 +1725,12 @@
       <c r="E33" t="str">
         <v>우리 연구실에 허태혁, 김찬우, 김하린 학생이 학부연구생으로 합류하였습니다. 환영합니다!</v>
       </c>
-      <c r="F33" t="str">
-        <v/>
-      </c>
-      <c r="G33" t="str">
-        <v/>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B34">
+      <c r="B34" t="str">
         <v>330</v>
       </c>
       <c r="C34" t="str">
@@ -1983,18 +1742,12 @@
       <c r="E34" t="str">
         <v>우리 연구실에 박태호, 한진성 학생이 학부연구생으로 합류하였습니다. 환영합니다!</v>
       </c>
-      <c r="F34" t="str">
-        <v/>
-      </c>
-      <c r="G34" t="str">
-        <v/>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B35">
+      <c r="B35" t="str">
         <v>340</v>
       </c>
       <c r="C35" t="str">
@@ -2006,15 +1759,8 @@
       <c r="E35" t="str">
         <v>박수환 교수 동국대학교 기계로봇에너지공학과 부임 및 전동화 추진시스템 연구실이 설립되었습니다.</v>
       </c>
-      <c r="F35" t="str">
-        <v/>
-      </c>
-      <c r="G35" t="str">
-        <v/>
-      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:G35"/>
   </ignoredErrors>
@@ -2055,7 +1801,7 @@
       <c r="A2" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B2">
+      <c r="B2" t="str">
         <v>10</v>
       </c>
       <c r="C2" t="str">
@@ -2067,7 +1813,7 @@
       <c r="E2" t="str">
         <v>연구실 전원</v>
       </c>
-      <c r="F2">
+      <c r="F2" t="str">
         <v>3</v>
       </c>
       <c r="G2" t="str">
@@ -2081,7 +1827,7 @@
       <c r="A3" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B3">
+      <c r="B3" t="str">
         <v>20</v>
       </c>
       <c r="C3" t="str">
@@ -2093,7 +1839,7 @@
       <c r="E3" t="str">
         <v>장민우, 정성원, 유재경</v>
       </c>
-      <c r="F3">
+      <c r="F3" t="str">
         <v>4</v>
       </c>
       <c r="G3" t="str">
@@ -2107,7 +1853,7 @@
       <c r="A4" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B4">
+      <c r="B4" t="str">
         <v>30</v>
       </c>
       <c r="C4" t="str">
@@ -2119,7 +1865,7 @@
       <c r="E4" t="str">
         <v>김찬우, 김재윤</v>
       </c>
-      <c r="F4">
+      <c r="F4" t="str">
         <v>5</v>
       </c>
       <c r="G4" t="str">
@@ -2133,7 +1879,7 @@
       <c r="A5" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B5">
+      <c r="B5" t="str">
         <v>40</v>
       </c>
       <c r="C5" t="str">
@@ -2145,7 +1891,7 @@
       <c r="E5" t="str">
         <v>김찬우, 김재윤, 서영주</v>
       </c>
-      <c r="F5">
+      <c r="F5" t="str">
         <v>3</v>
       </c>
       <c r="G5" t="str">
@@ -2159,7 +1905,7 @@
       <c r="A6" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B6">
+      <c r="B6" t="str">
         <v>50</v>
       </c>
       <c r="C6" t="str">
@@ -2171,7 +1917,7 @@
       <c r="E6" t="str">
         <v>허태혁, 한진성, 엄기웅 졸업</v>
       </c>
-      <c r="F6">
+      <c r="F6" t="str">
         <v>3</v>
       </c>
       <c r="G6" t="str">
@@ -2185,7 +1931,7 @@
       <c r="A7" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B7">
+      <c r="B7" t="str">
         <v>60</v>
       </c>
       <c r="C7" t="str">
@@ -2197,7 +1943,7 @@
       <c r="E7" t="str">
         <v>한국자동차연구원 하이브리드기술부문과 함께</v>
       </c>
-      <c r="F7">
+      <c r="F7" t="str">
         <v>4</v>
       </c>
       <c r="G7" t="str">
@@ -2211,7 +1957,7 @@
       <c r="A8" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B8">
+      <c r="B8" t="str">
         <v>70</v>
       </c>
       <c r="C8" t="str">
@@ -2223,7 +1969,7 @@
       <c r="E8" t="str">
         <v>김찬우, 박태호 졸업</v>
       </c>
-      <c r="F8">
+      <c r="F8" t="str">
         <v>2</v>
       </c>
       <c r="G8" t="str">
@@ -2237,7 +1983,7 @@
       <c r="A9" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B9">
+      <c r="B9" t="str">
         <v>80</v>
       </c>
       <c r="C9" t="str">
@@ -2249,7 +1995,7 @@
       <c r="E9" t="str">
         <v>김찬우, 이준범</v>
       </c>
-      <c r="F9">
+      <c r="F9" t="str">
         <v>3</v>
       </c>
       <c r="G9" t="str">
@@ -2263,7 +2009,7 @@
       <c r="A10" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B10">
+      <c r="B10" t="str">
         <v>90</v>
       </c>
       <c r="C10" t="str">
@@ -2275,7 +2021,7 @@
       <c r="E10" t="str">
         <v>연구실 전원</v>
       </c>
-      <c r="F10">
+      <c r="F10" t="str">
         <v>3</v>
       </c>
       <c r="G10" t="str">
@@ -2286,7 +2032,6 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:H10"/>
   </ignoredErrors>
@@ -2295,7 +2040,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:E25"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2324,19 +2069,16 @@
       <c r="D2" t="str">
         <v/>
       </c>
+      <c r="E2" t="str">
+        <v>value_en, value_ko 병기 시 value_ko 우선적용</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
         <v>site_short</v>
       </c>
       <c r="B3" t="str">
-        <v>eP Lab.</v>
-      </c>
-      <c r="C3" t="str">
-        <v>eP Lab.</v>
-      </c>
-      <c r="D3" t="str">
-        <v/>
+        <v>electrified Propulsion Lab.</v>
       </c>
     </row>
     <row r="4">
@@ -2349,9 +2091,6 @@
       <c r="C4" t="str">
         <v>동국대학교</v>
       </c>
-      <c r="D4" t="str">
-        <v/>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -2411,66 +2150,60 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>about_p1</v>
+        <v>about_title</v>
       </c>
       <c r="B9" t="str">
-        <v/>
-      </c>
-      <c r="C9" t="str">
-        <v>전동화 추진시스템 연구실(electrified Propulsion Lab.)은 전기기기(electric machinery)의 설계와 다물리(multi-physics) 해석을 기반으로, 자동차·선박·항공·생활가전·로봇용 전동화 추진시스템의 성능을 예측하고 최적화하는 연구를 수행합니다. 또한, 시험-해석 정합성 확보를 위한 해석기법의 연구를 바탕으로 1-D 시스템 모델 관련 연구를 수행합니다.</v>
-      </c>
-      <c r="D9" t="str">
-        <v>About 본문 1</v>
+        <v>전동화 추진시스템의|설계, 해석 및 시험</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>about_p2</v>
+        <v>about_p1</v>
       </c>
       <c r="B10" t="str">
         <v/>
       </c>
       <c r="C10" t="str">
-        <v>전자기 설계에서 시작해 손실·열·진동/소음을 함께 다루는 통합 해석 체계를 구축하고, 다중충실도 기반 설계 및 시험 효율화와 AI 기반 설계/시험 가속화 방법론을 개발합니다. 산업계와의 협력을 통해 연구 결과를 실제 양산 개발 프로세스에 적용하는 것을 목표로 합니다.</v>
+        <v>전동화 추진시스템 연구실은 전기기기의 설계와 다물리 해석을 기반으로, 자동차·선박·항공·생활가전·로봇용 전동화 추진시스템의 성능을 향상시키고 최적화하기 위한 연구를 수행합니다.</v>
       </c>
       <c r="D10" t="str">
-        <v>About 본문 2</v>
+        <v>About 본문 1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>stat_researchers</v>
+        <v>about_p2</v>
       </c>
       <c r="B11" t="str">
-        <v>11</v>
+        <v/>
       </c>
       <c r="C11" t="str">
-        <v/>
+        <v>자성재료 기반 전자기 해석과 열·진동/소음·회전자 강도를 함께 다루는 통합 해석 체계를 구축하고, 다중충실도 기반 설계 및 시험 효율화와 AI 기반 설계/시험 가속화 방법론을 개발합니다. 산업계와의 협력을 통해 연구 결과를 양산 개발 프로세스에 적용하는 것을 목표로 합니다.</v>
       </c>
       <c r="D11" t="str">
-        <v>통계 타일(자동집계 권장)</v>
+        <v>About 본문 2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>stat_publications</v>
+        <v>stat_researchers</v>
       </c>
       <c r="B12" t="str">
-        <v>30+</v>
+        <v>11</v>
       </c>
       <c r="C12" t="str">
         <v/>
       </c>
       <c r="D12" t="str">
-        <v>통계 타일</v>
+        <v>통계 타일(자동집계 권장)</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>stat_projects</v>
+        <v>stat_publications</v>
       </c>
       <c r="B13" t="str">
-        <v>13</v>
+        <v>30+</v>
       </c>
       <c r="C13" t="str">
         <v/>
@@ -2481,175 +2214,151 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>contact_lab</v>
+        <v>stat_projects</v>
       </c>
       <c r="B14" t="str">
-        <v>Wonheung-gwan E142, Dongguk University (Seoul Campus)</v>
+        <v>13</v>
       </c>
       <c r="C14" t="str">
-        <v>동국대학교 서울캠퍼스 전동화 추진시스템 연구실 (원흥관 E142)</v>
+        <v/>
       </c>
       <c r="D14" t="str">
-        <v>학생 연구실 — Contact 표기</v>
+        <v>통계 타일</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>contact_office</v>
+        <v>contact_lab</v>
       </c>
       <c r="B15" t="str">
-        <v>Wonheung-gwan F621</v>
+        <v>Wonheung-gwan E142, Dongguk University (Seoul Campus)</v>
       </c>
       <c r="C15" t="str">
-        <v>원흥관 F621</v>
+        <v>동국대학교 서울캠퍼스 전동화 추진시스템 연구실 (원흥관 E142)</v>
       </c>
       <c r="D15" t="str">
-        <v>교수(박수환) 연구실</v>
+        <v>학생 연구실 — Contact 표기</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>address</v>
+        <v>contact_office</v>
       </c>
       <c r="B16" t="str">
-        <v>30 Pildong-ro 1-gil, Jung-gu, Seoul 04620</v>
+        <v>Wonheung-gwan F621</v>
       </c>
       <c r="C16" t="str">
-        <v>서울특별시 중구 필동로1길 30 (04620)</v>
+        <v>원흥관 F621</v>
       </c>
       <c r="D16" t="str">
-        <v/>
+        <v>교수(박수환) 연구실</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>dept</v>
+        <v>address</v>
       </c>
       <c r="B17" t="str">
-        <v>Dept. of Mechanical, Robotics, and Energy Engineering</v>
+        <v>30 Pildong-ro 1-gil, Jung-gu, Seoul 04620</v>
       </c>
       <c r="C17" t="str">
-        <v>기계로봇에너지공학과</v>
-      </c>
-      <c r="D17" t="str">
-        <v/>
+        <v>서울특별시 중구 필동로1길 30 (04620)</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>tel</v>
+        <v>dept</v>
       </c>
       <c r="B18" t="str">
-        <v>+82-2-2260-3703</v>
+        <v>Dept. of Mechanical, Robotics, and Energy Engineering</v>
       </c>
       <c r="C18" t="str">
-        <v>02-2260-3703</v>
-      </c>
-      <c r="D18" t="str">
-        <v/>
+        <v>기계로봇에너지공학과</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>email</v>
+        <v>tel</v>
       </c>
       <c r="B19" t="str">
-        <v>parksh@dgu.ac.kr</v>
+        <v>+82-2-2260-3703</v>
       </c>
       <c r="C19" t="str">
-        <v>parksh@dgu.ac.kr</v>
-      </c>
-      <c r="D19" t="str">
-        <v/>
+        <v>02-2260-3703</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>scholar_url</v>
+        <v>email</v>
       </c>
       <c r="B20" t="str">
-        <v>https://scholar.google.com/citations?user=hocoJJAAAAAJ&amp;hl=ko</v>
+        <v>parksh@dgu.ac.kr</v>
       </c>
       <c r="C20" t="str">
-        <v/>
-      </c>
-      <c r="D20" t="str">
-        <v>교수 Google Scholar</v>
+        <v>parksh@dgu.ac.kr</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>subway</v>
+        <v>scholar_url</v>
       </c>
       <c r="B21" t="str">
-        <v>Line 3 Chungmuro Stn Exit 1 · Line 4 Dongguk Univ. Stn Exit 2</v>
+        <v>https://scholar.google.com/citations?user=hocoJJAAAAAJ&amp;hl=ko</v>
       </c>
       <c r="C21" t="str">
-        <v>지하철 3호선 충무로역 1번 출구 · 4호선 동대입구역 2번 출구</v>
+        <v/>
       </c>
       <c r="D21" t="str">
-        <v/>
+        <v>교수 Google Scholar</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>recruit_title</v>
+        <v>subway</v>
       </c>
       <c r="B22" t="str">
-        <v>We are looking for Self-motivated Pioneers.</v>
+        <v>Line 3 Chungmuro Stn Exit 1 · Line 4 Dongguk Univ. Stn Exit 2</v>
       </c>
       <c r="C22" t="str">
-        <v>우리는 Self-motivated Pioneer를 기다립니다.</v>
-      </c>
-      <c r="D22" t="str">
-        <v>Contact 채용 박스</v>
+        <v>지하철 3호선 충무로역 1번 출구 · 4호선 동대입구역 2번 출구</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>recruit_body</v>
+        <v>recruit_title</v>
       </c>
       <c r="B23" t="str">
-        <v/>
+        <v>We are looking for Self-motivated Pioneers.</v>
       </c>
       <c r="C23" t="str">
-        <v>전기기기 설계·해석, 전동화 파워트레인, AI 기반 설계 자동화에 관심 있는 대학원생 및 학부연구생은 이메일로 문의해 주세요.</v>
+        <v>우리는 Self-motivated Pioneer를 기다립니다.</v>
       </c>
       <c r="D23" t="str">
-        <v/>
+        <v>Contact 채용 박스</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>footer</v>
+        <v>recruit_body</v>
       </c>
       <c r="B24" t="str">
-        <v>Copyright © 2026 electrified Propulsion Lab. Dongguk University. All rights reserved.</v>
+        <v/>
       </c>
       <c r="C24" t="str">
-        <v/>
-      </c>
-      <c r="D24" t="str">
-        <v/>
+        <v>전기기기 설계·해석, 전동화 파워트레인, AI 기반 설계 자동화에 관심 있는 대학원생 및 학부연구생은 이메일로 문의해 주세요.</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>about_title</v>
+        <v>footer</v>
       </c>
       <c r="B25" t="str">
-        <v>전동화 추진시스템의|설계, 해석 및 시험</v>
-      </c>
-      <c r="C25" t="str">
-        <v/>
-      </c>
-      <c r="D25" t="str">
-        <v>Home About 제목. | 가 줄바꿈 자리</v>
+        <v>Copyright © 2026 electrified Propulsion Lab. Dongguk University. All rights reserved.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D25"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E25"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2700,7 +2409,7 @@
       <c r="A2" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B2">
+      <c r="B2" t="str">
         <v>10</v>
       </c>
       <c r="C2" t="str">
@@ -2738,7 +2447,7 @@
       <c r="A3" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B3">
+      <c r="B3" t="str">
         <v>110</v>
       </c>
       <c r="C3" t="str">
@@ -2756,27 +2465,12 @@
       <c r="G3" t="str">
         <v>kimcw_339@dgu.ac.kr</v>
       </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v/>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v/>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B4">
+      <c r="B4" t="str">
         <v>120</v>
       </c>
       <c r="C4" t="str">
@@ -2794,27 +2488,12 @@
       <c r="G4" t="str">
         <v>2025120179@dgu.ac.kr</v>
       </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v/>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v/>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B5">
+      <c r="B5" t="str">
         <v>130</v>
       </c>
       <c r="C5" t="str">
@@ -2832,27 +2511,12 @@
       <c r="G5" t="str">
         <v>2025120182@dgu.ac.kr</v>
       </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v/>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v/>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B6">
+      <c r="B6" t="str">
         <v>140</v>
       </c>
       <c r="C6" t="str">
@@ -2870,27 +2534,12 @@
       <c r="G6" t="str">
         <v>ca1ifornia1@dgu.ac.kr</v>
       </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v/>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v/>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B7">
+      <c r="B7" t="str">
         <v>150</v>
       </c>
       <c r="C7" t="str">
@@ -2908,27 +2557,12 @@
       <c r="G7" t="str">
         <v>kimjy_333@dgu.ac.kr</v>
       </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v/>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v/>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B8">
+      <c r="B8" t="str">
         <v>160</v>
       </c>
       <c r="C8" t="str">
@@ -2946,27 +2580,12 @@
       <c r="G8" t="str">
         <v>yujk_361@dgu.ac.kr</v>
       </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v/>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v/>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B9">
+      <c r="B9" t="str">
         <v>170</v>
       </c>
       <c r="C9" t="str">
@@ -2984,27 +2603,12 @@
       <c r="G9" t="str">
         <v>njt0731@dgu.ac.kr</v>
       </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v/>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v/>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B10">
+      <c r="B10" t="str">
         <v>210</v>
       </c>
       <c r="C10" t="str">
@@ -3019,30 +2623,12 @@
       <c r="F10" t="str">
         <v>학부연구생</v>
       </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
-      <c r="H10" t="str">
-        <v/>
-      </c>
-      <c r="I10" t="str">
-        <v/>
-      </c>
-      <c r="J10" t="str">
-        <v/>
-      </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
-      <c r="L10" t="str">
-        <v/>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B11">
+      <c r="B11" t="str">
         <v>220</v>
       </c>
       <c r="C11" t="str">
@@ -3057,30 +2643,12 @@
       <c r="F11" t="str">
         <v>학부연구생</v>
       </c>
-      <c r="G11" t="str">
-        <v/>
-      </c>
-      <c r="H11" t="str">
-        <v/>
-      </c>
-      <c r="I11" t="str">
-        <v/>
-      </c>
-      <c r="J11" t="str">
-        <v/>
-      </c>
-      <c r="K11" t="str">
-        <v/>
-      </c>
-      <c r="L11" t="str">
-        <v/>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B12">
+      <c r="B12" t="str">
         <v>230</v>
       </c>
       <c r="C12" t="str">
@@ -3095,30 +2663,12 @@
       <c r="F12" t="str">
         <v>학부연구생</v>
       </c>
-      <c r="G12" t="str">
-        <v/>
-      </c>
-      <c r="H12" t="str">
-        <v/>
-      </c>
-      <c r="I12" t="str">
-        <v/>
-      </c>
-      <c r="J12" t="str">
-        <v/>
-      </c>
-      <c r="K12" t="str">
-        <v/>
-      </c>
-      <c r="L12" t="str">
-        <v/>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B13">
+      <c r="B13" t="str">
         <v>240</v>
       </c>
       <c r="C13" t="str">
@@ -3133,30 +2683,12 @@
       <c r="F13" t="str">
         <v>학부연구생</v>
       </c>
-      <c r="G13" t="str">
-        <v/>
-      </c>
-      <c r="H13" t="str">
-        <v/>
-      </c>
-      <c r="I13" t="str">
-        <v/>
-      </c>
-      <c r="J13" t="str">
-        <v/>
-      </c>
-      <c r="K13" t="str">
-        <v/>
-      </c>
-      <c r="L13" t="str">
-        <v/>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B14">
+      <c r="B14" t="str">
         <v>310</v>
       </c>
       <c r="C14" t="str">
@@ -3180,21 +2712,12 @@
       <c r="I14" t="str">
         <v>현대자동차 연구개발본부</v>
       </c>
-      <c r="J14" t="str">
-        <v/>
-      </c>
-      <c r="K14" t="str">
-        <v/>
-      </c>
-      <c r="L14" t="str">
-        <v/>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B15">
+      <c r="B15" t="str">
         <v>320</v>
       </c>
       <c r="C15" t="str">
@@ -3218,21 +2741,12 @@
       <c r="I15" t="str">
         <v>현대제철</v>
       </c>
-      <c r="J15" t="str">
-        <v/>
-      </c>
-      <c r="K15" t="str">
-        <v/>
-      </c>
-      <c r="L15" t="str">
-        <v/>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B16">
+      <c r="B16" t="str">
         <v>330</v>
       </c>
       <c r="C16" t="str">
@@ -3256,21 +2770,12 @@
       <c r="I16" t="str">
         <v>현대자동차 연구개발본부</v>
       </c>
-      <c r="J16" t="str">
-        <v/>
-      </c>
-      <c r="K16" t="str">
-        <v/>
-      </c>
-      <c r="L16" t="str">
-        <v/>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B17">
+      <c r="B17" t="str">
         <v>340</v>
       </c>
       <c r="C17" t="str">
@@ -3294,21 +2799,12 @@
       <c r="I17" t="str">
         <v>KAIST 석사과정</v>
       </c>
-      <c r="J17" t="str">
-        <v/>
-      </c>
-      <c r="K17" t="str">
-        <v/>
-      </c>
-      <c r="L17" t="str">
-        <v/>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B18">
+      <c r="B18" t="str">
         <v>350</v>
       </c>
       <c r="C18" t="str">
@@ -3332,21 +2828,12 @@
       <c r="I18" t="str">
         <v>볼보그룹코리아</v>
       </c>
-      <c r="J18" t="str">
-        <v/>
-      </c>
-      <c r="K18" t="str">
-        <v/>
-      </c>
-      <c r="L18" t="str">
-        <v/>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B19">
+      <c r="B19" t="str">
         <v>360</v>
       </c>
       <c r="C19" t="str">
@@ -3370,18 +2857,8 @@
       <c r="I19" t="str">
         <v>—</v>
       </c>
-      <c r="J19" t="str">
-        <v/>
-      </c>
-      <c r="K19" t="str">
-        <v/>
-      </c>
-      <c r="L19" t="str">
-        <v/>
-      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:L19"/>
   </ignoredErrors>
@@ -3419,7 +2896,7 @@
       <c r="B2" t="str">
         <v>ResearchInterest</v>
       </c>
-      <c r="C2">
+      <c r="C2" t="str">
         <v>10</v>
       </c>
       <c r="D2" t="str">
@@ -3428,9 +2905,6 @@
       <c r="E2" t="str">
         <v>Analysis and design of electric machines</v>
       </c>
-      <c r="F2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -3439,7 +2913,7 @@
       <c r="B3" t="str">
         <v>ResearchInterest</v>
       </c>
-      <c r="C3">
+      <c r="C3" t="str">
         <v>20</v>
       </c>
       <c r="D3" t="str">
@@ -3448,9 +2922,6 @@
       <c r="E3" t="str">
         <v>Multi-physics analysis of electric machines</v>
       </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -3459,7 +2930,7 @@
       <c r="B4" t="str">
         <v>ResearchInterest</v>
       </c>
-      <c r="C4">
+      <c r="C4" t="str">
         <v>30</v>
       </c>
       <c r="D4" t="str">
@@ -3468,9 +2939,6 @@
       <c r="E4" t="str">
         <v>Model-based electric machine design</v>
       </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -3479,7 +2947,7 @@
       <c r="B5" t="str">
         <v>ResearchInterest</v>
       </c>
-      <c r="C5">
+      <c r="C5" t="str">
         <v>40</v>
       </c>
       <c r="D5" t="str">
@@ -3488,9 +2956,6 @@
       <c r="E5" t="str">
         <v>AI-assisted acceleration of designing of electric machines</v>
       </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -3499,7 +2964,7 @@
       <c r="B6" t="str">
         <v>ResearchInterest</v>
       </c>
-      <c r="C6">
+      <c r="C6" t="str">
         <v>50</v>
       </c>
       <c r="D6" t="str">
@@ -3508,9 +2973,6 @@
       <c r="E6" t="str">
         <v>Design of 1-D electrified propulsion system</v>
       </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
@@ -3519,7 +2981,7 @@
       <c r="B7" t="str">
         <v>ResearchInterest</v>
       </c>
-      <c r="C7">
+      <c r="C7" t="str">
         <v>60</v>
       </c>
       <c r="D7" t="str">
@@ -3528,9 +2990,6 @@
       <c r="E7" t="str">
         <v>Integrated inverter-motor system analysis</v>
       </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
@@ -3539,7 +2998,7 @@
       <c r="B8" t="str">
         <v>ResearchInterest</v>
       </c>
-      <c r="C8">
+      <c r="C8" t="str">
         <v>70</v>
       </c>
       <c r="D8" t="str">
@@ -3548,9 +3007,6 @@
       <c r="E8" t="str">
         <v>Thermal management of e-powertrain system</v>
       </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
@@ -3559,7 +3015,7 @@
       <c r="B9" t="str">
         <v>ResearchInterest</v>
       </c>
-      <c r="C9">
+      <c r="C9" t="str">
         <v>80</v>
       </c>
       <c r="D9" t="str">
@@ -3568,9 +3024,6 @@
       <c r="E9" t="str">
         <v>Design automation with commercial software</v>
       </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
@@ -3579,7 +3032,7 @@
       <c r="B10" t="str">
         <v>Education</v>
       </c>
-      <c r="C10">
+      <c r="C10" t="str">
         <v>90</v>
       </c>
       <c r="D10" t="str">
@@ -3599,7 +3052,7 @@
       <c r="B11" t="str">
         <v>Education</v>
       </c>
-      <c r="C11">
+      <c r="C11" t="str">
         <v>100</v>
       </c>
       <c r="D11" t="str">
@@ -3608,9 +3061,6 @@
       <c r="E11" t="str">
         <v>(B.S.) Department of Mechanical Engineering, Hanyang University</v>
       </c>
-      <c r="F11" t="str">
-        <v/>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
@@ -3619,7 +3069,7 @@
       <c r="B12" t="str">
         <v>Experience</v>
       </c>
-      <c r="C12">
+      <c r="C12" t="str">
         <v>110</v>
       </c>
       <c r="D12" t="str">
@@ -3628,9 +3078,6 @@
       <c r="E12" t="str">
         <v>Assistant Professor, Dongguk University</v>
       </c>
-      <c r="F12" t="str">
-        <v/>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
@@ -3639,7 +3086,7 @@
       <c r="B13" t="str">
         <v>Experience</v>
       </c>
-      <c r="C13">
+      <c r="C13" t="str">
         <v>120</v>
       </c>
       <c r="D13" t="str">
@@ -3648,9 +3095,6 @@
       <c r="E13" t="str">
         <v>Lecturer, Global Partnership Center, Hyundai Motor Group</v>
       </c>
-      <c r="F13" t="str">
-        <v/>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
@@ -3659,7 +3103,7 @@
       <c r="B14" t="str">
         <v>Experience</v>
       </c>
-      <c r="C14">
+      <c r="C14" t="str">
         <v>130</v>
       </c>
       <c r="D14" t="str">
@@ -3668,9 +3112,6 @@
       <c r="E14" t="str">
         <v>Senior Research Engineer, R&amp;D Division, Hyundai Motor Company</v>
       </c>
-      <c r="F14" t="str">
-        <v/>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
@@ -3679,7 +3120,7 @@
       <c r="B15" t="str">
         <v>Experience</v>
       </c>
-      <c r="C15">
+      <c r="C15" t="str">
         <v>140</v>
       </c>
       <c r="D15" t="str">
@@ -3688,9 +3129,6 @@
       <c r="E15" t="str">
         <v>Researcher, Korea Institute of Industrial Technology (KITECH)</v>
       </c>
-      <c r="F15" t="str">
-        <v/>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
@@ -3699,7 +3137,7 @@
       <c r="B16" t="str">
         <v>Award</v>
       </c>
-      <c r="C16">
+      <c r="C16" t="str">
         <v>150</v>
       </c>
       <c r="D16" t="str">
@@ -3708,9 +3146,6 @@
       <c r="E16" t="str">
         <v>신진연구 우수논문상, 대한기계학회 CAE및응용역학부문</v>
       </c>
-      <c r="F16" t="str">
-        <v/>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
@@ -3719,7 +3154,7 @@
       <c r="B17" t="str">
         <v>Award</v>
       </c>
-      <c r="C17">
+      <c r="C17" t="str">
         <v>160</v>
       </c>
       <c r="D17" t="str">
@@ -3728,9 +3163,6 @@
       <c r="E17" t="str">
         <v>우수신진연구자상, 한국PHM학회</v>
       </c>
-      <c r="F17" t="str">
-        <v/>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
@@ -3739,7 +3171,7 @@
       <c r="B18" t="str">
         <v>Award</v>
       </c>
-      <c r="C18">
+      <c r="C18" t="str">
         <v>170</v>
       </c>
       <c r="D18" t="str">
@@ -3748,9 +3180,6 @@
       <c r="E18" t="str">
         <v>신진연구 우수발표상, 전산구조공학회</v>
       </c>
-      <c r="F18" t="str">
-        <v/>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
@@ -3759,7 +3188,7 @@
       <c r="B19" t="str">
         <v>Award</v>
       </c>
-      <c r="C19">
+      <c r="C19" t="str">
         <v>180</v>
       </c>
       <c r="D19" t="str">
@@ -3768,9 +3197,6 @@
       <c r="E19" t="str">
         <v>EMC Prize Paper Award, IEEE Electric Machinery Committee</v>
       </c>
-      <c r="F19" t="str">
-        <v/>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
@@ -3779,7 +3205,7 @@
       <c r="B20" t="str">
         <v>Award</v>
       </c>
-      <c r="C20">
+      <c r="C20" t="str">
         <v>190</v>
       </c>
       <c r="D20" t="str">
@@ -3788,9 +3214,6 @@
       <c r="E20" t="str">
         <v>Distinguished Dissertation Award, Hanyang University</v>
       </c>
-      <c r="F20" t="str">
-        <v/>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
@@ -3799,7 +3222,7 @@
       <c r="B21" t="str">
         <v>Activity</v>
       </c>
-      <c r="C21">
+      <c r="C21" t="str">
         <v>200</v>
       </c>
       <c r="D21" t="str">
@@ -3808,9 +3231,6 @@
       <c r="E21" t="str">
         <v>학술이사, 대한전기학회 (전기기기 및 에너지변환시스템 부문)</v>
       </c>
-      <c r="F21" t="str">
-        <v/>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
@@ -3819,7 +3239,7 @@
       <c r="B22" t="str">
         <v>Activity</v>
       </c>
-      <c r="C22">
+      <c r="C22" t="str">
         <v>210</v>
       </c>
       <c r="D22" t="str">
@@ -3828,9 +3248,6 @@
       <c r="E22" t="str">
         <v>교육이사, 한국PHM학회</v>
       </c>
-      <c r="F22" t="str">
-        <v/>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
@@ -3839,7 +3256,7 @@
       <c r="B23" t="str">
         <v>Activity</v>
       </c>
-      <c r="C23">
+      <c r="C23" t="str">
         <v>220</v>
       </c>
       <c r="D23" t="str">
@@ -3848,9 +3265,6 @@
       <c r="E23" t="str">
         <v>산학협력이사, 대한기계학회 (CAE 및 응용역학 부문)</v>
       </c>
-      <c r="F23" t="str">
-        <v/>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
@@ -3859,7 +3273,7 @@
       <c r="B24" t="str">
         <v>Activity</v>
       </c>
-      <c r="C24">
+      <c r="C24" t="str">
         <v>230</v>
       </c>
       <c r="D24" t="str">
@@ -3868,9 +3282,6 @@
       <c r="E24" t="str">
         <v>Member, IEEE</v>
       </c>
-      <c r="F24" t="str">
-        <v/>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
@@ -3879,7 +3290,7 @@
       <c r="B25" t="str">
         <v>Activity</v>
       </c>
-      <c r="C25">
+      <c r="C25" t="str">
         <v>240</v>
       </c>
       <c r="D25" t="str">
@@ -3888,12 +3299,8 @@
       <c r="E25" t="str">
         <v>Reviewer: TIE, TMECH, TTE, TMAG, TEC, IEEE ACCESS, JEET, JOM</v>
       </c>
-      <c r="F25" t="str">
-        <v/>
-      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:F25"/>
   </ignoredErrors>
@@ -3902,7 +3309,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:G7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3924,9 +3331,6 @@
         <v>description</v>
       </c>
       <c r="G1" t="str">
-        <v>tags</v>
-      </c>
-      <c r="H1" t="str">
         <v>image_url</v>
       </c>
     </row>
@@ -3934,7 +3338,7 @@
       <c r="A2" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B2">
+      <c r="B2" t="str">
         <v>10</v>
       </c>
       <c r="C2" t="str">
@@ -3947,20 +3351,14 @@
         <v>전기기기 설계</v>
       </c>
       <c r="F2" t="str">
-        <v>전자기 등가회로와 유한요소해석을 기반으로 IPMSM, SPMSM, WFSM, 축방향자속 전동기의 초기 사이징부터 형상 최적설계까지 수행합니다.</v>
-      </c>
-      <c r="G2" t="str">
-        <v>IPMSM, Sizing, Optimization</v>
-      </c>
-      <c r="H2" t="str">
-        <v/>
+        <v>전자기 등가회로와 유한요소해석을 기반으로 PMSM, WFSM, AFPM 등 고성능 전기기기의 다중물리 고려 최적설계 프로세스를 연구합니다.</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B3">
+      <c r="B3" t="str">
         <v>20</v>
       </c>
       <c r="C3" t="str">
@@ -3975,128 +3373,97 @@
       <c r="F3" t="str">
         <v>전자기-열-구조-제어 영역을 연계한 해석 체계를 구축하여, 실제 운전 조건에서의 손실과 성능을 예측하고 시험 결과와의 정합성을 향상시킵니다.</v>
       </c>
-      <c r="G3" t="str">
-        <v>Coupled analysis, AC copper loss, Iron loss</v>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B4">
+      <c r="B4" t="str">
         <v>30</v>
       </c>
       <c r="C4" t="str">
         <v>T-03</v>
       </c>
       <c r="D4" t="str">
-        <v>NVH analysis of electric machinery</v>
+        <v>Design of cooling system for electric machinery</v>
       </c>
       <c r="E4" t="str">
-        <v>전기기기 진동·소음 해석</v>
+        <v>전기기기 냉각시스템 설계</v>
       </c>
       <c r="F4" t="str">
-        <v>극/슬롯 조합에 따른 전자기 가진력과 모드 특성을 분석하여 구동모터 및 압축기의 진동·소음을 저감하는 설계 방법을 연구합니다.</v>
-      </c>
-      <c r="G4" t="str">
-        <v>Radial force, Modal analysis, Vibration</v>
-      </c>
-      <c r="H4" t="str">
-        <v/>
+        <v>전자기-열 연성해석을 바탕으로 권선·자석 등 주요 부품의 온도 상승을 억제하고 전기기기의 신뢰성 확보를 위한 고성능 냉각시스템을 설계합니다.</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B5">
+      <c r="B5" t="str">
         <v>40</v>
       </c>
       <c r="C5" t="str">
         <v>T-04</v>
       </c>
       <c r="D5" t="str">
-        <v>Thermal analysis of electric machinery</v>
+        <v>Thermal management of electrified powertrain</v>
       </c>
       <c r="E5" t="str">
-        <v>전기기기 열해석</v>
+        <v>전동화 파워트레인 열관리</v>
       </c>
       <c r="F5" t="str">
-        <v>권선·자석·회전자의 발열 특성과 냉각 구조를 열등가회로 및 CFD로 해석하여 연속/최대 출력 성능의 한계를 규명합니다.</v>
-      </c>
-      <c r="G5" t="str">
-        <v>LPTN, Cooling, Demagnetization</v>
-      </c>
-      <c r="H5" t="str">
-        <v/>
+        <v>인버터-모터-감속기를 포함한 전동화 파워트레인의 1-D 시스템 모델을 구축하고, 차량 열관리 전략과 비효율 제어 기반 발열 모드를 연구합니다.</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B6">
+      <c r="B6" t="str">
         <v>50</v>
       </c>
       <c r="C6" t="str">
         <v>T-05</v>
       </c>
       <c r="D6" t="str">
-        <v>Thermal management of electrified powertrain</v>
+        <v>Agentic AI-based design automation of electric machinery</v>
       </c>
       <c r="E6" t="str">
-        <v>전동화 파워트레인 열관리</v>
+        <v>AI 기반 전기기기 설계 자동화</v>
       </c>
       <c r="F6" t="str">
-        <v>인버터-모터-감속기를 포함한 전동화 파워트레인의 1-D 시스템 모델을 구축하고, 차량 열관리 전략과 비효율 제어 기반 발열 모드를 검토합니다.</v>
-      </c>
-      <c r="G6" t="str">
-        <v>1-D system, e-Powertrain, VTM</v>
-      </c>
-      <c r="H6" t="str">
-        <v/>
+        <v>상용 해석 소프트웨어와 AI 에이전트를 연계하여 설계 자동화를 위한 코드 개발을 수행합니다.</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B7">
+      <c r="B7" t="str">
         <v>60</v>
       </c>
       <c r="C7" t="str">
         <v>T-06</v>
       </c>
       <c r="D7" t="str">
-        <v>AI-assisted acceleration of designing electric machinery</v>
+        <v>Multi-fidelity surrogate modeling for efficient design optimization of electric machinery</v>
       </c>
       <c r="E7" t="str">
-        <v>AI 기반 전기기기 설계 가속</v>
+        <v>다중충실도 대리모델 기반 전기기기 설계 가속화</v>
       </c>
       <c r="F7" t="str">
-        <v>심층전이학습과 능동학습, 다중충실도 대체모델을 활용하여 해석 비용이 큰 설계 문제의 탐색 시간을 획기적으로 단축합니다.</v>
-      </c>
-      <c r="G7" t="str">
-        <v>Transfer learning, Active learning, Surrogate</v>
-      </c>
-      <c r="H7" t="str">
-        <v/>
+        <v>저비용의 Low-fidelity 데이터와 고비용의 High-fidelity를 연계한 다중충실도 대리모델을 바탕으로 전기기기 설계/해석/시험 가속화를 위한 다양한 연구를 수행합니다.</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G7"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J27"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -4109,7 +3476,7 @@
         <v>status</v>
       </c>
       <c r="D1" t="str">
-        <v>title_en</v>
+        <v>role</v>
       </c>
       <c r="E1" t="str">
         <v>title_ko</v>
@@ -4134,81 +3501,75 @@
       <c r="A2" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B2">
-        <v>10</v>
+      <c r="B2" t="str">
+        <v>260</v>
       </c>
       <c r="C2" t="str">
-        <v>Ongoing</v>
+        <v>Completed</v>
       </c>
       <c r="D2" t="str">
-        <v>Current command map extraction based on measured data for improving motor system efficiency</v>
+        <v/>
       </c>
       <c r="E2" t="str">
-        <v>모터시스템 효율 향상을 위한 실측데이터 기반 전류지령맵 추출 기술 개발</v>
+        <v>전기자동차의 전비 향상을 위한 구동모터 냉각시스템의 최적제어에 관한 연구</v>
       </c>
       <c r="F2" t="str">
-        <v>현대자동차</v>
+        <v>동국대학교</v>
       </c>
       <c r="G2" t="str">
         <v/>
       </c>
       <c r="H2" t="str">
-        <v>2026.03</v>
+        <v>2023.09</v>
       </c>
       <c r="I2" t="str">
-        <v>2026.12</v>
-      </c>
-      <c r="J2" t="str">
-        <v/>
+        <v>2025.02</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B3">
-        <v>20</v>
+      <c r="B3" t="str">
+        <v>250</v>
       </c>
       <c r="C3" t="str">
-        <v>Ongoing</v>
+        <v>Completed</v>
       </c>
       <c r="D3" t="str">
-        <v>Analysis model for reviewing vehicle thermal management performance under PE inefficiency control</v>
+        <v/>
       </c>
       <c r="E3" t="str">
-        <v>PE 비효율 제어 시, 차량 열관리 시스템 성능 검토를 위한 해석 모델 개발</v>
+        <v>수리온(KUH-1)용 NR 센서의 작동 메커니즘 분석</v>
       </c>
       <c r="F3" t="str">
-        <v>현대자동차</v>
+        <v>국방기술진흥연구소</v>
       </c>
       <c r="G3" t="str">
         <v/>
       </c>
       <c r="H3" t="str">
-        <v>2026.03</v>
+        <v>2023.11</v>
       </c>
       <c r="I3" t="str">
-        <v>2026.12</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
+        <v>2024.11</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B4">
-        <v>30</v>
+      <c r="B4" t="str">
+        <v>240</v>
       </c>
       <c r="C4" t="str">
-        <v>Ongoing</v>
+        <v>Completed</v>
       </c>
       <c r="D4" t="str">
-        <v>PE system optimization for low-cost motors</v>
+        <v/>
       </c>
       <c r="E4" t="str">
-        <v>저가형 모터를 위한 PE 시스템 최적화 기술 개발</v>
+        <v>비희토류 PMa-SynRM 고속화를 위한 회전자 최적 설계 기법 개발</v>
       </c>
       <c r="F4" t="str">
         <v>현대자동차</v>
@@ -4217,187 +3578,169 @@
         <v/>
       </c>
       <c r="H4" t="str">
-        <v>2026.03</v>
+        <v>2024.02</v>
       </c>
       <c r="I4" t="str">
-        <v>2026.12</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
+        <v>2024.12</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B5">
-        <v>40</v>
+      <c r="B5" t="str">
+        <v>230</v>
       </c>
       <c r="C5" t="str">
-        <v>Ongoing</v>
+        <v>Completed</v>
       </c>
       <c r="D5" t="str">
-        <v>LECM fault analysis and design for eco-fuel HiMSEN engine solenoid valves</v>
+        <v/>
       </c>
       <c r="E5" t="str">
-        <v>친환경연료 힘센엔진 솔레노이드 밸브 LECM Fault 분석 및 설계 기술 개발</v>
+        <v>VTM 모델의 전비 예측 정확도 향상을 위한 2-Stage PE 시스템 손실맵 확장 프로세스 개발</v>
       </c>
       <c r="F5" t="str">
-        <v>HD현대중공업</v>
+        <v>현대자동차</v>
       </c>
       <c r="G5" t="str">
         <v/>
       </c>
       <c r="H5" t="str">
-        <v>2026.03</v>
+        <v>2024.02</v>
       </c>
       <c r="I5" t="str">
-        <v>2026.12</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
+        <v>2024.12</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B6">
-        <v>50</v>
+      <c r="B6" t="str">
+        <v>220</v>
       </c>
       <c r="C6" t="str">
-        <v>Ongoing</v>
+        <v>Completed</v>
       </c>
       <c r="D6" t="str">
-        <v>Analysis and test-evaluation for solenoid valves of eco-fuel HiMSEN engine fuel injection pump (e-FIP)</v>
+        <v/>
       </c>
       <c r="E6" t="str">
-        <v>친환경연료 힘센엔진 연료분사펌프(e-FIP)용 솔레노이드 밸브 해석 및 시험평가 기술 개발</v>
+        <v>스마트 헬스케어 머신의 감성품질 향상을 위한 부하정밀제어 캘리브레이션 기술개발 및 출고 검사 장비 개발</v>
       </c>
       <c r="F6" t="str">
-        <v>HD현대중공업</v>
+        <v>과학기술정보통신부</v>
       </c>
       <c r="G6" t="str">
         <v/>
       </c>
       <c r="H6" t="str">
-        <v>2025.09</v>
+        <v>2024.08</v>
       </c>
       <c r="I6" t="str">
-        <v>2026.08</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
+        <v>2024.11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B7">
-        <v>60</v>
+      <c r="B7" t="str">
+        <v>210</v>
       </c>
       <c r="C7" t="str">
-        <v>Ongoing</v>
+        <v>Completed</v>
       </c>
       <c r="D7" t="str">
-        <v>Development of axial-flux machines applying flat-wire distributed winding technology</v>
+        <v/>
       </c>
       <c r="E7" t="str">
-        <v>평각동선 분포권 기술 적용 축방향자속 전동기 개발</v>
+        <v>구동모터 특성해석 시간 단축을 위한 프로그램 개발</v>
       </c>
       <c r="F7" t="str">
-        <v>효성전기 · 한국자동차연구원 · 대구대학교</v>
+        <v>현대트랜시스</v>
       </c>
       <c r="G7" t="str">
         <v/>
       </c>
       <c r="H7" t="str">
-        <v>2025.04</v>
+        <v>2024.08</v>
       </c>
       <c r="I7" t="str">
-        <v>2027.12</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
+        <v>2025.08</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B8">
-        <v>70</v>
+      <c r="B8" t="str">
+        <v>200</v>
       </c>
       <c r="C8" t="str">
         <v>Completed</v>
       </c>
       <c r="D8" t="str">
-        <v>e2DT drive-motor excitation-force optimal design</v>
+        <v/>
       </c>
       <c r="E8" t="str">
-        <v>e2DT 구동모터 가진력 최적 설계 개발</v>
+        <v>회전자 관성을 이용한 토크 산정 알고리즘 개선</v>
       </c>
       <c r="F8" t="str">
-        <v>현대트랜시스</v>
+        <v>한국생산기술연구원</v>
       </c>
       <c r="G8" t="str">
         <v/>
       </c>
       <c r="H8" t="str">
-        <v>2025.03</v>
+        <v>2024.09</v>
       </c>
       <c r="I8" t="str">
-        <v>2025.12</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
+        <v>2024.11</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B9">
-        <v>80</v>
+      <c r="B9" t="str">
+        <v>190</v>
       </c>
       <c r="C9" t="str">
         <v>Completed</v>
       </c>
       <c r="D9" t="str">
-        <v>System analysis, modeling, verification, and simulation tool for resonance analysis of high-voltage power-net networks</v>
+        <v/>
       </c>
       <c r="E9" t="str">
-        <v>고전압 파워넷 네트워크의 공진 해석을 위한 시스템 해석 기법 및 모델링, 검증, 시뮬레이션 툴 개발</v>
+        <v>전기자동차 주행가능거리 극대화를 위한 구동모터/인버터, 냉각시스템의 비효율 전류벡터제어 기반 최적제어</v>
       </c>
       <c r="F9" t="str">
-        <v>현대자동차</v>
+        <v>한국연구재단(석사과정생연구장려금지원사업)</v>
       </c>
       <c r="G9" t="str">
         <v/>
       </c>
       <c r="H9" t="str">
-        <v>2025.03</v>
+        <v>2024.09</v>
       </c>
       <c r="I9" t="str">
-        <v>2025.12</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
+        <v>2025.09</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B10">
-        <v>90</v>
+      <c r="B10" t="str">
+        <v>180</v>
       </c>
       <c r="C10" t="str">
         <v>Completed</v>
       </c>
       <c r="D10" t="str">
-        <v>Power model construction and PE-system scaling method for VTM base technology and data building</v>
+        <v/>
       </c>
       <c r="E10" t="str">
         <v>VTM 기반기술 확보 및 데이터 구축을 위한 전력 모델 구축 및 PE시스템 Scaling 기법 개발</v>
@@ -4412,144 +3755,505 @@
         <v>2025.02</v>
       </c>
       <c r="I10" t="str">
-        <v>2025.11</v>
-      </c>
-      <c r="J10" t="str">
-        <v/>
+        <v>2025.12</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B11">
-        <v>100</v>
+      <c r="B11" t="str">
+        <v>170</v>
       </c>
       <c r="C11" t="str">
         <v>Completed</v>
       </c>
       <c r="D11" t="str">
-        <v>Improvement of torque estimation algorithm using rotor inertia</v>
+        <v/>
       </c>
       <c r="E11" t="str">
-        <v>회전자 관성을 이용한 토크 산정 알고리즘 개선</v>
+        <v>e2DT 구동모터 가진력 최적 설계 개발</v>
       </c>
       <c r="F11" t="str">
-        <v>한국생산기술연구원</v>
+        <v>현대트랜시스</v>
       </c>
       <c r="G11" t="str">
         <v/>
       </c>
       <c r="H11" t="str">
-        <v>2024.09</v>
+        <v>2025.03</v>
       </c>
       <c r="I11" t="str">
-        <v>2024.12</v>
-      </c>
-      <c r="J11" t="str">
-        <v/>
+        <v>2025.10</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B12">
-        <v>110</v>
+      <c r="B12" t="str">
+        <v>160</v>
       </c>
       <c r="C12" t="str">
         <v>Completed</v>
       </c>
       <c r="D12" t="str">
-        <v>Load-precision-control calibration technology and shipment inspection equipment for smart healthcare machines</v>
+        <v/>
       </c>
       <c r="E12" t="str">
-        <v>스마트 헬스케어 머신의 감성품질 향상을 위한 부하정밀제어 캘리브레이션 기술개발 및 출고 검사 장비 개발</v>
+        <v>고전압 파워넷 네트워크의 공진 해석을 위한 시스템 해석 기법 및 모델링, 검증, 시뮬레이션 툴 개발</v>
       </c>
       <c r="F12" t="str">
-        <v>WESPION</v>
+        <v>현대자동차</v>
       </c>
       <c r="G12" t="str">
         <v/>
       </c>
       <c r="H12" t="str">
-        <v>2024.08</v>
+        <v>2025.03</v>
       </c>
       <c r="I12" t="str">
-        <v>2025.07</v>
-      </c>
-      <c r="J12" t="str">
-        <v/>
+        <v>2026.02</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B13">
-        <v>120</v>
+      <c r="B13" t="str">
+        <v>150</v>
       </c>
       <c r="C13" t="str">
         <v>Completed</v>
       </c>
       <c r="D13" t="str">
-        <v>Program development for reducing drive-motor characteristic analysis time</v>
+        <v/>
       </c>
       <c r="E13" t="str">
-        <v>구동모터 특성해석 시간 단축을 위한 프로그램 개발</v>
+        <v>친환경연료 힘센엔진 연료분사펌프(e-FIP)용 솔레노이드 밸브 해석 및 시험평가 기술 개발</v>
       </c>
       <c r="F13" t="str">
-        <v>현대트랜시스</v>
+        <v>HD현대중공업</v>
       </c>
       <c r="G13" t="str">
         <v/>
       </c>
       <c r="H13" t="str">
-        <v>2024.08</v>
+        <v>2025.09</v>
       </c>
       <c r="I13" t="str">
-        <v>2024.12</v>
-      </c>
-      <c r="J13" t="str">
-        <v/>
+        <v>2025.12</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B14">
-        <v>130</v>
+      <c r="B14" t="str">
+        <v>140</v>
       </c>
       <c r="C14" t="str">
         <v>Completed</v>
       </c>
       <c r="D14" t="str">
-        <v>2-Stage PE system loss-map extension process for improving fuel-economy prediction accuracy of VTM model</v>
+        <v/>
       </c>
       <c r="E14" t="str">
-        <v>VTM 모델의 전비 예측 정확도 향상을 위한 2-Stage PE 시스템 손실맵 확장 프로세스 개발</v>
+        <v>피트니스 인공지능 개발을 위한 고분해능 기어리스 자기식 엔코더 기반 전동식 피트니스 머신 구동부 기술 개발</v>
       </c>
       <c r="F14" t="str">
+        <v>서울연구원(RISE사업)</v>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v>2025.09</v>
+      </c>
+      <c r="I14" t="str">
+        <v>2026.01</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="B15" t="str">
+        <v>130</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Ongoing</v>
+      </c>
+      <c r="D15" t="str">
+        <v/>
+      </c>
+      <c r="E15" t="str">
+        <v>AI-핵심소재 기반 첨단산업 지능형 로봇 글로벌인재양성</v>
+      </c>
+      <c r="F15" t="str">
+        <v>한국산업기술진흥원</v>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v>2024.03</v>
+      </c>
+      <c r="I15" t="str">
+        <v>2027.02</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="B16" t="str">
+        <v>120</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Ongoing</v>
+      </c>
+      <c r="D16" t="str">
+        <v/>
+      </c>
+      <c r="E16" t="str">
+        <v>평각동선 분포권 기술 적용 축방향자속 전동기 개발</v>
+      </c>
+      <c r="F16" t="str">
+        <v>효성전기 · 한국자동차연구원 · 대구대학교</v>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v>2025.04</v>
+      </c>
+      <c r="I16" t="str">
+        <v>2028.12</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="B17" t="str">
+        <v>110</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Ongoing</v>
+      </c>
+      <c r="D17" t="str">
+        <v/>
+      </c>
+      <c r="E17" t="str">
+        <v>다족보행로봇의 에너지효율 향상을 위한 다중물리모델 기반 구동계 최적설계기술 연구</v>
+      </c>
+      <c r="F17" t="str">
+        <v>한국연구재단(석사과정생연구장려금지원사업)</v>
+      </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
+      <c r="H17" t="str">
+        <v>2025.09</v>
+      </c>
+      <c r="I17" t="str">
+        <v>2026.09</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="B18" t="str">
+        <v>100</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Ongoing</v>
+      </c>
+      <c r="D18" t="str">
+        <v/>
+      </c>
+      <c r="E18" t="str">
+        <v>전기차 파워트레인의 데이터 주도 고장예지를 위한 고장데이터 생성 다중물리 해석모델 연구</v>
+      </c>
+      <c r="F18" t="str">
+        <v>한국연구재단(석사과정생연구장려금지원사업)</v>
+      </c>
+      <c r="G18" t="str">
+        <v/>
+      </c>
+      <c r="H18" t="str">
+        <v>2025.09</v>
+      </c>
+      <c r="I18" t="str">
+        <v>2026.09</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="B19" t="str">
+        <v>90</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Ongoing</v>
+      </c>
+      <c r="D19" t="str">
+        <v/>
+      </c>
+      <c r="E19" t="str">
+        <v>PE 비효율 제어 시, 차량 열관리 시스템 성능 검토를 위한 해석 모델 개발</v>
+      </c>
+      <c r="F19" t="str">
         <v>현대자동차</v>
       </c>
-      <c r="G14" t="str">
-        <v/>
-      </c>
-      <c r="H14" t="str">
-        <v>2024.03</v>
-      </c>
-      <c r="I14" t="str">
-        <v>2024.12</v>
-      </c>
-      <c r="J14" t="str">
-        <v/>
+      <c r="G19" t="str">
+        <v/>
+      </c>
+      <c r="H19" t="str">
+        <v>2026.02</v>
+      </c>
+      <c r="I19" t="str">
+        <v>2026.12</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="B20" t="str">
+        <v>80</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Ongoing</v>
+      </c>
+      <c r="D20" t="str">
+        <v/>
+      </c>
+      <c r="E20" t="str">
+        <v>모터시스템 효율 향상을 위한 실측데이터 기반 전류지령맵 추출 기술 개발</v>
+      </c>
+      <c r="F20" t="str">
+        <v>현대자동차</v>
+      </c>
+      <c r="G20" t="str">
+        <v/>
+      </c>
+      <c r="H20" t="str">
+        <v>2026.03</v>
+      </c>
+      <c r="I20" t="str">
+        <v>2026.09</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="B21" t="str">
+        <v>70</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Ongoing</v>
+      </c>
+      <c r="D21" t="str">
+        <v/>
+      </c>
+      <c r="E21" t="str">
+        <v>저가형 모터를 위한 PE 시스템 최적화 기술 개발</v>
+      </c>
+      <c r="F21" t="str">
+        <v>현대자동차</v>
+      </c>
+      <c r="G21" t="str">
+        <v/>
+      </c>
+      <c r="H21" t="str">
+        <v>2026.04</v>
+      </c>
+      <c r="I21" t="str">
+        <v>2027.04</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="B22" t="str">
+        <v>60</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Ongoing</v>
+      </c>
+      <c r="D22" t="str">
+        <v/>
+      </c>
+      <c r="E22" t="str">
+        <v>친환경연료 힘센엔진 솔레노이드 밸브 LECM Fault 분석 및 설계 기술 개발</v>
+      </c>
+      <c r="F22" t="str">
+        <v>HD현대중공업</v>
+      </c>
+      <c r="G22" t="str">
+        <v/>
+      </c>
+      <c r="H22" t="str">
+        <v>2026.03</v>
+      </c>
+      <c r="I22" t="str">
+        <v>2026.11</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="B23" t="str">
+        <v>50</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Ongoing</v>
+      </c>
+      <c r="D23" t="str">
+        <v/>
+      </c>
+      <c r="E23" t="str">
+        <v>T/L 세탁기 모터 구동부 박형 기술 개발</v>
+      </c>
+      <c r="F23" t="str">
+        <v>LG전자</v>
+      </c>
+      <c r="G23" t="str">
+        <v/>
+      </c>
+      <c r="H23" t="str">
+        <v>2026.05</v>
+      </c>
+      <c r="I23" t="str">
+        <v>2027.01</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="B24" t="str">
+        <v>40</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Ongoing</v>
+      </c>
+      <c r="D24" t="str">
+        <v/>
+      </c>
+      <c r="E24" t="str">
+        <v>EV/HEV 보조 구동 성능 향상을 위한 WRSM 전자기 설계</v>
+      </c>
+      <c r="F24" t="str">
+        <v>현대자동차</v>
+      </c>
+      <c r="G24" t="str">
+        <v/>
+      </c>
+      <c r="H24" t="str">
+        <v>2026.06</v>
+      </c>
+      <c r="I24" t="str">
+        <v>2027.06</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="B25" t="str">
+        <v>30</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Ongoing</v>
+      </c>
+      <c r="D25" t="str">
+        <v/>
+      </c>
+      <c r="E25" t="str">
+        <v>축방향 극대 온도차 터보기기 구동모터의 열강건성을 위한 열해석 및 열차폐 구조설계</v>
+      </c>
+      <c r="F25" t="str">
+        <v>서울앵커(ANCHOR)사업</v>
+      </c>
+      <c r="G25" t="str">
+        <v/>
+      </c>
+      <c r="H25" t="str">
+        <v>2026.07</v>
+      </c>
+      <c r="I25" t="str">
+        <v>2026.12</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="B26" t="str">
+        <v>20</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Ongoing</v>
+      </c>
+      <c r="D26" t="str">
+        <v/>
+      </c>
+      <c r="E26" t="str">
+        <v>Super-resolution</v>
+      </c>
+      <c r="F26" t="str">
+        <v>한국연구재단(석사과정생연구장려금지원사업)</v>
+      </c>
+      <c r="G26" t="str">
+        <v/>
+      </c>
+      <c r="H26" t="str">
+        <v>2026.09</v>
+      </c>
+      <c r="I26" t="str">
+        <v>2027.08</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="B27" t="str">
+        <v>10</v>
+      </c>
+      <c r="C27" t="str">
+        <v>Ongoing</v>
+      </c>
+      <c r="D27" t="str">
+        <v/>
+      </c>
+      <c r="E27" t="str">
+        <v>상변환물질 기반 잠열을 활용한 휴머노이드 로봇 관절 액추에이터의 순간 과부하 열관리 기법 개발</v>
+      </c>
+      <c r="F27" t="str">
+        <v>한국연구재단(개인기초연구-기본연구A)</v>
+      </c>
+      <c r="G27" t="str">
+        <v/>
+      </c>
+      <c r="H27" t="str">
+        <v>2026.09</v>
+      </c>
+      <c r="I27" t="str">
+        <v>2028.08</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J14"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J27"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -4591,7 +4295,7 @@
       <c r="A2" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B2">
+      <c r="B2" t="str">
         <v>10</v>
       </c>
       <c r="C2" t="str">
@@ -4620,7 +4324,7 @@
       <c r="A3" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B3">
+      <c r="B3" t="str">
         <v>20</v>
       </c>
       <c r="C3" t="str">
@@ -4649,7 +4353,7 @@
       <c r="A4" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B4">
+      <c r="B4" t="str">
         <v>30</v>
       </c>
       <c r="C4" t="str">
@@ -4678,7 +4382,7 @@
       <c r="A5" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B5">
+      <c r="B5" t="str">
         <v>40</v>
       </c>
       <c r="C5" t="str">
@@ -4707,7 +4411,7 @@
       <c r="A6" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B6">
+      <c r="B6" t="str">
         <v>50</v>
       </c>
       <c r="C6" t="str">
@@ -4736,7 +4440,7 @@
       <c r="A7" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B7">
+      <c r="B7" t="str">
         <v>60</v>
       </c>
       <c r="C7" t="str">
@@ -4765,7 +4469,7 @@
       <c r="A8" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B8">
+      <c r="B8" t="str">
         <v>70</v>
       </c>
       <c r="C8" t="str">
@@ -4794,7 +4498,7 @@
       <c r="A9" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B9">
+      <c r="B9" t="str">
         <v>80</v>
       </c>
       <c r="C9" t="str">
@@ -4823,7 +4527,7 @@
       <c r="A10" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B10">
+      <c r="B10" t="str">
         <v>90</v>
       </c>
       <c r="C10" t="str">
@@ -4852,7 +4556,7 @@
       <c r="A11" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B11">
+      <c r="B11" t="str">
         <v>100</v>
       </c>
       <c r="C11" t="str">
@@ -4881,7 +4585,7 @@
       <c r="A12" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B12">
+      <c r="B12" t="str">
         <v>110</v>
       </c>
       <c r="C12" t="str">
@@ -4910,7 +4614,7 @@
       <c r="A13" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B13">
+      <c r="B13" t="str">
         <v>120</v>
       </c>
       <c r="C13" t="str">
@@ -4939,7 +4643,7 @@
       <c r="A14" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B14">
+      <c r="B14" t="str">
         <v>130</v>
       </c>
       <c r="C14" t="str">
@@ -4968,7 +4672,7 @@
       <c r="A15" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B15">
+      <c r="B15" t="str">
         <v>140</v>
       </c>
       <c r="C15" t="str">
@@ -4997,7 +4701,7 @@
       <c r="A16" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B16">
+      <c r="B16" t="str">
         <v>150</v>
       </c>
       <c r="C16" t="str">
@@ -5026,7 +4730,7 @@
       <c r="A17" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B17">
+      <c r="B17" t="str">
         <v>160</v>
       </c>
       <c r="C17" t="str">
@@ -5055,7 +4759,7 @@
       <c r="A18" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B18">
+      <c r="B18" t="str">
         <v>170</v>
       </c>
       <c r="C18" t="str">
@@ -5084,7 +4788,7 @@
       <c r="A19" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B19">
+      <c r="B19" t="str">
         <v>180</v>
       </c>
       <c r="C19" t="str">
@@ -5113,7 +4817,7 @@
       <c r="A20" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B20">
+      <c r="B20" t="str">
         <v>190</v>
       </c>
       <c r="C20" t="str">
@@ -5142,7 +4846,7 @@
       <c r="A21" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B21">
+      <c r="B21" t="str">
         <v>200</v>
       </c>
       <c r="C21" t="str">
@@ -5171,7 +4875,7 @@
       <c r="A22" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B22">
+      <c r="B22" t="str">
         <v>210</v>
       </c>
       <c r="C22" t="str">
@@ -5200,7 +4904,7 @@
       <c r="A23" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B23">
+      <c r="B23" t="str">
         <v>220</v>
       </c>
       <c r="C23" t="str">
@@ -5229,7 +4933,7 @@
       <c r="A24" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B24">
+      <c r="B24" t="str">
         <v>230</v>
       </c>
       <c r="C24" t="str">
@@ -5258,7 +4962,7 @@
       <c r="A25" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B25">
+      <c r="B25" t="str">
         <v>240</v>
       </c>
       <c r="C25" t="str">
@@ -5287,7 +4991,7 @@
       <c r="A26" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B26">
+      <c r="B26" t="str">
         <v>250</v>
       </c>
       <c r="C26" t="str">
@@ -5316,7 +5020,7 @@
       <c r="A27" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B27">
+      <c r="B27" t="str">
         <v>260</v>
       </c>
       <c r="C27" t="str">
@@ -5345,7 +5049,7 @@
       <c r="A28" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B28">
+      <c r="B28" t="str">
         <v>270</v>
       </c>
       <c r="C28" t="str">
@@ -5374,7 +5078,7 @@
       <c r="A29" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B29">
+      <c r="B29" t="str">
         <v>280</v>
       </c>
       <c r="C29" t="str">
@@ -5403,7 +5107,7 @@
       <c r="A30" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B30">
+      <c r="B30" t="str">
         <v>290</v>
       </c>
       <c r="C30" t="str">
@@ -5432,7 +5136,7 @@
       <c r="A31" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B31">
+      <c r="B31" t="str">
         <v>300</v>
       </c>
       <c r="C31" t="str">
@@ -5461,7 +5165,7 @@
       <c r="A32" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B32">
+      <c r="B32" t="str">
         <v>310</v>
       </c>
       <c r="C32" t="str">
@@ -5490,7 +5194,7 @@
       <c r="A33" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B33">
+      <c r="B33" t="str">
         <v>320</v>
       </c>
       <c r="C33" t="str">
@@ -5519,7 +5223,7 @@
       <c r="A34" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B34">
+      <c r="B34" t="str">
         <v>330</v>
       </c>
       <c r="C34" t="str">
@@ -5548,7 +5252,7 @@
       <c r="A35" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B35">
+      <c r="B35" t="str">
         <v>340</v>
       </c>
       <c r="C35" t="str">
@@ -5574,7 +5278,6 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:I35"/>
   </ignoredErrors>
@@ -5745,7 +5448,7 @@
       <c r="A2" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B2">
+      <c r="B2" t="str">
         <v>10</v>
       </c>
       <c r="C2" t="str">
@@ -5763,18 +5466,12 @@
       <c r="G2" t="str">
         <v>US 11,848,598 B2</v>
       </c>
-      <c r="H2" t="str">
-        <v/>
-      </c>
-      <c r="I2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
         <v>TRUE</v>
       </c>
-      <c r="B3">
+      <c r="B3" t="str">
         <v>20</v>
       </c>
       <c r="C3" t="str">
@@ -5792,15 +5489,8 @@
       <c r="G3" t="str">
         <v>US 11,757,383 B2</v>
       </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v/>
-      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:I3"/>
   </ignoredErrors>

--- a/eplab_website_content.xlsx
+++ b/eplab_website_content.xlsx
@@ -3463,7 +3463,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:I27"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -3485,15 +3485,12 @@
         <v>partner</v>
       </c>
       <c r="G1" t="str">
-        <v>partner_logo_url</v>
+        <v>period_start</v>
       </c>
       <c r="H1" t="str">
-        <v>period_start</v>
+        <v>period_end</v>
       </c>
       <c r="I1" t="str">
-        <v>period_end</v>
-      </c>
-      <c r="J1" t="str">
         <v>notes</v>
       </c>
     </row>
@@ -3508,7 +3505,7 @@
         <v>Completed</v>
       </c>
       <c r="D2" t="str">
-        <v/>
+        <v>PI</v>
       </c>
       <c r="E2" t="str">
         <v>전기자동차의 전비 향상을 위한 구동모터 냉각시스템의 최적제어에 관한 연구</v>
@@ -3517,12 +3514,9 @@
         <v>동국대학교</v>
       </c>
       <c r="G2" t="str">
-        <v/>
+        <v>2023.09</v>
       </c>
       <c r="H2" t="str">
-        <v>2023.09</v>
-      </c>
-      <c r="I2" t="str">
         <v>2025.02</v>
       </c>
     </row>
@@ -3537,7 +3531,7 @@
         <v>Completed</v>
       </c>
       <c r="D3" t="str">
-        <v/>
+        <v>PI</v>
       </c>
       <c r="E3" t="str">
         <v>수리온(KUH-1)용 NR 센서의 작동 메커니즘 분석</v>
@@ -3546,12 +3540,9 @@
         <v>국방기술진흥연구소</v>
       </c>
       <c r="G3" t="str">
-        <v/>
+        <v>2023.11</v>
       </c>
       <c r="H3" t="str">
-        <v>2023.11</v>
-      </c>
-      <c r="I3" t="str">
         <v>2024.11</v>
       </c>
     </row>
@@ -3566,7 +3557,7 @@
         <v>Completed</v>
       </c>
       <c r="D4" t="str">
-        <v/>
+        <v>Co-I</v>
       </c>
       <c r="E4" t="str">
         <v>비희토류 PMa-SynRM 고속화를 위한 회전자 최적 설계 기법 개발</v>
@@ -3575,12 +3566,9 @@
         <v>현대자동차</v>
       </c>
       <c r="G4" t="str">
-        <v/>
+        <v>2024.02</v>
       </c>
       <c r="H4" t="str">
-        <v>2024.02</v>
-      </c>
-      <c r="I4" t="str">
         <v>2024.12</v>
       </c>
     </row>
@@ -3595,7 +3583,7 @@
         <v>Completed</v>
       </c>
       <c r="D5" t="str">
-        <v/>
+        <v>PI</v>
       </c>
       <c r="E5" t="str">
         <v>VTM 모델의 전비 예측 정확도 향상을 위한 2-Stage PE 시스템 손실맵 확장 프로세스 개발</v>
@@ -3604,12 +3592,9 @@
         <v>현대자동차</v>
       </c>
       <c r="G5" t="str">
-        <v/>
+        <v>2024.02</v>
       </c>
       <c r="H5" t="str">
-        <v>2024.02</v>
-      </c>
-      <c r="I5" t="str">
         <v>2024.12</v>
       </c>
     </row>
@@ -3624,7 +3609,7 @@
         <v>Completed</v>
       </c>
       <c r="D6" t="str">
-        <v/>
+        <v>PI</v>
       </c>
       <c r="E6" t="str">
         <v>스마트 헬스케어 머신의 감성품질 향상을 위한 부하정밀제어 캘리브레이션 기술개발 및 출고 검사 장비 개발</v>
@@ -3633,12 +3618,9 @@
         <v>과학기술정보통신부</v>
       </c>
       <c r="G6" t="str">
-        <v/>
+        <v>2024.08</v>
       </c>
       <c r="H6" t="str">
-        <v>2024.08</v>
-      </c>
-      <c r="I6" t="str">
         <v>2024.11</v>
       </c>
     </row>
@@ -3653,7 +3635,7 @@
         <v>Completed</v>
       </c>
       <c r="D7" t="str">
-        <v/>
+        <v>PI</v>
       </c>
       <c r="E7" t="str">
         <v>구동모터 특성해석 시간 단축을 위한 프로그램 개발</v>
@@ -3662,12 +3644,9 @@
         <v>현대트랜시스</v>
       </c>
       <c r="G7" t="str">
-        <v/>
+        <v>2024.08</v>
       </c>
       <c r="H7" t="str">
-        <v>2024.08</v>
-      </c>
-      <c r="I7" t="str">
         <v>2025.08</v>
       </c>
     </row>
@@ -3682,7 +3661,7 @@
         <v>Completed</v>
       </c>
       <c r="D8" t="str">
-        <v/>
+        <v>PI</v>
       </c>
       <c r="E8" t="str">
         <v>회전자 관성을 이용한 토크 산정 알고리즘 개선</v>
@@ -3691,12 +3670,9 @@
         <v>한국생산기술연구원</v>
       </c>
       <c r="G8" t="str">
-        <v/>
+        <v>2024.09</v>
       </c>
       <c r="H8" t="str">
-        <v>2024.09</v>
-      </c>
-      <c r="I8" t="str">
         <v>2024.11</v>
       </c>
     </row>
@@ -3711,7 +3687,7 @@
         <v>Completed</v>
       </c>
       <c r="D9" t="str">
-        <v/>
+        <v>Advisor</v>
       </c>
       <c r="E9" t="str">
         <v>전기자동차 주행가능거리 극대화를 위한 구동모터/인버터, 냉각시스템의 비효율 전류벡터제어 기반 최적제어</v>
@@ -3720,12 +3696,9 @@
         <v>한국연구재단(석사과정생연구장려금지원사업)</v>
       </c>
       <c r="G9" t="str">
-        <v/>
+        <v>2024.09</v>
       </c>
       <c r="H9" t="str">
-        <v>2024.09</v>
-      </c>
-      <c r="I9" t="str">
         <v>2025.09</v>
       </c>
     </row>
@@ -3740,7 +3713,7 @@
         <v>Completed</v>
       </c>
       <c r="D10" t="str">
-        <v/>
+        <v>PI</v>
       </c>
       <c r="E10" t="str">
         <v>VTM 기반기술 확보 및 데이터 구축을 위한 전력 모델 구축 및 PE시스템 Scaling 기법 개발</v>
@@ -3749,12 +3722,9 @@
         <v>현대자동차</v>
       </c>
       <c r="G10" t="str">
-        <v/>
+        <v>2025.02</v>
       </c>
       <c r="H10" t="str">
-        <v>2025.02</v>
-      </c>
-      <c r="I10" t="str">
         <v>2025.12</v>
       </c>
     </row>
@@ -3769,7 +3739,7 @@
         <v>Completed</v>
       </c>
       <c r="D11" t="str">
-        <v/>
+        <v>PI</v>
       </c>
       <c r="E11" t="str">
         <v>e2DT 구동모터 가진력 최적 설계 개발</v>
@@ -3778,12 +3748,9 @@
         <v>현대트랜시스</v>
       </c>
       <c r="G11" t="str">
-        <v/>
+        <v>2025.03</v>
       </c>
       <c r="H11" t="str">
-        <v>2025.03</v>
-      </c>
-      <c r="I11" t="str">
         <v>2025.10</v>
       </c>
     </row>
@@ -3798,7 +3765,7 @@
         <v>Completed</v>
       </c>
       <c r="D12" t="str">
-        <v/>
+        <v>Co-I</v>
       </c>
       <c r="E12" t="str">
         <v>고전압 파워넷 네트워크의 공진 해석을 위한 시스템 해석 기법 및 모델링, 검증, 시뮬레이션 툴 개발</v>
@@ -3807,12 +3774,9 @@
         <v>현대자동차</v>
       </c>
       <c r="G12" t="str">
-        <v/>
+        <v>2025.03</v>
       </c>
       <c r="H12" t="str">
-        <v>2025.03</v>
-      </c>
-      <c r="I12" t="str">
         <v>2026.02</v>
       </c>
     </row>
@@ -3827,7 +3791,7 @@
         <v>Completed</v>
       </c>
       <c r="D13" t="str">
-        <v/>
+        <v>PI</v>
       </c>
       <c r="E13" t="str">
         <v>친환경연료 힘센엔진 연료분사펌프(e-FIP)용 솔레노이드 밸브 해석 및 시험평가 기술 개발</v>
@@ -3836,12 +3800,9 @@
         <v>HD현대중공업</v>
       </c>
       <c r="G13" t="str">
-        <v/>
+        <v>2025.09</v>
       </c>
       <c r="H13" t="str">
-        <v>2025.09</v>
-      </c>
-      <c r="I13" t="str">
         <v>2025.12</v>
       </c>
     </row>
@@ -3856,7 +3817,7 @@
         <v>Completed</v>
       </c>
       <c r="D14" t="str">
-        <v/>
+        <v>PI</v>
       </c>
       <c r="E14" t="str">
         <v>피트니스 인공지능 개발을 위한 고분해능 기어리스 자기식 엔코더 기반 전동식 피트니스 머신 구동부 기술 개발</v>
@@ -3865,12 +3826,9 @@
         <v>서울연구원(RISE사업)</v>
       </c>
       <c r="G14" t="str">
-        <v/>
+        <v>2025.09</v>
       </c>
       <c r="H14" t="str">
-        <v>2025.09</v>
-      </c>
-      <c r="I14" t="str">
         <v>2026.01</v>
       </c>
     </row>
@@ -3885,7 +3843,7 @@
         <v>Ongoing</v>
       </c>
       <c r="D15" t="str">
-        <v/>
+        <v>Co-I</v>
       </c>
       <c r="E15" t="str">
         <v>AI-핵심소재 기반 첨단산업 지능형 로봇 글로벌인재양성</v>
@@ -3894,12 +3852,9 @@
         <v>한국산업기술진흥원</v>
       </c>
       <c r="G15" t="str">
-        <v/>
+        <v>2024.03</v>
       </c>
       <c r="H15" t="str">
-        <v>2024.03</v>
-      </c>
-      <c r="I15" t="str">
         <v>2027.02</v>
       </c>
     </row>
@@ -3914,7 +3869,7 @@
         <v>Ongoing</v>
       </c>
       <c r="D16" t="str">
-        <v/>
+        <v>Co-I</v>
       </c>
       <c r="E16" t="str">
         <v>평각동선 분포권 기술 적용 축방향자속 전동기 개발</v>
@@ -3923,12 +3878,9 @@
         <v>효성전기 · 한국자동차연구원 · 대구대학교</v>
       </c>
       <c r="G16" t="str">
-        <v/>
+        <v>2025.04</v>
       </c>
       <c r="H16" t="str">
-        <v>2025.04</v>
-      </c>
-      <c r="I16" t="str">
         <v>2028.12</v>
       </c>
     </row>
@@ -3943,7 +3895,7 @@
         <v>Ongoing</v>
       </c>
       <c r="D17" t="str">
-        <v/>
+        <v>Advisor</v>
       </c>
       <c r="E17" t="str">
         <v>다족보행로봇의 에너지효율 향상을 위한 다중물리모델 기반 구동계 최적설계기술 연구</v>
@@ -3952,12 +3904,9 @@
         <v>한국연구재단(석사과정생연구장려금지원사업)</v>
       </c>
       <c r="G17" t="str">
-        <v/>
+        <v>2025.09</v>
       </c>
       <c r="H17" t="str">
-        <v>2025.09</v>
-      </c>
-      <c r="I17" t="str">
         <v>2026.09</v>
       </c>
     </row>
@@ -3972,7 +3921,7 @@
         <v>Ongoing</v>
       </c>
       <c r="D18" t="str">
-        <v/>
+        <v>Advisor</v>
       </c>
       <c r="E18" t="str">
         <v>전기차 파워트레인의 데이터 주도 고장예지를 위한 고장데이터 생성 다중물리 해석모델 연구</v>
@@ -3981,12 +3930,9 @@
         <v>한국연구재단(석사과정생연구장려금지원사업)</v>
       </c>
       <c r="G18" t="str">
-        <v/>
+        <v>2025.09</v>
       </c>
       <c r="H18" t="str">
-        <v>2025.09</v>
-      </c>
-      <c r="I18" t="str">
         <v>2026.09</v>
       </c>
     </row>
@@ -4001,7 +3947,7 @@
         <v>Ongoing</v>
       </c>
       <c r="D19" t="str">
-        <v/>
+        <v>PI</v>
       </c>
       <c r="E19" t="str">
         <v>PE 비효율 제어 시, 차량 열관리 시스템 성능 검토를 위한 해석 모델 개발</v>
@@ -4010,12 +3956,9 @@
         <v>현대자동차</v>
       </c>
       <c r="G19" t="str">
-        <v/>
+        <v>2026.02</v>
       </c>
       <c r="H19" t="str">
-        <v>2026.02</v>
-      </c>
-      <c r="I19" t="str">
         <v>2026.12</v>
       </c>
     </row>
@@ -4030,7 +3973,7 @@
         <v>Ongoing</v>
       </c>
       <c r="D20" t="str">
-        <v/>
+        <v>PI</v>
       </c>
       <c r="E20" t="str">
         <v>모터시스템 효율 향상을 위한 실측데이터 기반 전류지령맵 추출 기술 개발</v>
@@ -4039,12 +3982,9 @@
         <v>현대자동차</v>
       </c>
       <c r="G20" t="str">
-        <v/>
+        <v>2026.03</v>
       </c>
       <c r="H20" t="str">
-        <v>2026.03</v>
-      </c>
-      <c r="I20" t="str">
         <v>2026.09</v>
       </c>
     </row>
@@ -4059,7 +3999,7 @@
         <v>Ongoing</v>
       </c>
       <c r="D21" t="str">
-        <v/>
+        <v>PI</v>
       </c>
       <c r="E21" t="str">
         <v>저가형 모터를 위한 PE 시스템 최적화 기술 개발</v>
@@ -4068,12 +4008,9 @@
         <v>현대자동차</v>
       </c>
       <c r="G21" t="str">
-        <v/>
+        <v>2026.04</v>
       </c>
       <c r="H21" t="str">
-        <v>2026.04</v>
-      </c>
-      <c r="I21" t="str">
         <v>2027.04</v>
       </c>
     </row>
@@ -4088,7 +4025,7 @@
         <v>Ongoing</v>
       </c>
       <c r="D22" t="str">
-        <v/>
+        <v>PI</v>
       </c>
       <c r="E22" t="str">
         <v>친환경연료 힘센엔진 솔레노이드 밸브 LECM Fault 분석 및 설계 기술 개발</v>
@@ -4097,12 +4034,9 @@
         <v>HD현대중공업</v>
       </c>
       <c r="G22" t="str">
-        <v/>
+        <v>2026.03</v>
       </c>
       <c r="H22" t="str">
-        <v>2026.03</v>
-      </c>
-      <c r="I22" t="str">
         <v>2026.11</v>
       </c>
     </row>
@@ -4117,7 +4051,7 @@
         <v>Ongoing</v>
       </c>
       <c r="D23" t="str">
-        <v/>
+        <v>PI</v>
       </c>
       <c r="E23" t="str">
         <v>T/L 세탁기 모터 구동부 박형 기술 개발</v>
@@ -4126,12 +4060,9 @@
         <v>LG전자</v>
       </c>
       <c r="G23" t="str">
-        <v/>
+        <v>2026.05</v>
       </c>
       <c r="H23" t="str">
-        <v>2026.05</v>
-      </c>
-      <c r="I23" t="str">
         <v>2027.01</v>
       </c>
     </row>
@@ -4146,7 +4077,7 @@
         <v>Ongoing</v>
       </c>
       <c r="D24" t="str">
-        <v/>
+        <v>PI</v>
       </c>
       <c r="E24" t="str">
         <v>EV/HEV 보조 구동 성능 향상을 위한 WRSM 전자기 설계</v>
@@ -4155,12 +4086,9 @@
         <v>현대자동차</v>
       </c>
       <c r="G24" t="str">
-        <v/>
+        <v>2026.06</v>
       </c>
       <c r="H24" t="str">
-        <v>2026.06</v>
-      </c>
-      <c r="I24" t="str">
         <v>2027.06</v>
       </c>
     </row>
@@ -4175,7 +4103,7 @@
         <v>Ongoing</v>
       </c>
       <c r="D25" t="str">
-        <v/>
+        <v>PI</v>
       </c>
       <c r="E25" t="str">
         <v>축방향 극대 온도차 터보기기 구동모터의 열강건성을 위한 열해석 및 열차폐 구조설계</v>
@@ -4184,12 +4112,9 @@
         <v>서울앵커(ANCHOR)사업</v>
       </c>
       <c r="G25" t="str">
-        <v/>
+        <v>2026.07</v>
       </c>
       <c r="H25" t="str">
-        <v>2026.07</v>
-      </c>
-      <c r="I25" t="str">
         <v>2026.12</v>
       </c>
     </row>
@@ -4204,7 +4129,7 @@
         <v>Ongoing</v>
       </c>
       <c r="D26" t="str">
-        <v/>
+        <v>Advisor</v>
       </c>
       <c r="E26" t="str">
         <v>Super-resolution</v>
@@ -4213,12 +4138,9 @@
         <v>한국연구재단(석사과정생연구장려금지원사업)</v>
       </c>
       <c r="G26" t="str">
-        <v/>
+        <v>2026.09</v>
       </c>
       <c r="H26" t="str">
-        <v>2026.09</v>
-      </c>
-      <c r="I26" t="str">
         <v>2027.08</v>
       </c>
     </row>
@@ -4233,7 +4155,7 @@
         <v>Ongoing</v>
       </c>
       <c r="D27" t="str">
-        <v/>
+        <v>PI</v>
       </c>
       <c r="E27" t="str">
         <v>상변환물질 기반 잠열을 활용한 휴머노이드 로봇 관절 액추에이터의 순간 과부하 열관리 기법 개발</v>
@@ -4242,18 +4164,15 @@
         <v>한국연구재단(개인기초연구-기본연구A)</v>
       </c>
       <c r="G27" t="str">
-        <v/>
+        <v>2026.09</v>
       </c>
       <c r="H27" t="str">
-        <v>2026.09</v>
-      </c>
-      <c r="I27" t="str">
         <v>2028.08</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J27"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I27"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/eplab_website_content.xlsx
+++ b/eplab_website_content.xlsx
@@ -2365,7 +2365,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:L24"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2434,7 +2434,7 @@
         <v/>
       </c>
       <c r="J2" t="str">
-        <v/>
+        <v>https://drive.google.com/file/d/1-eUVLZB_tvi-zcc7MZEBk5DMaBMFAa26/view?usp=drive_link</v>
       </c>
       <c r="K2" t="str">
         <v>https://scholar.google.com/citations?user=hocoJJAAAAAJ&amp;hl=ko</v>
@@ -2445,25 +2445,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="B3" t="str">
-        <v>110</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Graduate</v>
-      </c>
-      <c r="D3" t="str">
-        <v>Chan-Woo Kim</v>
-      </c>
-      <c r="E3" t="str">
-        <v>김찬우</v>
-      </c>
-      <c r="F3" t="str">
-        <v>석사과정</v>
-      </c>
-      <c r="G3" t="str">
-        <v>kimcw_339@dgu.ac.kr</v>
+        <v>FALSE</v>
       </c>
     </row>
     <row r="4">
@@ -2471,7 +2453,7 @@
         <v>TRUE</v>
       </c>
       <c r="B4" t="str">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="C4" t="str">
         <v>Graduate</v>
@@ -2486,7 +2468,16 @@
         <v>석사과정</v>
       </c>
       <c r="G4" t="str">
-        <v>2025120179@dgu.ac.kr</v>
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v/>
+      </c>
+      <c r="J4" t="str">
+        <v>https://drive.google.com/file/d/1L8FKAnnXBu2csNkXJpblR9TYvJe1LmZl/view?usp=drive_link</v>
       </c>
     </row>
     <row r="5">
@@ -2494,7 +2485,7 @@
         <v>TRUE</v>
       </c>
       <c r="B5" t="str">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="C5" t="str">
         <v>Graduate</v>
@@ -2509,7 +2500,16 @@
         <v>석사과정</v>
       </c>
       <c r="G5" t="str">
-        <v>2025120182@dgu.ac.kr</v>
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v/>
+      </c>
+      <c r="J5" t="str">
+        <v>https://drive.google.com/file/d/1CD74TQb85FmslshtOUiYL24W276tXYFi/view?usp=drive_link</v>
       </c>
     </row>
     <row r="6">
@@ -2517,7 +2517,7 @@
         <v>TRUE</v>
       </c>
       <c r="B6" t="str">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="C6" t="str">
         <v>Graduate</v>
@@ -2532,7 +2532,16 @@
         <v>석사과정</v>
       </c>
       <c r="G6" t="str">
-        <v>ca1ifornia1@dgu.ac.kr</v>
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v/>
+      </c>
+      <c r="J6" t="str">
+        <v>https://drive.google.com/file/d/1yW6H6xlYqwSAAvGMMY6Z8rSvxmcLdge_/view?usp=drive_link</v>
       </c>
     </row>
     <row r="7">
@@ -2540,7 +2549,7 @@
         <v>TRUE</v>
       </c>
       <c r="B7" t="str">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="C7" t="str">
         <v>Graduate</v>
@@ -2555,7 +2564,16 @@
         <v>석사과정</v>
       </c>
       <c r="G7" t="str">
-        <v>kimjy_333@dgu.ac.kr</v>
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v/>
+      </c>
+      <c r="J7" t="str">
+        <v>https://drive.google.com/file/d/1RiwTn7oh3nWOnANtLxtcljFpqKMYVY9s/view?usp=drive_link</v>
       </c>
     </row>
     <row r="8">
@@ -2563,7 +2581,7 @@
         <v>TRUE</v>
       </c>
       <c r="B8" t="str">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="C8" t="str">
         <v>Graduate</v>
@@ -2578,7 +2596,16 @@
         <v>석사과정</v>
       </c>
       <c r="G8" t="str">
-        <v>yujk_361@dgu.ac.kr</v>
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v/>
+      </c>
+      <c r="J8" t="str">
+        <v>https://drive.google.com/file/d/1eAq-Dbv5DMas0WsXQtGQdnEyhF6zQJqT/view?usp=drive_link</v>
       </c>
     </row>
     <row r="9">
@@ -2586,7 +2613,7 @@
         <v>TRUE</v>
       </c>
       <c r="B9" t="str">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="C9" t="str">
         <v>Graduate</v>
@@ -2601,7 +2628,16 @@
         <v>석사과정</v>
       </c>
       <c r="G9" t="str">
-        <v>njt0731@dgu.ac.kr</v>
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v/>
+      </c>
+      <c r="J9" t="str">
+        <v>https://drive.google.com/file/d/1mHPwOXItQnAXxwwNG7CSHN3uGccJ09td/view?usp=drive_link</v>
       </c>
     </row>
     <row r="10">
@@ -2609,10 +2645,10 @@
         <v>TRUE</v>
       </c>
       <c r="B10" t="str">
-        <v>210</v>
+        <v>170</v>
       </c>
       <c r="C10" t="str">
-        <v>Undergraduate</v>
+        <v>Graduate</v>
       </c>
       <c r="D10" t="str">
         <v>Chae-Young Jeong</v>
@@ -2621,7 +2657,19 @@
         <v>정채영</v>
       </c>
       <c r="F10" t="str">
-        <v>학부연구생</v>
+        <v>석사과정</v>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v/>
+      </c>
+      <c r="J10" t="str">
+        <v>https://drive.google.com/file/d/1yH2AV-U0LUkMC_uhN7S7GiYKr6jL03vI/view?usp=drive_link</v>
       </c>
     </row>
     <row r="11">
@@ -2629,10 +2677,10 @@
         <v>TRUE</v>
       </c>
       <c r="B11" t="str">
-        <v>220</v>
+        <v>180</v>
       </c>
       <c r="C11" t="str">
-        <v>Undergraduate</v>
+        <v>Graduate</v>
       </c>
       <c r="D11" t="str">
         <v>Hye-Chan Cho</v>
@@ -2641,7 +2689,7 @@
         <v>조혜찬</v>
       </c>
       <c r="F11" t="str">
-        <v>학부연구생</v>
+        <v>석사과정</v>
       </c>
     </row>
     <row r="12">
@@ -2649,10 +2697,10 @@
         <v>TRUE</v>
       </c>
       <c r="B12" t="str">
-        <v>230</v>
+        <v>190</v>
       </c>
       <c r="C12" t="str">
-        <v>Undergraduate</v>
+        <v>Graduate</v>
       </c>
       <c r="D12" t="str">
         <v>Seo-Hyun Hong</v>
@@ -2661,27 +2709,24 @@
         <v>홍서현</v>
       </c>
       <c r="F12" t="str">
-        <v>학부연구생</v>
+        <v>석사과정</v>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v/>
+      </c>
+      <c r="J12" t="str">
+        <v>https://drive.google.com/file/d/134PHTlSa-z_qlzAf80lYYruh42-GVz7U/view?usp=drive_link</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="B13" t="str">
-        <v>240</v>
-      </c>
-      <c r="C13" t="str">
-        <v>Undergraduate</v>
-      </c>
-      <c r="D13" t="str">
-        <v>Na-Kyung Yoo</v>
-      </c>
-      <c r="E13" t="str">
-        <v>유나경</v>
-      </c>
-      <c r="F13" t="str">
-        <v>학부연구생</v>
+        <v>FALSE</v>
       </c>
     </row>
     <row r="14">
@@ -2689,115 +2734,64 @@
         <v>TRUE</v>
       </c>
       <c r="B14" t="str">
-        <v>310</v>
+        <v>210</v>
       </c>
       <c r="C14" t="str">
-        <v>Alumni</v>
+        <v>Undergraduate</v>
       </c>
       <c r="D14" t="str">
-        <v>Tae-Ho Park</v>
+        <v>Na-Kyung Yoo</v>
       </c>
       <c r="E14" t="str">
-        <v>박태호</v>
+        <v>유나경</v>
       </c>
       <c r="F14" t="str">
         <v>학부연구생</v>
       </c>
-      <c r="G14" t="str">
-        <v/>
-      </c>
-      <c r="H14" t="str">
-        <v>23.10 ~ 24.08</v>
-      </c>
-      <c r="I14" t="str">
-        <v>현대자동차 연구개발본부</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
         <v>TRUE</v>
       </c>
       <c r="B15" t="str">
-        <v>320</v>
+        <v>220</v>
       </c>
       <c r="C15" t="str">
-        <v>Alumni</v>
+        <v>Undergraduate</v>
       </c>
       <c r="D15" t="str">
-        <v>Ki-Woong Eom</v>
+        <v>Jin-Woo Jung</v>
       </c>
       <c r="E15" t="str">
-        <v>엄기웅</v>
+        <v>정진우</v>
       </c>
       <c r="F15" t="str">
         <v>학부연구생</v>
       </c>
-      <c r="G15" t="str">
-        <v/>
-      </c>
-      <c r="H15" t="str">
-        <v>24.08 ~ 24.12</v>
-      </c>
-      <c r="I15" t="str">
-        <v>현대제철</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
         <v>TRUE</v>
       </c>
       <c r="B16" t="str">
-        <v>330</v>
+        <v>230</v>
       </c>
       <c r="C16" t="str">
-        <v>Alumni</v>
+        <v>Undergraduate</v>
       </c>
       <c r="D16" t="str">
-        <v>Tae-Hyeok Heo</v>
+        <v>Ji-Min Sun</v>
       </c>
       <c r="E16" t="str">
-        <v>허태혁</v>
+        <v>선지민</v>
       </c>
       <c r="F16" t="str">
         <v>학부연구생</v>
       </c>
-      <c r="G16" t="str">
-        <v/>
-      </c>
-      <c r="H16" t="str">
-        <v>24.01 ~ 24.12</v>
-      </c>
-      <c r="I16" t="str">
-        <v>현대자동차 연구개발본부</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="B17" t="str">
-        <v>340</v>
-      </c>
-      <c r="C17" t="str">
-        <v>Alumni</v>
-      </c>
-      <c r="D17" t="str">
-        <v>Jinseong Han</v>
-      </c>
-      <c r="E17" t="str">
-        <v>한진성</v>
-      </c>
-      <c r="F17" t="str">
-        <v>학부연구생</v>
-      </c>
-      <c r="G17" t="str">
-        <v/>
-      </c>
-      <c r="H17" t="str">
-        <v>23.10 ~ 24.08</v>
-      </c>
-      <c r="I17" t="str">
-        <v>KAIST 석사과정</v>
+        <v>FALSE</v>
       </c>
     </row>
     <row r="18">
@@ -2805,16 +2799,16 @@
         <v>TRUE</v>
       </c>
       <c r="B18" t="str">
-        <v>350</v>
+        <v>370</v>
       </c>
       <c r="C18" t="str">
         <v>Alumni</v>
       </c>
       <c r="D18" t="str">
-        <v>Harin Kim</v>
+        <v>Tae-Ho Park</v>
       </c>
       <c r="E18" t="str">
-        <v>김하린</v>
+        <v>박태호</v>
       </c>
       <c r="F18" t="str">
         <v>학부연구생</v>
@@ -2823,10 +2817,10 @@
         <v/>
       </c>
       <c r="H18" t="str">
-        <v>24.01 ~ 24.12</v>
+        <v>23.10 ~ 24.08</v>
       </c>
       <c r="I18" t="str">
-        <v>볼보그룹코리아</v>
+        <v>현대자동차 연구개발본부</v>
       </c>
     </row>
     <row r="19">
@@ -2840,10 +2834,10 @@
         <v>Alumni</v>
       </c>
       <c r="D19" t="str">
-        <v>Joon-Beom Lee</v>
+        <v>Jinseong Han</v>
       </c>
       <c r="E19" t="str">
-        <v>이준범</v>
+        <v>한진성</v>
       </c>
       <c r="F19" t="str">
         <v>학부연구생</v>
@@ -2852,15 +2846,163 @@
         <v/>
       </c>
       <c r="H19" t="str">
+        <v>23.10 ~ 24.08</v>
+      </c>
+      <c r="I19" t="str">
+        <v>KAIST 석사과정</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="B20" t="str">
+        <v>350</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Alumni</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Tae-Hyeok Heo</v>
+      </c>
+      <c r="E20" t="str">
+        <v>허태혁</v>
+      </c>
+      <c r="F20" t="str">
+        <v>학부연구생</v>
+      </c>
+      <c r="G20" t="str">
+        <v/>
+      </c>
+      <c r="H20" t="str">
+        <v>24.01 ~ 24.12</v>
+      </c>
+      <c r="I20" t="str">
+        <v>현대자동차 연구개발본부</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="B21" t="str">
+        <v>340</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Alumni</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Harin Kim</v>
+      </c>
+      <c r="E21" t="str">
+        <v>김하린</v>
+      </c>
+      <c r="F21" t="str">
+        <v>학부연구생</v>
+      </c>
+      <c r="G21" t="str">
+        <v/>
+      </c>
+      <c r="H21" t="str">
+        <v>24.01 ~ 24.12</v>
+      </c>
+      <c r="I21" t="str">
+        <v>볼보그룹코리아</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="B22" t="str">
+        <v>330</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Alumni</v>
+      </c>
+      <c r="D22" t="str">
+        <v>Ki-Woong Eom</v>
+      </c>
+      <c r="E22" t="str">
+        <v>엄기웅</v>
+      </c>
+      <c r="F22" t="str">
+        <v>학부연구생</v>
+      </c>
+      <c r="G22" t="str">
+        <v/>
+      </c>
+      <c r="H22" t="str">
         <v>24.08 ~ 24.12</v>
       </c>
-      <c r="I19" t="str">
-        <v>—</v>
+      <c r="I22" t="str">
+        <v>현대제철</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="B23" t="str">
+        <v>320</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Alumni</v>
+      </c>
+      <c r="D23" t="str">
+        <v>Joon-Beom Lee</v>
+      </c>
+      <c r="E23" t="str">
+        <v>이준범</v>
+      </c>
+      <c r="F23" t="str">
+        <v>학부연구생</v>
+      </c>
+      <c r="G23" t="str">
+        <v/>
+      </c>
+      <c r="H23" t="str">
+        <v>24.08 ~ 24.12</v>
+      </c>
+      <c r="I23" t="str">
+        <v>LG에너지솔루션</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="B24" t="str">
+        <v>310</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Alumni</v>
+      </c>
+      <c r="D24" t="str">
+        <v>Chan-Woo Kim</v>
+      </c>
+      <c r="E24" t="str">
+        <v>김찬우</v>
+      </c>
+      <c r="F24" t="str">
+        <v>석사</v>
+      </c>
+      <c r="G24" t="str">
+        <v>kimcw_339@dgu.ac.kr</v>
+      </c>
+      <c r="H24" t="str">
+        <v>24.09 ~ 26.08</v>
+      </c>
+      <c r="I24" t="str">
+        <v>현대자동차 연구개발본부</v>
+      </c>
+      <c r="J24" t="str">
+        <v>https://drive.google.com/file/d/1blfnVhSgsE67BmBnMRVNrVeLoyyeIUZy/view?usp=drive_link</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L19"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L24"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/eplab_website_content.xlsx
+++ b/eplab_website_content.xlsx
@@ -505,7 +505,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E28"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -529,16 +529,16 @@
         <v>TRUE</v>
       </c>
       <c r="B2" t="str">
-        <v>10</v>
+        <v>270</v>
       </c>
       <c r="C2" t="str">
-        <v>2026.03</v>
+        <v>2023.09</v>
       </c>
       <c r="D2" t="str">
-        <v>전기자동차 구동모터 개발동향 및 열관리 전략</v>
+        <v>전기자동차 파워트레인의 기술 동향</v>
       </c>
       <c r="E2" t="str">
-        <v>한양대학교</v>
+        <v>동국대학교 BK21 초청세미나</v>
       </c>
     </row>
     <row r="3">
@@ -546,16 +546,16 @@
         <v>TRUE</v>
       </c>
       <c r="B3" t="str">
-        <v>20</v>
+        <v>260</v>
       </c>
       <c r="C3" t="str">
-        <v>2025.09</v>
+        <v>2023.10</v>
       </c>
       <c r="D3" t="str">
-        <v>협동로봇 구동모듈의 PHM</v>
+        <v>전기자동차 파워트레인의 기술 동향</v>
       </c>
       <c r="E3" t="str">
-        <v>두산로보틱스</v>
+        <v>한국자동차연구원</v>
       </c>
     </row>
     <row r="4">
@@ -563,16 +563,16 @@
         <v>TRUE</v>
       </c>
       <c r="B4" t="str">
-        <v>30</v>
+        <v>250</v>
       </c>
       <c r="C4" t="str">
-        <v>2025.08</v>
+        <v>2023.12</v>
       </c>
       <c r="D4" t="str">
-        <v>Scaling 기반 모터 설계 효율화 및 심층전이학습 기반 설계/시험 효율화</v>
+        <v>전동화 파워트레인 연구동향</v>
       </c>
       <c r="E4" t="str">
-        <v>대구대학교</v>
+        <v>한국자동차연구원</v>
       </c>
     </row>
     <row r="5">
@@ -580,16 +580,16 @@
         <v>TRUE</v>
       </c>
       <c r="B5" t="str">
-        <v>40</v>
+        <v>240</v>
       </c>
       <c r="C5" t="str">
-        <v>2025.08</v>
+        <v>2024.02</v>
       </c>
       <c r="D5" t="str">
-        <v>전자기 액추에이터 기초 이론 및 실습</v>
+        <v>전기자동차 구동모터의 시험-해석 정합성 향상에 관한 연구</v>
       </c>
       <c r="E5" t="str">
-        <v>한국최적설계학회 하계강습회</v>
+        <v>서울대학교 기계공학부</v>
       </c>
     </row>
     <row r="6">
@@ -597,16 +597,16 @@
         <v>TRUE</v>
       </c>
       <c r="B6" t="str">
-        <v>50</v>
+        <v>230</v>
       </c>
       <c r="C6" t="str">
-        <v>2025.07</v>
+        <v>2024.03</v>
       </c>
       <c r="D6" t="str">
-        <v>구동모터 기초이론 및 비효율 전류벡터제어 기반 강제발열모드</v>
+        <v>전자기 유한요소해석 기반 철손해석</v>
       </c>
       <c r="E6" t="str">
-        <v>현대자동차 열에너지통합개발실</v>
+        <v>한국생산기술연구원</v>
       </c>
     </row>
     <row r="7">
@@ -614,16 +614,16 @@
         <v>TRUE</v>
       </c>
       <c r="B7" t="str">
-        <v>60</v>
+        <v>220</v>
       </c>
       <c r="C7" t="str">
-        <v>2025.07</v>
+        <v>2024.06</v>
       </c>
       <c r="D7" t="str">
-        <v>핵심 구동 부품 전자기-기계 성능 최신 연구동향</v>
+        <v>전기자동차 구동모터의 시험-해석 정합성 향상에 관한 연구</v>
       </c>
       <c r="E7" t="str">
-        <v>한국자동차연구원</v>
+        <v>영남대학교 기계공학부</v>
       </c>
     </row>
     <row r="8">
@@ -631,16 +631,16 @@
         <v>TRUE</v>
       </c>
       <c r="B8" t="str">
-        <v>70</v>
+        <v>210</v>
       </c>
       <c r="C8" t="str">
-        <v>2025.06</v>
+        <v>2024.07</v>
       </c>
       <c r="D8" t="str">
-        <v>2-Stage 인버터 토폴로지 적용 PE 시스템의 설계, 제어 및 응용</v>
+        <v>개방형 권선 구조 및 IPMSM의 전자기 성능해석 및 응용</v>
       </c>
       <c r="E8" t="str">
-        <v>현대모비스 전동화BU</v>
+        <v>한국생산기술연구원</v>
       </c>
     </row>
     <row r="9">
@@ -648,16 +648,16 @@
         <v>TRUE</v>
       </c>
       <c r="B9" t="str">
-        <v>80</v>
+        <v>200</v>
       </c>
       <c r="C9" t="str">
-        <v>2025.05</v>
+        <v>2024.08</v>
       </c>
       <c r="D9" t="str">
-        <v>Scaling 기반 모터 설계 효율화 및 심층전이학습 기반 설계/시험 효율화</v>
+        <v>전기자동차 구동모터 연구개발 동향 및 고효율/고출력 구동시스템 신구조</v>
       </c>
       <c r="E9" t="str">
-        <v>LG전자</v>
+        <v>충남대학교 전기공학과</v>
       </c>
     </row>
     <row r="10">
@@ -665,16 +665,16 @@
         <v>TRUE</v>
       </c>
       <c r="B10" t="str">
-        <v>90</v>
+        <v>190</v>
       </c>
       <c r="C10" t="str">
-        <v>2025.05</v>
+        <v>2024.08</v>
       </c>
       <c r="D10" t="str">
-        <v>전동화 가속을 위한 AI 및 CAE 빅데이터 기반 구동모터 시험/설계 효율화 기술</v>
+        <v>고효율/고출력 구동시스템 신구조 및 시험-해석 가속화 연구</v>
       </c>
       <c r="E10" t="str">
-        <v>한국자동차연구원</v>
+        <v>LG전자 가산R&amp;D캠퍼스</v>
       </c>
     </row>
     <row r="11">
@@ -682,16 +682,16 @@
         <v>TRUE</v>
       </c>
       <c r="B11" t="str">
-        <v>100</v>
+        <v>180</v>
       </c>
       <c r="C11" t="str">
-        <v>2025.05</v>
+        <v>2024.09</v>
       </c>
       <c r="D11" t="str">
-        <v>고효율 구동시스템을 위한 권선 토폴로지 &amp; PE 시스템의 Multi-physics 성능해석</v>
+        <v>고출력밀도 전기모터를 위한 적층제조 코일 연구동향</v>
       </c>
       <c r="E11" t="str">
-        <v>보그워너</v>
+        <v>한국생산기술연구원</v>
       </c>
     </row>
     <row r="12">
@@ -699,16 +699,16 @@
         <v>TRUE</v>
       </c>
       <c r="B12" t="str">
-        <v>110</v>
+        <v>170</v>
       </c>
       <c r="C12" t="str">
-        <v>2025.02</v>
+        <v>2024.10</v>
       </c>
       <c r="D12" t="str">
-        <v>친환경자동차 PE 시스템 권선절환 토폴로지 &amp; 전이학습 기반 시험/설계 효율화</v>
+        <v>전기자동차 구동모터의 글로벌 최신 연구 동향</v>
       </c>
       <c r="E12" t="str">
-        <v>현대자동차 전동화시험센터</v>
+        <v>한국생산기술연구원</v>
       </c>
     </row>
     <row r="13">
@@ -716,13 +716,13 @@
         <v>TRUE</v>
       </c>
       <c r="B13" t="str">
-        <v>120</v>
+        <v>160</v>
       </c>
       <c r="C13" t="str">
-        <v>2024.12</v>
+        <v>2024.10</v>
       </c>
       <c r="D13" t="str">
-        <v>xEV 구동모터 개발기간 단축을 위한 설계 및 시험기술</v>
+        <v>친환경자동차 구동시스템 토폴로지</v>
       </c>
       <c r="E13" t="str">
         <v>한국자동차연구원</v>
@@ -733,13 +733,13 @@
         <v>TRUE</v>
       </c>
       <c r="B14" t="str">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="C14" t="str">
-        <v>2024.10</v>
+        <v>2024.12</v>
       </c>
       <c r="D14" t="str">
-        <v>친환경자동차 구동시스템 토폴로지</v>
+        <v>xEV 구동모터 개발기간 단축을 위한 설계 및 시험기술</v>
       </c>
       <c r="E14" t="str">
         <v>한국자동차연구원</v>
@@ -753,13 +753,13 @@
         <v>140</v>
       </c>
       <c r="C15" t="str">
-        <v>2024.10</v>
+        <v>2025.02</v>
       </c>
       <c r="D15" t="str">
-        <v>전기자동차 구동모터의 글로벌 최신 연구 동향</v>
+        <v>친환경자동차 PE 시스템 권선절환 토폴로지 &amp; 전이학습 기반 시험/설계 효율화</v>
       </c>
       <c r="E15" t="str">
-        <v>한국생산기술연구원</v>
+        <v>현대자동차 전동화시험센터</v>
       </c>
     </row>
     <row r="16">
@@ -767,16 +767,16 @@
         <v>TRUE</v>
       </c>
       <c r="B16" t="str">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="C16" t="str">
-        <v>2024.09</v>
+        <v>2025.05</v>
       </c>
       <c r="D16" t="str">
-        <v>고출력밀도 전기모터를 위한 적층제조 코일 연구동향</v>
+        <v>고효율 구동시스템을 위한 권선 토폴로지 &amp; PE 시스템의 Multi-physics 성능해석</v>
       </c>
       <c r="E16" t="str">
-        <v>한국생산기술연구원</v>
+        <v>보그워너</v>
       </c>
     </row>
     <row r="17">
@@ -784,16 +784,16 @@
         <v>TRUE</v>
       </c>
       <c r="B17" t="str">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="C17" t="str">
-        <v>2024.08</v>
+        <v>2025.05</v>
       </c>
       <c r="D17" t="str">
-        <v>고효율/고출력 구동시스템 신구조 및 시험-해석 가속화 연구</v>
+        <v>전동화 가속을 위한 AI 및 CAE 빅데이터 기반 구동모터 시험/설계 효율화 기술</v>
       </c>
       <c r="E17" t="str">
-        <v>LG전자 가산R&amp;D캠퍼스</v>
+        <v>한국자동차연구원</v>
       </c>
     </row>
     <row r="18">
@@ -801,16 +801,16 @@
         <v>TRUE</v>
       </c>
       <c r="B18" t="str">
-        <v>170</v>
+        <v>110</v>
       </c>
       <c r="C18" t="str">
-        <v>2024.08</v>
+        <v>2025.05</v>
       </c>
       <c r="D18" t="str">
-        <v>전기자동차 구동모터 연구개발 동향 및 고효율/고출력 구동시스템 신구조</v>
+        <v>Scaling 기반 모터 설계 효율화 및 심층전이학습 기반 설계/시험 효율화</v>
       </c>
       <c r="E18" t="str">
-        <v>충남대학교 전기공학과</v>
+        <v>LG전자</v>
       </c>
     </row>
     <row r="19">
@@ -818,16 +818,16 @@
         <v>TRUE</v>
       </c>
       <c r="B19" t="str">
-        <v>180</v>
+        <v>100</v>
       </c>
       <c r="C19" t="str">
-        <v>2024.07</v>
+        <v>2025.06</v>
       </c>
       <c r="D19" t="str">
-        <v>개방형 권선 구조 및 IPMSM의 전자기 성능해석 및 응용</v>
+        <v>2-Stage 인버터 토폴로지 적용 PE 시스템의 설계, 제어 및 응용</v>
       </c>
       <c r="E19" t="str">
-        <v>한국생산기술연구원</v>
+        <v>현대모비스 전동화BU</v>
       </c>
     </row>
     <row r="20">
@@ -835,16 +835,16 @@
         <v>TRUE</v>
       </c>
       <c r="B20" t="str">
-        <v>190</v>
+        <v>90</v>
       </c>
       <c r="C20" t="str">
-        <v>2024.06</v>
+        <v>2025.07</v>
       </c>
       <c r="D20" t="str">
-        <v>전기자동차 구동모터의 시험-해석 정합성 향상에 관한 연구</v>
+        <v>핵심 구동 부품 전자기-기계 성능 최신 연구동향</v>
       </c>
       <c r="E20" t="str">
-        <v>영남대학교 기계공학부</v>
+        <v>한국자동차연구원</v>
       </c>
     </row>
     <row r="21">
@@ -852,16 +852,16 @@
         <v>TRUE</v>
       </c>
       <c r="B21" t="str">
-        <v>200</v>
+        <v>80</v>
       </c>
       <c r="C21" t="str">
-        <v>2024.03</v>
+        <v>2025.07</v>
       </c>
       <c r="D21" t="str">
-        <v>전자기 유한요소해석 기반 철손해석</v>
+        <v>구동모터 기초이론 및 비효율 전류벡터제어 기반 강제발열모드</v>
       </c>
       <c r="E21" t="str">
-        <v>한국생산기술연구원</v>
+        <v>현대자동차 열에너지통합개발실</v>
       </c>
     </row>
     <row r="22">
@@ -869,16 +869,16 @@
         <v>TRUE</v>
       </c>
       <c r="B22" t="str">
-        <v>210</v>
+        <v>70</v>
       </c>
       <c r="C22" t="str">
-        <v>2024.02</v>
+        <v>2025.08</v>
       </c>
       <c r="D22" t="str">
-        <v>전기자동차 구동모터의 시험-해석 정합성 향상에 관한 연구</v>
+        <v>전자기 액추에이터 기초 이론 및 실습</v>
       </c>
       <c r="E22" t="str">
-        <v>서울대학교 기계공학부</v>
+        <v>한국최적설계학회 하계강습회</v>
       </c>
     </row>
     <row r="23">
@@ -886,16 +886,16 @@
         <v>TRUE</v>
       </c>
       <c r="B23" t="str">
-        <v>220</v>
+        <v>60</v>
       </c>
       <c r="C23" t="str">
-        <v>2023.12</v>
+        <v>2025.08</v>
       </c>
       <c r="D23" t="str">
-        <v>전동화 파워트레인 연구동향</v>
+        <v>Scaling 기반 모터 설계 효율화 및 심층전이학습 기반 설계/시험 효율화</v>
       </c>
       <c r="E23" t="str">
-        <v>한국자동차연구원</v>
+        <v>대구대학교</v>
       </c>
     </row>
     <row r="24">
@@ -903,16 +903,16 @@
         <v>TRUE</v>
       </c>
       <c r="B24" t="str">
-        <v>230</v>
+        <v>50</v>
       </c>
       <c r="C24" t="str">
-        <v>2023.10</v>
+        <v>2025.09</v>
       </c>
       <c r="D24" t="str">
-        <v>전기자동차 파워트레인의 기술 동향</v>
+        <v>협동로봇 구동모듈의 PHM</v>
       </c>
       <c r="E24" t="str">
-        <v>한국자동차연구원</v>
+        <v>두산로보틱스</v>
       </c>
     </row>
     <row r="25">
@@ -920,21 +920,72 @@
         <v>TRUE</v>
       </c>
       <c r="B25" t="str">
-        <v>240</v>
+        <v>40</v>
       </c>
       <c r="C25" t="str">
-        <v>2023.09</v>
+        <v>2026.03</v>
       </c>
       <c r="D25" t="str">
-        <v>전기자동차 파워트레인의 기술 동향</v>
+        <v>전기자동차 구동모터 개발동향 및 열관리 전략</v>
       </c>
       <c r="E25" t="str">
-        <v>동국대학교 BK21 초청세미나</v>
+        <v>한양대학교</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="B26" t="str">
+        <v>30</v>
+      </c>
+      <c r="C26" t="str">
+        <v>2026.04</v>
+      </c>
+      <c r="D26" t="str">
+        <v>전기자동차 구동모터 개발동향 및 열관리 전략</v>
+      </c>
+      <c r="E26" t="str">
+        <v>GIST</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="B27" t="str">
+        <v>20</v>
+      </c>
+      <c r="C27" t="str">
+        <v>2026.07</v>
+      </c>
+      <c r="D27" t="str">
+        <v>전동화 가속을 위한 AI 및 CAE 빅데이터 기반구동모터 시험/설계 효율화 기술</v>
+      </c>
+      <c r="E27" t="str">
+        <v>한국자동차연구원</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="B28" t="str">
+        <v>10</v>
+      </c>
+      <c r="C28" t="str">
+        <v>2026.08</v>
+      </c>
+      <c r="D28" t="str">
+        <v>모터 응용 분야별 열관리 기법_x000d_</v>
+      </c>
+      <c r="E28" t="str">
+        <v>PHM 리더양성을 위한 전문기술 강좌</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E25"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E28"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2189,7 +2240,7 @@
         <v>stat_researchers</v>
       </c>
       <c r="B12" t="str">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C12" t="str">
         <v/>
@@ -2217,7 +2268,7 @@
         <v>stat_projects</v>
       </c>
       <c r="B14" t="str">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C14" t="str">
         <v/>
@@ -3436,7 +3487,7 @@
         <v>240</v>
       </c>
       <c r="D25" t="str">
-        <v/>
+        <v>2023 – present</v>
       </c>
       <c r="E25" t="str">
         <v>Reviewer: TIE, TMECH, TTE, TMAG, TEC, IEEE ACCESS, JEET, JOM</v>
@@ -3641,7 +3692,7 @@
         <v>TRUE</v>
       </c>
       <c r="B2" t="str">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="C2" t="str">
         <v>Completed</v>
@@ -3667,7 +3718,7 @@
         <v>TRUE</v>
       </c>
       <c r="B3" t="str">
-        <v>250</v>
+        <v>230</v>
       </c>
       <c r="C3" t="str">
         <v>Completed</v>
@@ -3693,7 +3744,7 @@
         <v>TRUE</v>
       </c>
       <c r="B4" t="str">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="C4" t="str">
         <v>Completed</v>
@@ -3719,7 +3770,7 @@
         <v>TRUE</v>
       </c>
       <c r="B5" t="str">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="C5" t="str">
         <v>Completed</v>
@@ -3745,7 +3796,7 @@
         <v>TRUE</v>
       </c>
       <c r="B6" t="str">
-        <v>220</v>
+        <v>200</v>
       </c>
       <c r="C6" t="str">
         <v>Completed</v>
@@ -3771,7 +3822,7 @@
         <v>TRUE</v>
       </c>
       <c r="B7" t="str">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="C7" t="str">
         <v>Completed</v>
@@ -3797,7 +3848,7 @@
         <v>TRUE</v>
       </c>
       <c r="B8" t="str">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="C8" t="str">
         <v>Completed</v>
@@ -3823,7 +3874,7 @@
         <v>TRUE</v>
       </c>
       <c r="B9" t="str">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="C9" t="str">
         <v>Completed</v>
@@ -3849,7 +3900,7 @@
         <v>TRUE</v>
       </c>
       <c r="B10" t="str">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="C10" t="str">
         <v>Completed</v>
@@ -3875,7 +3926,7 @@
         <v>TRUE</v>
       </c>
       <c r="B11" t="str">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="C11" t="str">
         <v>Completed</v>
@@ -3901,7 +3952,7 @@
         <v>TRUE</v>
       </c>
       <c r="B12" t="str">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="C12" t="str">
         <v>Completed</v>
@@ -3927,7 +3978,7 @@
         <v>TRUE</v>
       </c>
       <c r="B13" t="str">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="C13" t="str">
         <v>Completed</v>
@@ -3953,7 +4004,7 @@
         <v>TRUE</v>
       </c>
       <c r="B14" t="str">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="C14" t="str">
         <v>Completed</v>
@@ -3982,22 +4033,22 @@
         <v>130</v>
       </c>
       <c r="C15" t="str">
-        <v>Ongoing</v>
+        <v>Completed</v>
       </c>
       <c r="D15" t="str">
-        <v>Co-I</v>
+        <v>Advisor</v>
       </c>
       <c r="E15" t="str">
-        <v>AI-핵심소재 기반 첨단산업 지능형 로봇 글로벌인재양성</v>
+        <v>다족보행로봇의 에너지효율 향상을 위한 다중물리모델 기반 구동계 최적설계기술 연구</v>
       </c>
       <c r="F15" t="str">
-        <v>한국산업기술진흥원</v>
+        <v>한국연구재단(석사과정생연구장려금지원사업)</v>
       </c>
       <c r="G15" t="str">
-        <v>2024.03</v>
+        <v>2025.09</v>
       </c>
       <c r="H15" t="str">
-        <v>2027.02</v>
+        <v>2026.09</v>
       </c>
     </row>
     <row r="16">
@@ -4008,22 +4059,22 @@
         <v>120</v>
       </c>
       <c r="C16" t="str">
-        <v>Ongoing</v>
+        <v>Completed</v>
       </c>
       <c r="D16" t="str">
-        <v>Co-I</v>
+        <v>Advisor</v>
       </c>
       <c r="E16" t="str">
-        <v>평각동선 분포권 기술 적용 축방향자속 전동기 개발</v>
+        <v>전기차 파워트레인의 데이터 주도 고장예지를 위한 고장데이터 생성 다중물리 해석모델 연구</v>
       </c>
       <c r="F16" t="str">
-        <v>효성전기 · 한국자동차연구원 · 대구대학교</v>
+        <v>한국연구재단(석사과정생연구장려금지원사업)</v>
       </c>
       <c r="G16" t="str">
-        <v>2025.04</v>
+        <v>2025.09</v>
       </c>
       <c r="H16" t="str">
-        <v>2028.12</v>
+        <v>2026.09</v>
       </c>
     </row>
     <row r="17">
@@ -4037,19 +4088,19 @@
         <v>Ongoing</v>
       </c>
       <c r="D17" t="str">
-        <v>Advisor</v>
+        <v>Co-I</v>
       </c>
       <c r="E17" t="str">
-        <v>다족보행로봇의 에너지효율 향상을 위한 다중물리모델 기반 구동계 최적설계기술 연구</v>
+        <v>AI-핵심소재 기반 첨단산업 지능형 로봇 글로벌인재양성</v>
       </c>
       <c r="F17" t="str">
-        <v>한국연구재단(석사과정생연구장려금지원사업)</v>
+        <v>한국산업기술진흥원</v>
       </c>
       <c r="G17" t="str">
-        <v>2025.09</v>
+        <v>2024.03</v>
       </c>
       <c r="H17" t="str">
-        <v>2026.09</v>
+        <v>2027.02</v>
       </c>
     </row>
     <row r="18">
@@ -4063,19 +4114,19 @@
         <v>Ongoing</v>
       </c>
       <c r="D18" t="str">
-        <v>Advisor</v>
+        <v>Co-I</v>
       </c>
       <c r="E18" t="str">
-        <v>전기차 파워트레인의 데이터 주도 고장예지를 위한 고장데이터 생성 다중물리 해석모델 연구</v>
+        <v>평각동선 분포권 기술 적용 축방향자속 전동기 개발</v>
       </c>
       <c r="F18" t="str">
-        <v>한국연구재단(석사과정생연구장려금지원사업)</v>
+        <v>한국산업기획평가원</v>
       </c>
       <c r="G18" t="str">
-        <v>2025.09</v>
+        <v>2025.04</v>
       </c>
       <c r="H18" t="str">
-        <v>2026.09</v>
+        <v>2028.12</v>
       </c>
     </row>
     <row r="19">
@@ -4274,7 +4325,7 @@
         <v>Advisor</v>
       </c>
       <c r="E26" t="str">
-        <v>Super-resolution</v>
+        <v>AI 기반 초해상도을 활용한 축방향 자속 모터의 다중 메쉬 해상도 기반 전자계 해석 가속화 연구</v>
       </c>
       <c r="F26" t="str">
         <v>한국연구재단(석사과정생연구장려금지원사업)</v>
@@ -4321,7 +4372,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:H39"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -4348,37 +4399,31 @@
       <c r="H1" t="str">
         <v>doi</v>
       </c>
-      <c r="I1" t="str">
-        <v>featured</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
         <v>TRUE</v>
       </c>
       <c r="B2" t="str">
-        <v>10</v>
+        <v>370</v>
       </c>
       <c r="C2" t="str">
-        <v>2026</v>
+        <v>2019</v>
       </c>
       <c r="D2" t="str">
-        <v>J. H. Lee, S. H. Park, D. H. Park, J. H. Jeong, and M. S. Lim*</v>
+        <v>S. H. Park, J. C. Park, J. W. Chin, H. J. Park, S. O. Kwon, S. I. Kim, and M. S. Lim*</v>
       </c>
       <c r="E2" t="str">
-        <v>Deep Transfer Learning-Based Demagnetization Analysis for Linear Oscillating Actuator Considering Circumferential Segmented Structure</v>
+        <v>Design of Surface-mounted Permanent Magnet Synchronous Motor using Electromagnetic and Thermal Analysis</v>
       </c>
       <c r="F2" t="str">
-        <v>IEEE Transactions on Industry Applications, vol. 62, no. 1, pp. 821–829, Jan. 2026</v>
+        <v>Journal of Magnetics, vol. 24, no. 4, pp. 606–615, Dec. 2019</v>
       </c>
       <c r="G2" t="str">
-        <v>IF 4.2 · Q1 · JCR 13.0%</v>
+        <v>IF 0.628 · Q4</v>
       </c>
       <c r="H2" t="str">
-        <v>https://doi.org/10.1109/TIA.2025.3585098</v>
-      </c>
-      <c r="I2" t="str">
-        <v>FALSE</v>
+        <v>https://doi.org/10.4283/JMAG.2019.24.4.606</v>
       </c>
     </row>
     <row r="3">
@@ -4386,28 +4431,25 @@
         <v>TRUE</v>
       </c>
       <c r="B3" t="str">
-        <v>20</v>
+        <v>360</v>
       </c>
       <c r="C3" t="str">
-        <v>2025</v>
+        <v>2020</v>
       </c>
       <c r="D3" t="str">
-        <v>K. S. Cha**, S. H. Park**, and Y. H. Jung*</v>
+        <v>S. H. Park, J. C. Park, S. W. Hwang, J. H. Kim, H. J. Park, and M. S. Lim*</v>
       </c>
       <c r="E3" t="str">
-        <v>Design of WFSM using Sizing Method Combining 2D Equivalent Magnetic Circuit considering Nonlinear Characteristics</v>
+        <v>Suppression of Torque Ripple Caused by Misalignment of the Gearbox by Using Harmonic Current Injection Method</v>
       </c>
       <c r="F3" t="str">
-        <v>IEEE Transactions on Magnetics, Early Access, 2025</v>
+        <v>IEEE/ASME Transactions on Mechatronics, vol. 25, no. 4, pp. 1990–1999, Aug. 2020</v>
       </c>
       <c r="G3" t="str">
-        <v>IF 2.1 · Q3 · JCR 54.5%</v>
+        <v>IF 4.943 · Q1 · JCR 5.0%</v>
       </c>
       <c r="H3" t="str">
-        <v>https://doi.org/10.1109/TMAG.2025.3624623</v>
-      </c>
-      <c r="I3" t="str">
-        <v>FALSE</v>
+        <v>https://doi.org/10.1109/TMECH.2020.2999379</v>
       </c>
     </row>
     <row r="4">
@@ -4415,28 +4457,25 @@
         <v>TRUE</v>
       </c>
       <c r="B4" t="str">
-        <v>30</v>
+        <v>350</v>
       </c>
       <c r="C4" t="str">
-        <v>2025</v>
+        <v>2020</v>
       </c>
       <c r="D4" t="str">
-        <v>Y. M. Lee, D. H. Ko, S. Yoon, J. Cho, S. H. Park*, and M. R. Park*</v>
+        <v>S. H. Park, J. C. Park, H. Y. Lee, S. O. Kwon, and M. S. Lim*</v>
       </c>
       <c r="E4" t="str">
-        <v>Characteristics Estimation and Design of SPMSM using Analytic Method-based Transfer Learning</v>
+        <v>Design of High-Bandwidth Motor System Considering Electrical and Mechanical Time Constant</v>
       </c>
       <c r="F4" t="str">
-        <v>IEEE Transactions on Magnetics, Early Access, 2025</v>
+        <v>IEEE Transactions on Industry Applications, vol. 56, no. 5, pp. 4738–4747, Sep. 2020</v>
       </c>
       <c r="G4" t="str">
-        <v>IF 2.1 · Q3 · JCR 54.5%</v>
+        <v>IF 2.743 · Q1 · JCR 15.7%</v>
       </c>
       <c r="H4" t="str">
-        <v>https://doi.org/10.1109/TMAG.2025.3640767</v>
-      </c>
-      <c r="I4" t="str">
-        <v>FALSE</v>
+        <v>https://doi.org/10.1109/TIA.2020.2998674</v>
       </c>
     </row>
     <row r="5">
@@ -4444,28 +4483,25 @@
         <v>TRUE</v>
       </c>
       <c r="B5" t="str">
-        <v>40</v>
+        <v>340</v>
       </c>
       <c r="C5" t="str">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="D5" t="str">
-        <v>S. H. Park, D. H. Ko, S. G. Lee, J. C. Park, and M. R. Park*</v>
+        <v>S. H. Park, E. C. Lee, J. C. Park, S. W. Hwang, and M. S. Lim*</v>
       </c>
       <c r="E5" t="str">
-        <v>Robust Design Optimization of SPMSM based on Manufacturing Uncertainty Analysis of Prototype</v>
+        <v>Prediction of Mechanical Loss for High-Power-Density PMSM Considering Eddy Current Loss of PMs and Conductors</v>
       </c>
       <c r="F5" t="str">
-        <v>IEEE Transactions on Magnetics, Early Access, 2025</v>
+        <v>IEEE Transactions on Magnetics, vol. 57, no. 2, Feb. 2021</v>
       </c>
       <c r="G5" t="str">
-        <v>IF 2.1 · Q3 · JCR 54.5%</v>
+        <v>IF 1.651 · Q3</v>
       </c>
       <c r="H5" t="str">
-        <v>https://doi.org/10.1109/TMAG.2025.3616812</v>
-      </c>
-      <c r="I5" t="str">
-        <v>FALSE</v>
+        <v>https://doi.org/10.1109/TMAG.2020.3007439</v>
       </c>
     </row>
     <row r="6">
@@ -4473,28 +4509,25 @@
         <v>TRUE</v>
       </c>
       <c r="B6" t="str">
-        <v>50</v>
+        <v>330</v>
       </c>
       <c r="C6" t="str">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="D6" t="str">
-        <v>S. Khalid, J. W. Song, M. H. Yazdani, M. U. Elahi, S. H. Park, H. S. Kim*, Y. G. Yoon, and J. S. Lee</v>
+        <v>J. C. Park, S. H. Park, J. H. Kim, S. G. Lee, G. H. Lee, and M. S. Lim*</v>
       </c>
       <c r="E6" t="str">
-        <v>Advances in prognostics and health management of light emitting diodes: A comprehensive review</v>
+        <v>Diagnosis and Robust Design Optimization of SPMSM Considering Back EMF and Cogging Torque due to Static Eccentricity</v>
       </c>
       <c r="F6" t="str">
-        <v>Journal of Computational Design and Engineering, vol. 12, no. 9, pp. 184–203, Sept. 2025</v>
+        <v>Energies, vol. 14, no. 10, pp. 2900–2918, May 2021</v>
       </c>
       <c r="G6" t="str">
-        <v>IF 4.8 · Q1 · JCR 11.3%</v>
+        <v>IF 2.702 · Q3</v>
       </c>
       <c r="H6" t="str">
-        <v>https://doi.org/10.1093/jcde/qwaf090</v>
-      </c>
-      <c r="I6" t="str">
-        <v>FALSE</v>
+        <v>https://doi.org/10.3390/en14102900</v>
       </c>
     </row>
     <row r="7">
@@ -4502,28 +4535,25 @@
         <v>TRUE</v>
       </c>
       <c r="B7" t="str">
-        <v>60</v>
+        <v>320</v>
       </c>
       <c r="C7" t="str">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="D7" t="str">
-        <v>Y. H. Jung**, D. M. Kim**, K. S. Cha, S. H. Park*, and M. R. Park*</v>
+        <v>S. H. Park, E. C. Lee, G. J. Lee, S. O. Kwon, and M. S. Lim*</v>
       </c>
       <c r="E7" t="str">
-        <v>Vibration Reduction of Permanent Magnet Synchronous Motors by Four-Layer Winding: Mathematical Modeling and Experimental Validation</v>
+        <v>Effect of Pole and Slot Combination on the AC Joule Loss of Outer-Rotor Permanent Magnet Synchronous Motors Using a High Fill Factor Machined Coil</v>
       </c>
       <c r="F7" t="str">
-        <v>Mathematics, vol. 13, no. 9, pp. 1603–1621, May 2025</v>
+        <v>Energies, vol. 14, no. 10, pp. 3073–3083, May 2021</v>
       </c>
       <c r="G7" t="str">
-        <v>IF 2.3 · Q1 · JCR 4.2%</v>
+        <v>IF 2.702 · Q3</v>
       </c>
       <c r="H7" t="str">
-        <v>https://doi.org/10.3390/math13101603</v>
-      </c>
-      <c r="I7" t="str">
-        <v>FALSE</v>
+        <v>https://doi.org/10.3390/en14113073</v>
       </c>
     </row>
     <row r="8">
@@ -4531,28 +4561,25 @@
         <v>TRUE</v>
       </c>
       <c r="B8" t="str">
-        <v>70</v>
+        <v>310</v>
       </c>
       <c r="C8" t="str">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="D8" t="str">
-        <v>K. S. Cha**, Y. H. Jung**, S. H. Park*, and M. R. Park*</v>
+        <v>S. W. Hwang, J. Y. Ryu, J. W. Chin, S. H. Park, D. K. Kim, and M. S. Lim*</v>
       </c>
       <c r="E8" t="str">
-        <v>Optimal Design Considering AC Copper Loss of Traction Motor Applied HSFF Coil for Improving Electric Bus Fuel Economy</v>
+        <v>Coupled Electromagnetic-Thermal Analysis for Predicting Traction Motor Characteristics According to Electric Vehicle Driving Cycle</v>
       </c>
       <c r="F8" t="str">
-        <v>Mathematics, vol. 13, no. 9, pp. 1509–1528, May 2025</v>
+        <v>IEEE Transactions on Vehicular Technology, vol. 70, no. 5, pp. 4262–4272, May 2021</v>
       </c>
       <c r="G8" t="str">
-        <v>IF 2.3 · Q1 · JCR 4.2%</v>
+        <v>IF 5.339 · Q1 · JCR 11.1%</v>
       </c>
       <c r="H8" t="str">
-        <v>https://doi.org/10.3390/math13091509</v>
-      </c>
-      <c r="I8" t="str">
-        <v>FALSE</v>
+        <v>https://doi.org/10.1109/TVT.2021.3071943</v>
       </c>
     </row>
     <row r="9">
@@ -4560,28 +4587,25 @@
         <v>TRUE</v>
       </c>
       <c r="B9" t="str">
-        <v>80</v>
+        <v>300</v>
       </c>
       <c r="C9" t="str">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="D9" t="str">
-        <v>M. H. Sung**, S. H. Park**, K. S. Cha, J. H. Sim, and M. S. Lim*</v>
+        <v>J. W. Chin, K. S. Cha, M. R. Park, S. H. Park, E. C. Lee, and M. S. Lim*</v>
       </c>
       <c r="E9" t="str">
-        <v>Deep Transfer Learning-Based Performance Prediction Considering 3-D Flux in Outer Rotor Interior Permanent Magnet Synchronous Motors</v>
+        <v>High Efficiency PMSM With High Slot Fill Factor Coil for Heavy-Duty EV Traction Considering AC Resistance</v>
       </c>
       <c r="F9" t="str">
-        <v>Machines, vol. 13, no. 4, pp. 302–313, Apr. 2025</v>
+        <v>IEEE Transactions on Energy Conversion, vol. 36, no. 2, pp. 883–894, June 2021</v>
       </c>
       <c r="G9" t="str">
-        <v>IF 2.1 · Q2 · JCR 45.1%</v>
+        <v>IF 4.614 · Q1 · JCR 14.9%</v>
       </c>
       <c r="H9" t="str">
-        <v>https://doi.org/10.3390/machines13040302</v>
-      </c>
-      <c r="I9" t="str">
-        <v>FALSE</v>
+        <v>https://doi.org/10.1109/TEC.2020.3035165</v>
       </c>
     </row>
     <row r="10">
@@ -4589,28 +4613,25 @@
         <v>TRUE</v>
       </c>
       <c r="B10" t="str">
-        <v>90</v>
+        <v>290</v>
       </c>
       <c r="C10" t="str">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="D10" t="str">
-        <v>S. H. Park and M. S. Lim*</v>
+        <v>S. H. Park, J. C. Park, S. W. Hwang, J. H. Kim, and M. S. Lim*</v>
       </c>
       <c r="E10" t="str">
-        <v>Computationally Efficient Design of 16-Poles and 24-Slots IPMSM for EV Traction Considering PWM-Induced Iron Loss Using Active Transfer Learning</v>
+        <v>Model Predictive Control for Torque Ripple Suppression Caused by Misalignment of the Gearbox</v>
       </c>
       <c r="F10" t="str">
-        <v>Mathematics, vol. 13, no. 6, pp. 915–930, Mar. 2025</v>
+        <v>IEEE Transactions on Energy Conversion, vol. 36, no. 2, pp. 1517–1527, June 2021</v>
       </c>
       <c r="G10" t="str">
-        <v>IF 2.3 · Q1 · JCR 4.2%</v>
+        <v>IF 4.614 · Q1 · JCR 14.9%</v>
       </c>
       <c r="H10" t="str">
-        <v>https://doi.org/10.3390/math13060915</v>
-      </c>
-      <c r="I10" t="str">
-        <v>FALSE</v>
+        <v>https://doi.org/10.1109/TEC.2021.3060536</v>
       </c>
     </row>
     <row r="11">
@@ -4618,28 +4639,25 @@
         <v>TRUE</v>
       </c>
       <c r="B11" t="str">
-        <v>100</v>
+        <v>280</v>
       </c>
       <c r="C11" t="str">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="D11" t="str">
-        <v>K. S. Cha**, J. H. Kim**, S. W. Hwang, M. S. Lim*, and S. H. Park*</v>
+        <v>K. S. Cha, J. W. Chin, S. H. Park, Y. H. Jung, E. C. Lee, and M. S. Lim*</v>
       </c>
       <c r="E11" t="str">
-        <v>High-Efficiency e-Powertrain Topology by Integrating Open-End Winding and Winding Changeover for Improving Fuel Economy of Electric Vehicles</v>
+        <v>Design Method for Reducing AC Resistance of Traction Motor Using High Fill Factor Coil to Improve the Fuel Economy of eBus</v>
       </c>
       <c r="F11" t="str">
-        <v>Mathematics, vol. 12, no. 21, pp. 3415–3433, Dec. 2024</v>
+        <v>IEEE/ASME Transactions on Mechatronics, vol. 26, no. 3, pp. 1260–1270, June 2021</v>
       </c>
       <c r="G11" t="str">
-        <v>IF 2.4 · Q1 · JCR 6.8%</v>
+        <v>IF 4.943 · Q1 · JCR 5.0%</v>
       </c>
       <c r="H11" t="str">
-        <v>https://doi.org/10.3390/math12213415</v>
-      </c>
-      <c r="I11" t="str">
-        <v>FALSE</v>
+        <v>https://doi.org/10.1109/TMECH.2021.3054798</v>
       </c>
     </row>
     <row r="12">
@@ -4647,28 +4665,25 @@
         <v>TRUE</v>
       </c>
       <c r="B12" t="str">
-        <v>110</v>
+        <v>270</v>
       </c>
       <c r="C12" t="str">
-        <v>2024</v>
+        <v>2021</v>
       </c>
       <c r="D12" t="str">
-        <v>J. H. Kim, J. Y. Ryu, S. H. Park, K. S. Cha, Y. J. Won, C. S. Park, and M. S. Lim*</v>
+        <v>H. Y. Lee, S. Y. Yoon, S. O. Kwon, J. Y. Shin, S. H. Park, and M. S. Lim*</v>
       </c>
       <c r="E12" t="str">
-        <v>Investigation on Radial Vibration of FSCW PMSM According to Pole/Slot Combination Considering Phase of Radial, Tangential Force and Moment</v>
+        <v>A Study on a Slotless Brushless DC Motor with Toroidal Winding</v>
       </c>
       <c r="F12" t="str">
-        <v>IEEE Transactions on Industry Applications, vol. 60, no. 1, pp. 439–449, Jan. 2024</v>
+        <v>Processes, vol. 9, no. 11, pp. 1881–1900, Oct. 2021</v>
       </c>
       <c r="G12" t="str">
-        <v>IF 4.079 · Q1 · JCR 24.5%</v>
+        <v>IF 2.753 · Q2</v>
       </c>
       <c r="H12" t="str">
-        <v>https://doi.org/10.1109/TIA.2023.3326425</v>
-      </c>
-      <c r="I12" t="str">
-        <v>FALSE</v>
+        <v>https://doi.org/10.3390/pr9111881</v>
       </c>
     </row>
     <row r="13">
@@ -4676,28 +4691,25 @@
         <v>TRUE</v>
       </c>
       <c r="B13" t="str">
-        <v>120</v>
+        <v>260</v>
       </c>
       <c r="C13" t="str">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="D13" t="str">
-        <v>S. H. Park, J. W. Chin, K. S. Cha, J. Y. Ryu, and M. S. Lim*</v>
+        <v>S. H. Park, J. W. Chin, K. S. Cha, and M. S. Lim*</v>
       </c>
       <c r="E13" t="str">
-        <v>Investigation of AC Copper Loss Considering Effect of Field and Armature Excitation on IPMSM With Hairpin Winding</v>
+        <v>Deep Transfer Learning-Based Sizing Method of Permanent Magnet Synchronous Motors Considering Axial Leakage Flux</v>
       </c>
       <c r="F13" t="str">
-        <v>IEEE Transactions on Industrial Electronics, vol. 70, no. 12, pp. 12102–12112, Dec. 2023</v>
+        <v>IEEE Transactions on Magnetics, vol. 58, no. 9, Sep. 2022</v>
       </c>
       <c r="G13" t="str">
-        <v>IF 8.236 · Q1 · JCR 2.3%</v>
+        <v>IF 1.700 · Q3</v>
       </c>
       <c r="H13" t="str">
-        <v>https://doi.org/10.1109/TIE.2023.3234154</v>
-      </c>
-      <c r="I13" t="str">
-        <v>FALSE</v>
+        <v>https://doi.org/10.1109/TMAG.2022.3181804</v>
       </c>
     </row>
     <row r="14">
@@ -4705,28 +4717,25 @@
         <v>TRUE</v>
       </c>
       <c r="B14" t="str">
-        <v>130</v>
+        <v>250</v>
       </c>
       <c r="C14" t="str">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="D14" t="str">
-        <v>S. H. Park, K. O. Kim, and M. S. Lim*</v>
+        <v>J. C. Park, J. Y. Ryu, S. H. Park, and M. S. Lim*</v>
       </c>
       <c r="E14" t="str">
-        <v>Computationally Efficient Estimation of PWM-Induced Iron Loss of PMSM Using Deep Transfer Learning</v>
+        <v>Electronic Throttle Valve Modeling Considering Nonlinearity of Electrical and Mechanical Parameters Based on Experiments</v>
       </c>
       <c r="F14" t="str">
-        <v>IEEE Transactions on Magnetics, vol. 59, no. 11, Nov. 2023</v>
+        <v>IEEE/ASME Transactions on Mechatronics, vol. 27, no. 5, pp. 3309–3314, Oct. 2022</v>
       </c>
       <c r="G14" t="str">
-        <v>IF 1.848 · Q3</v>
+        <v>IF 5.673 · Q1 · JCR 5.0%</v>
       </c>
       <c r="H14" t="str">
-        <v>https://doi.org/10.1109/TMAG.2023.3304981</v>
-      </c>
-      <c r="I14" t="str">
-        <v>FALSE</v>
+        <v>https://doi.org/10.1109/TMECH.2021.3123137</v>
       </c>
     </row>
     <row r="15">
@@ -4734,28 +4743,25 @@
         <v>TRUE</v>
       </c>
       <c r="B15" t="str">
-        <v>140</v>
+        <v>240</v>
       </c>
       <c r="C15" t="str">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="D15" t="str">
-        <v>Y. J. Won, J. H. Kim, S. H. Park, J. H. Lee, S. M. An, D. Y. Kim, and M. S. Lim*</v>
+        <v>C. S. Park, J. H. Kim, S. H. Park, Y. D. Yoon, and M. S. Lim*</v>
       </c>
       <c r="E15" t="str">
-        <v>Transfer Learning-Based Design Method for Cogging Torque Reduction in PMSM With Step-Skew Considering 3-D Leakage Flux</v>
+        <v>Multi-physics characteristics of PMSM for compressor according to driving mode considering PWM frequency</v>
       </c>
       <c r="F15" t="str">
-        <v>IEEE Transactions on Magnetics, vol. 59, no. 11, Nov. 2023</v>
+        <v>IEEE Access, vol. 10, Oct. 2022</v>
       </c>
       <c r="G15" t="str">
-        <v>IF 1.848 · Q3</v>
+        <v>IF 3.367 · Q2</v>
       </c>
       <c r="H15" t="str">
-        <v>https://doi.org/10.1109/TMAG.2023.3294601</v>
-      </c>
-      <c r="I15" t="str">
-        <v>FALSE</v>
+        <v>https://doi.org/10.1109/ACCESS.2022.3217779</v>
       </c>
     </row>
     <row r="16">
@@ -4763,28 +4769,25 @@
         <v>TRUE</v>
       </c>
       <c r="B16" t="str">
-        <v>150</v>
+        <v>230</v>
       </c>
       <c r="C16" t="str">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="D16" t="str">
-        <v>J. C. Park, J. H. Kim, S. H. Park, K. O. Kim, M. H. Sung, and M. S. Lim</v>
+        <v>S. W. Hwang, D. K. Son, S. H. Park, G. H. Lee, Y. D. Yoon, and M. S. Lim*</v>
       </c>
       <c r="E16" t="str">
-        <v>Design Optimization Using Asymmetric Rotor in IPMSM for Torque Ripple Reduction Considering Forward and Reverse Directions</v>
+        <v>Design and Analysis of Dual Stator PMSM With Separately Controlled Dual Three-Phase Winding for eVTOL Propulsion</v>
       </c>
       <c r="F16" t="str">
-        <v>IEEE Transactions on Magnetics, vol. 59, no. 11, Nov. 2023</v>
+        <v>IEEE Transactions on Transportation Electrification, vol. 8, no. 4, pp. 4255–4264, Dec. 2022</v>
       </c>
       <c r="G16" t="str">
-        <v>IF 1.848 · Q3</v>
+        <v>IF 5.444 · Q1 · JCR 12.5%</v>
       </c>
       <c r="H16" t="str">
-        <v>https://doi.org/10.1109/TMAG.2023.3292295</v>
-      </c>
-      <c r="I16" t="str">
-        <v>FALSE</v>
+        <v>https://doi.org/10.1109/TTE.2022.3192353</v>
       </c>
     </row>
     <row r="17">
@@ -4792,28 +4795,25 @@
         <v>TRUE</v>
       </c>
       <c r="B17" t="str">
-        <v>160</v>
+        <v>220</v>
       </c>
       <c r="C17" t="str">
         <v>2023</v>
       </c>
       <c r="D17" t="str">
-        <v>J. H. Lee, S. H. Park, P. J. Kim, D. H. Park, and M. S. Lim*</v>
+        <v>J. H. Kim, S. H. Park, J. Y. Ryu, and M. S. Lim*</v>
       </c>
       <c r="E17" t="str">
-        <v>Two-Dimensional FEA-Based Iron Loss Calculation Method for Linear Oscillating Actuator Considering the Circumferential Segmented Structure</v>
+        <v>Comparative Study of Vibration on 10-Pole 12-Slot and 14-Pole 12-Slot PMSM Considering Tooth Modulation Effect</v>
       </c>
       <c r="F17" t="str">
-        <v>IEEE Transactions on Magnetics, vol. 59, no. 11, Nov. 2023</v>
+        <v>IEEE Transactions on Industrial Electronics, vol. 70, no. 4, pp. 4007–4017, Apr. 2023</v>
       </c>
       <c r="G17" t="str">
-        <v>IF 1.848 · Q3</v>
+        <v>IF 8.236 · Q1 · JCR 2.3%</v>
       </c>
       <c r="H17" t="str">
-        <v>https://doi.org/10.1109/TMAG.2023.3275152</v>
-      </c>
-      <c r="I17" t="str">
-        <v>FALSE</v>
+        <v>https://doi.org/10.1109/TIE.2022.3181418</v>
       </c>
     </row>
     <row r="18">
@@ -4821,7 +4821,7 @@
         <v>TRUE</v>
       </c>
       <c r="B18" t="str">
-        <v>170</v>
+        <v>210</v>
       </c>
       <c r="C18" t="str">
         <v>2023</v>
@@ -4833,7 +4833,7 @@
         <v>Effect of Electromagnetic Force Caused by PMSM on the Vibration/Noise of Reciprocating Compressors</v>
       </c>
       <c r="F18" t="str">
-        <v>IEEE Access, vol. 11, 2023</v>
+        <v>IEEE Access, vol. 11, June 2023</v>
       </c>
       <c r="G18" t="str">
         <v>IF 3.476 · Q2</v>
@@ -4841,37 +4841,31 @@
       <c r="H18" t="str">
         <v>https://doi.org/10.1109/ACCESS.2023.3283144</v>
       </c>
-      <c r="I18" t="str">
-        <v>FALSE</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
         <v>TRUE</v>
       </c>
       <c r="B19" t="str">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="C19" t="str">
         <v>2023</v>
       </c>
       <c r="D19" t="str">
-        <v>J. H. Kim, S. H. Park, J. Y. Ryu, and M. S. Lim*</v>
+        <v>J. H. Lee, S. H. Park, P. J. Kim, D. H. Park, and M. S. Lim*</v>
       </c>
       <c r="E19" t="str">
-        <v>Comparative Study of Vibration on 10-Pole 12-Slot and 14-Pole 12-Slot PMSM Considering Tooth Modulation Effect</v>
+        <v>Two-Dimensional FEA-Based Iron Loss Calculation Method for Linear Oscillating Actuator Considering the Circumferential Segmented Structure</v>
       </c>
       <c r="F19" t="str">
-        <v>IEEE Transactions on Industrial Electronics, vol. 70, no. 4, pp. 4007–4017, Apr. 2023</v>
+        <v>IEEE Transactions on Magnetics, vol. 59, no. 11, Nov. 2023</v>
       </c>
       <c r="G19" t="str">
-        <v>IF 8.236 · Q1 · JCR 2.3%</v>
+        <v>IF 1.848 · Q3</v>
       </c>
       <c r="H19" t="str">
-        <v>https://doi.org/10.1109/TIE.2022.3181418</v>
-      </c>
-      <c r="I19" t="str">
-        <v>FALSE</v>
+        <v>https://doi.org/10.1109/TMAG.2023.3275152</v>
       </c>
     </row>
     <row r="20">
@@ -4882,25 +4876,22 @@
         <v>190</v>
       </c>
       <c r="C20" t="str">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="D20" t="str">
-        <v>C. S. Park, J. H. Kim, S. H. Park, Y. D. Yoon, and M. S. Lim*</v>
+        <v>J. C. Park, J. H. Kim, S. H. Park, K. O. Kim, M. H. Sung, and M. S. Lim*</v>
       </c>
       <c r="E20" t="str">
-        <v>Multi-physics characteristics of PMSM for compressor according to driving mode considering PWM frequency</v>
+        <v>Design Optimization Using Asymmetric Rotor in IPMSM for Torque Ripple Reduction Considering Forward and Reverse Directions</v>
       </c>
       <c r="F20" t="str">
-        <v>IEEE Access, vol. 10, 2022</v>
+        <v>IEEE Transactions on Magnetics, vol. 59, no. 11, Nov. 2023</v>
       </c>
       <c r="G20" t="str">
-        <v>IF 3.367 · Q2</v>
+        <v>IF 1.848 · Q3</v>
       </c>
       <c r="H20" t="str">
-        <v>https://doi.org/10.1109/ACCESS.2022.3217779</v>
-      </c>
-      <c r="I20" t="str">
-        <v>FALSE</v>
+        <v>https://doi.org/10.1109/TMAG.2023.3292295</v>
       </c>
     </row>
     <row r="21">
@@ -4908,28 +4899,25 @@
         <v>TRUE</v>
       </c>
       <c r="B21" t="str">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="C21" t="str">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="D21" t="str">
-        <v>S. W. Hwang, D. K. Son, S. H. Park, G. H. Lee, Y. D. Yoon, and M. S. Lim*</v>
+        <v>Y. J. Won, J. H. Kim, S. H. Park, J. H. Lee, S. M. An, D. Y. Kim, and M. S. Lim*</v>
       </c>
       <c r="E21" t="str">
-        <v>Design and Analysis of Dual Stator PMSM With Separately Controlled Dual Three-Phase Winding for eVTOL Propulsion</v>
+        <v>Transfer Learning-Based Design Method for Cogging Torque Reduction in PMSM With Step-Skew Considering 3-D Leakage Flux</v>
       </c>
       <c r="F21" t="str">
-        <v>IEEE Transactions on Transportation Electrification, vol. 8, no. 4, pp. 4255–4264, Dec. 2022</v>
+        <v>IEEE Transactions on Magnetics, vol. 59, no. 11, Nov. 2023</v>
       </c>
       <c r="G21" t="str">
-        <v>IF 5.444 · Q1 · JCR 12.5%</v>
+        <v>IF 1.848 · Q3</v>
       </c>
       <c r="H21" t="str">
-        <v>https://doi.org/10.1109/TTE.2022.3192353</v>
-      </c>
-      <c r="I21" t="str">
-        <v>FALSE</v>
+        <v>https://doi.org/10.1109/TMAG.2023.3294601</v>
       </c>
     </row>
     <row r="22">
@@ -4937,28 +4925,25 @@
         <v>TRUE</v>
       </c>
       <c r="B22" t="str">
-        <v>210</v>
+        <v>170</v>
       </c>
       <c r="C22" t="str">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="D22" t="str">
-        <v>J. C. Park, J. Y. Ryu, S. H. Park, and M. S. Lim*</v>
+        <v>S. H. Park, K. O. Kim, and M. S. Lim*</v>
       </c>
       <c r="E22" t="str">
-        <v>Electronic Throttle Valve Modeling Considering Nonlinearity of Electrical and Mechanical Parameters Based on Experiments</v>
+        <v>Computationally Efficient Estimation of PWM-Induced Iron Loss of PMSM Using Deep Transfer Learning</v>
       </c>
       <c r="F22" t="str">
-        <v>IEEE/ASME Transactions on Mechatronics, vol. 27, no. 5, pp. 3309–3314, Oct. 2022</v>
+        <v>IEEE Transactions on Magnetics, vol. 59, no. 11, Nov. 2023</v>
       </c>
       <c r="G22" t="str">
-        <v>IF 5.673 · Q1 · JCR 5.0%</v>
+        <v>IF 1.848 · Q3</v>
       </c>
       <c r="H22" t="str">
-        <v>https://doi.org/10.1109/TMECH.2021.3123137</v>
-      </c>
-      <c r="I22" t="str">
-        <v>FALSE</v>
+        <v>https://doi.org/10.1109/TMAG.2023.3304981</v>
       </c>
     </row>
     <row r="23">
@@ -4966,28 +4951,25 @@
         <v>TRUE</v>
       </c>
       <c r="B23" t="str">
-        <v>220</v>
+        <v>160</v>
       </c>
       <c r="C23" t="str">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="D23" t="str">
-        <v>S. H. Park, J. W. Chin, K. S. Cha, and M. S. Lim*</v>
+        <v>S. H. Park, J. W. Chin, K. S. Cha, J. Y. Ryu, and M. S. Lim*</v>
       </c>
       <c r="E23" t="str">
-        <v>Deep Transfer Learning-Based Sizing Method of Permanent Magnet Synchronous Motors Considering Axial Leakage Flux</v>
+        <v>Investigation of AC Copper Loss Considering Effect of Field and Armature Excitation on IPMSM With Hairpin Winding</v>
       </c>
       <c r="F23" t="str">
-        <v>IEEE Transactions on Magnetics, vol. 58, no. 9, Sep. 2022</v>
+        <v>IEEE Transactions on Industrial Electronics, vol. 70, no. 12, pp. 12102–12112, Dec. 2023</v>
       </c>
       <c r="G23" t="str">
-        <v>IF 1.700 · Q3</v>
+        <v>IF 8.236 · Q1 · JCR 2.3%</v>
       </c>
       <c r="H23" t="str">
-        <v>https://doi.org/10.1109/TMAG.2022.3181804</v>
-      </c>
-      <c r="I23" t="str">
-        <v>FALSE</v>
+        <v>https://doi.org/10.1109/TIE.2023.3234154</v>
       </c>
     </row>
     <row r="24">
@@ -4995,28 +4977,25 @@
         <v>TRUE</v>
       </c>
       <c r="B24" t="str">
-        <v>230</v>
+        <v>150</v>
       </c>
       <c r="C24" t="str">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="D24" t="str">
-        <v>H. Y. Lee, S. Y. Yoon, S. O. Kwon, J. Y. Shin, S. H. Park, and M. S. Lim*</v>
+        <v>J. H. Kim, J. Y. Ryu, S. H. Park, K. S. Cha, Y. J. Won, C. S. Park, and M. S. Lim*</v>
       </c>
       <c r="E24" t="str">
-        <v>A Study on a Slotless Brushless DC Motor with Toroidal Winding</v>
+        <v>Investigation on Radial Vibration of FSCW PMSM According to Pole/Slot Combination Considering Phase of Radial, Tangential Force and Moment</v>
       </c>
       <c r="F24" t="str">
-        <v>Processes, vol. 9, no. 11, pp. 1881–1900, Oct. 2021</v>
+        <v>IEEE Transactions on Industry Applications, vol. 60, no. 1, pp. 439–449, Jan. 2024</v>
       </c>
       <c r="G24" t="str">
-        <v>IF 2.753 · Q2</v>
+        <v>IF 4.079 · Q1 · JCR 24.5%</v>
       </c>
       <c r="H24" t="str">
-        <v>https://doi.org/10.3390/pr9111881</v>
-      </c>
-      <c r="I24" t="str">
-        <v>FALSE</v>
+        <v>https://doi.org/10.1109/TIA.2023.3326425</v>
       </c>
     </row>
     <row r="25">
@@ -5024,28 +5003,25 @@
         <v>TRUE</v>
       </c>
       <c r="B25" t="str">
-        <v>240</v>
+        <v>140</v>
       </c>
       <c r="C25" t="str">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="D25" t="str">
-        <v>K. S. Cha, J. W. Chin, S. H. Park, Y. H. Jung, E. C. Lee, and M. S. Lim*</v>
+        <v>K. S. Cha**, J. H. Kim**, S. W. Hwang, M. S. Lim*, and S. H. Park*</v>
       </c>
       <c r="E25" t="str">
-        <v>Design Method for Reducing AC Resistance of Traction Motor Using High Fill Factor Coil to Improve the Fuel Economy of eBus</v>
+        <v>High-Efficiency e-Powertrain Topology by Integrating Open-End Winding and Winding Changeover for Improving Fuel Economy of Electric Vehicles</v>
       </c>
       <c r="F25" t="str">
-        <v>IEEE/ASME Transactions on Mechatronics, vol. 26, no. 3, pp. 1260–1270, June 2021</v>
+        <v>Mathematics, vol. 12, no. 21, pp. 3415–3433, Dec. 2024</v>
       </c>
       <c r="G25" t="str">
-        <v>IF 4.943 · Q1 · JCR 13.3%</v>
+        <v>IF 2.4 · Q1 · JCR 6.8%</v>
       </c>
       <c r="H25" t="str">
-        <v>https://doi.org/10.1109/TMECH.2021.3054798</v>
-      </c>
-      <c r="I25" t="str">
-        <v>FALSE</v>
+        <v>https://doi.org/10.3390/math12213415</v>
       </c>
     </row>
     <row r="26">
@@ -5053,28 +5029,25 @@
         <v>TRUE</v>
       </c>
       <c r="B26" t="str">
-        <v>250</v>
+        <v>130</v>
       </c>
       <c r="C26" t="str">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="D26" t="str">
-        <v>S. H. Park, J. C. Park, S. W. Hwang, J. H. Kim, and M. S. Lim*</v>
+        <v>S. H. Park and M. S. Lim*</v>
       </c>
       <c r="E26" t="str">
-        <v>Model Predictive Control for Torque Ripple Suppression Caused by Misalignment of the Gearbox</v>
+        <v>Computationally Efficient Design of 16-Poles and 24-Slots IPMSM for EV Traction Considering PWM-Induced Iron Loss Using Active Transfer Learning</v>
       </c>
       <c r="F26" t="str">
-        <v>IEEE Transactions on Energy Conversion, vol. 36, no. 2, pp. 1517–1527, June 2021</v>
+        <v>Mathematics, vol. 13, no. 6, pp. 915–930, Mar. 2025</v>
       </c>
       <c r="G26" t="str">
-        <v>IF 4.614 · Q1 · JCR 14.9%</v>
+        <v>IF 2.3 · Q1 · JCR 4.2%</v>
       </c>
       <c r="H26" t="str">
-        <v>https://doi.org/10.1109/TEC.2021.3060536</v>
-      </c>
-      <c r="I26" t="str">
-        <v>FALSE</v>
+        <v>https://doi.org/10.3390/math13060915</v>
       </c>
     </row>
     <row r="27">
@@ -5082,28 +5055,25 @@
         <v>TRUE</v>
       </c>
       <c r="B27" t="str">
-        <v>260</v>
+        <v>120</v>
       </c>
       <c r="C27" t="str">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="D27" t="str">
-        <v>J. W. Chin, K. S. Cha, M. R. Park, S. H. Park, E. C. Lee, and M. S. Lim*</v>
+        <v>M. H. Sung**, S. H. Park**, K. S. Cha, J. H. Sim, and M. S. Lim*</v>
       </c>
       <c r="E27" t="str">
-        <v>High Efficiency PMSM With High Slot Fill Factor Coil for Heavy-Duty EV Traction Considering AC Resistance</v>
+        <v>Deep Transfer Learning-Based Performance Prediction Considering 3-D Flux in Outer Rotor Interior Permanent Magnet Synchronous Motors</v>
       </c>
       <c r="F27" t="str">
-        <v>IEEE Transactions on Energy Conversion, vol. 36, no. 2, pp. 883–894, June 2021</v>
+        <v>Machines, vol. 13, no. 4, pp. 302–313, Apr. 2025</v>
       </c>
       <c r="G27" t="str">
-        <v>IF 4.614 · Q1 · JCR 14.9%</v>
+        <v>IF 2.1 · Q2</v>
       </c>
       <c r="H27" t="str">
-        <v>https://doi.org/10.1109/TEC.2020.3035165</v>
-      </c>
-      <c r="I27" t="str">
-        <v>FALSE</v>
+        <v>https://doi.org/10.3390/machines13040302</v>
       </c>
     </row>
     <row r="28">
@@ -5111,28 +5081,25 @@
         <v>TRUE</v>
       </c>
       <c r="B28" t="str">
-        <v>270</v>
+        <v>110</v>
       </c>
       <c r="C28" t="str">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="D28" t="str">
-        <v>S. W. Hwang, J. Y. Ryu, J. W. Chin, S. H. Park, D. K. Kim, and M. S. Lim*</v>
+        <v>K. S. Cha**, Y. H. Jung**, S. H. Park*, and M. R. Park*</v>
       </c>
       <c r="E28" t="str">
-        <v>Coupled Electromagnetic-Thermal Analysis for Predicting Traction Motor Characteristics According to Electric Vehicle Driving Cycle</v>
+        <v>Optimal Design Considering AC Copper Loss of Traction Motor Applied HSFF Coil for Improving Electric Bus Fuel Economy</v>
       </c>
       <c r="F28" t="str">
-        <v>IEEE Transactions on Vehicular Technology, vol. 70, no. 5, pp. 4262–4272, May 2021</v>
+        <v>Mathematics, vol. 13, no. 9, pp. 1509–1528, May 2025</v>
       </c>
       <c r="G28" t="str">
-        <v>IF 5.379 · Q1 · JCR 12.6%</v>
+        <v>IF 2.3 · Q1 · JCR 4.2%</v>
       </c>
       <c r="H28" t="str">
-        <v>https://doi.org/10.1109/TVT.2021.3071943</v>
-      </c>
-      <c r="I28" t="str">
-        <v>FALSE</v>
+        <v>https://doi.org/10.3390/math13091509</v>
       </c>
     </row>
     <row r="29">
@@ -5140,28 +5107,25 @@
         <v>TRUE</v>
       </c>
       <c r="B29" t="str">
-        <v>280</v>
+        <v>100</v>
       </c>
       <c r="C29" t="str">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="D29" t="str">
-        <v>S. H. Park, E. C. Lee, G. J. Lee, S. O. Kwon, and M. S. Lim*</v>
+        <v>Y. H. Jung**, D. M. Kim**, K. S. Cha, S. H. Park*, and M. R. Park*</v>
       </c>
       <c r="E29" t="str">
-        <v>Effect of Pole and Slot Combination on the AC Joule Loss of Outer-Rotor Permanent Magnet Synchronous Motors Using a High Fill Factor Machined Coil</v>
+        <v>Vibration Reduction of Permanent Magnet Synchronous Motors by Four-Layer Winding: Mathematical Modeling and Experimental Validation</v>
       </c>
       <c r="F29" t="str">
-        <v>Energies, vol. 14, no. 11, pp. 3073–3083, May 2021</v>
+        <v>Mathematics, vol. 13, no. 9, pp. 1603–1621, May 2025</v>
       </c>
       <c r="G29" t="str">
-        <v>IF 2.702 · Q3</v>
+        <v>IF 2.3 · Q1 · JCR 4.2%</v>
       </c>
       <c r="H29" t="str">
-        <v>https://doi.org/10.3390/en14113073</v>
-      </c>
-      <c r="I29" t="str">
-        <v>FALSE</v>
+        <v>https://doi.org/10.3390/math13101603</v>
       </c>
     </row>
     <row r="30">
@@ -5169,28 +5133,25 @@
         <v>TRUE</v>
       </c>
       <c r="B30" t="str">
-        <v>290</v>
+        <v>90</v>
       </c>
       <c r="C30" t="str">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="D30" t="str">
-        <v>J. C. Park, S. H. Park, J. H. Kim, S. G. Lee, G. H. Lee, and M. S. Lim*</v>
+        <v>S. Khalid, J. W. Song, M. H. Yazdani, M. U. Elahi, S. H. Park, H. S. Kim*, Y. G. Yoon, and J. S. Lee</v>
       </c>
       <c r="E30" t="str">
-        <v>Diagnosis and Robust Design Optimization of SPMSM Considering Back EMF and Cogging Torque due to Static Eccentricity</v>
+        <v>Advances in prognostics and health management of light emitting diodes: A comprehensive review</v>
       </c>
       <c r="F30" t="str">
-        <v>Energies, vol. 14, no. 10, pp. 2900–2918, May 2021</v>
+        <v>Journal of Computational Design and Engineering, vol. 12, no. 9, pp. 184–203, Sept. 2025</v>
       </c>
       <c r="G30" t="str">
-        <v>IF 2.702 · Q3</v>
+        <v>IF 4.8 · Q1 · JCR 11.3%</v>
       </c>
       <c r="H30" t="str">
-        <v>https://doi.org/10.3390/en14102900</v>
-      </c>
-      <c r="I30" t="str">
-        <v>FALSE</v>
+        <v>https://doi.org/10.1093/jcde/qwaf090</v>
       </c>
     </row>
     <row r="31">
@@ -5198,28 +5159,25 @@
         <v>TRUE</v>
       </c>
       <c r="B31" t="str">
-        <v>300</v>
+        <v>80</v>
       </c>
       <c r="C31" t="str">
-        <v>2021</v>
+        <v>2026</v>
       </c>
       <c r="D31" t="str">
-        <v>S. H. Park, E. C. Lee, J. C. Park, S. W. Hwang, and M. S. Lim*</v>
+        <v>J. H. Lee, S. H. Park, D. H. Park, J. H. Jeong, and M. S. Lim*</v>
       </c>
       <c r="E31" t="str">
-        <v>Prediction of Mechanical Loss for High-Power Density PMSM Considering Eddy Current Loss of PMs and Conductors</v>
+        <v>Deep Transfer Learning-Based Demagnetization Analysis for Linear Oscillating Actuator Considering Circumferential Segmented Structure</v>
       </c>
       <c r="F31" t="str">
-        <v>IEEE Transactions on Magnetics, vol. 57, no. 2, Feb. 2021</v>
+        <v>IEEE Transactions on Industry Applications, vol. 62, no. 1, pp. 821–829, Jan. 2026</v>
       </c>
       <c r="G31" t="str">
-        <v>IF 1.651 · Q3</v>
+        <v>IF 4.2 · Q1 · JCR 13.0%</v>
       </c>
       <c r="H31" t="str">
-        <v>https://doi.org/10.1109/TMAG.2020.3007439</v>
-      </c>
-      <c r="I31" t="str">
-        <v>FALSE</v>
+        <v>https://doi.org/10.1109/TIA.2025.3585098</v>
       </c>
     </row>
     <row r="32">
@@ -5227,28 +5185,25 @@
         <v>TRUE</v>
       </c>
       <c r="B32" t="str">
-        <v>310</v>
+        <v>70</v>
       </c>
       <c r="C32" t="str">
-        <v>2020</v>
+        <v>2026</v>
       </c>
       <c r="D32" t="str">
-        <v>S. H. Park, J. C. Park, H. Y. Lee, S. O. Kwon, and M. S. Lim*</v>
+        <v>J. H. Kim, Y. J. Won, S. H. Park, and M. S. Lim*</v>
       </c>
       <c r="E32" t="str">
-        <v>Design of High-Bandwidth Motor System Considering Electrical and Mechanical Time Constant</v>
+        <v>Effect of Manufacturing Tolerances and Magnetic Anisotropy of Electrical Steel on Surface-Mounted Permanent Magnet Synchronous Motor Cogging Torque</v>
       </c>
       <c r="F32" t="str">
-        <v>IEEE Transactions on Industry Applications, vol. 56, no. 5, pp. 4738–4747, Sep. 2020</v>
+        <v>Mathematics, vol. 14, no. 4, pp. 650–665, Feb. 2026</v>
       </c>
       <c r="G32" t="str">
-        <v>IF 2.743 · Q1 · JCR 15.7%</v>
+        <v>IF 2.2 · Q1 · JCR 6.0%</v>
       </c>
       <c r="H32" t="str">
-        <v>https://doi.org/10.1109/TIA.2020.2998674</v>
-      </c>
-      <c r="I32" t="str">
-        <v>FALSE</v>
+        <v>https://doi.org/10.3390/math14040650</v>
       </c>
     </row>
     <row r="33">
@@ -5256,28 +5211,25 @@
         <v>TRUE</v>
       </c>
       <c r="B33" t="str">
-        <v>320</v>
+        <v>60</v>
       </c>
       <c r="C33" t="str">
-        <v>2020</v>
+        <v>2026</v>
       </c>
       <c r="D33" t="str">
-        <v>S. H. Park, J. C. Park, S. W. Hwang, J. H. Kim, H. J. Park, and M. S. Lim*</v>
+        <v>J. K. Ryu, C. W. Kim, S. W. Jeong, M. R. Park*, and S. H. Park*</v>
       </c>
       <c r="E33" t="str">
-        <v>Suppression of Torque Ripple Caused by Misalignment of the Gearbox by Using Harmonic Current Injection Method</v>
+        <v>Efficient multi-objective design optimization of axial-flux permanent magnet machines for drone propulsion system using multi-fidelity gaussian process</v>
       </c>
       <c r="F33" t="str">
-        <v>IEEE/ASME Transactions on Mechatronics, vol. 25, no. 4, pp. 1990–1999, Aug. 2020</v>
+        <v>Structural and Multidisciplinary Optimization, vol. 69, no. 5, Apr. 2026</v>
       </c>
       <c r="G33" t="str">
-        <v>IF 4.943 · Q1 · JCR 5.0%</v>
+        <v>IF 4.0 · Q1 · JCR 16.5%</v>
       </c>
       <c r="H33" t="str">
-        <v>https://doi.org/10.1109/TMECH.2020.2999379</v>
-      </c>
-      <c r="I33" t="str">
-        <v>FALSE</v>
+        <v>https://doi.org/10.1007/s00158-026-04316-8</v>
       </c>
     </row>
     <row r="34">
@@ -5285,28 +5237,25 @@
         <v>TRUE</v>
       </c>
       <c r="B34" t="str">
-        <v>330</v>
+        <v>50</v>
       </c>
       <c r="C34" t="str">
-        <v>2020</v>
+        <v>2026</v>
       </c>
       <c r="D34" t="str">
-        <v>G. J. Lee, H. Y. Lee, E. C. Lee, S. H. Park, S. O. Kwon, H. S. Choi*, and J. H. Seo</v>
+        <v>S. H. Park, D. H. Ko, S. G. Lee, J. C. Park, and M. R. Park*</v>
       </c>
       <c r="E34" t="str">
-        <v>Analysis of AC Resistance according to Coil Shape of an Interior-Permanent Magnet Motor</v>
+        <v>Robust Design Optimization of SPMSM based on Manufacturing Uncertainty Analysis of Prototype</v>
       </c>
       <c r="F34" t="str">
-        <v>The Transactions of the Korean Institute of Electrical Engineers, vol. 69, no. 5, pp. 671–676, May 2020</v>
+        <v>IEEE Transactions on Magnetics, vol. 62, no. 7, Jul. 2026</v>
       </c>
       <c r="G34" t="str">
-        <v/>
+        <v>IF 2.1 · Q3</v>
       </c>
       <c r="H34" t="str">
-        <v>https://doi.org/10.5370/KIEE.2020.69.5.671</v>
-      </c>
-      <c r="I34" t="str">
-        <v>FALSE</v>
+        <v>https://doi.org/10.1109/TMAG.2025.3616812</v>
       </c>
     </row>
     <row r="35">
@@ -5314,40 +5263,121 @@
         <v>TRUE</v>
       </c>
       <c r="B35" t="str">
-        <v>340</v>
+        <v>40</v>
       </c>
       <c r="C35" t="str">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="D35" t="str">
-        <v>S. H. Park, J. C. Park, J. W. Chin, H. J. Park, S. O. Kwon, S. I. Kim, and M. S. Lim*</v>
+        <v>Y. M. Lee, D. H. Ko, S. Yoon, J. Cho, S. H. Park*, and M. R. Park*</v>
       </c>
       <c r="E35" t="str">
-        <v>Design of Surface-mounted Permanent Magnet Synchronous Motor using Electromagnetic and Thermal Analysis</v>
+        <v>Characteristics Estimation and Design of SPMSM using Analytic Method-based Transfer Learning</v>
       </c>
       <c r="F35" t="str">
-        <v>Journal of Magnetics, vol. 24, no. 4, pp. 606–615, Dec. 2019</v>
+        <v>IEEE Transactions on Magnetics, vol. 62, no. 7, Jul. 2026</v>
       </c>
       <c r="G35" t="str">
-        <v>IF 0.628 · Q4</v>
+        <v>IF 2.1 · Q3</v>
       </c>
       <c r="H35" t="str">
-        <v>https://doi.org/10.4283/JMAG.2019.24.4.606</v>
-      </c>
-      <c r="I35" t="str">
+        <v>https://doi.org/10.1109/TMAG.2025.3640767</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="B36" t="str">
+        <v>30</v>
+      </c>
+      <c r="C36" t="str">
+        <v>2026</v>
+      </c>
+      <c r="D36" t="str">
+        <v>K. S. Cha**, S. H. Park**, and Y. H. Jung*</v>
+      </c>
+      <c r="E36" t="str">
+        <v>Design of WFSM using Sizing Method Combining 2D Equivalent Magnetic Circuit Considering Nonlinear Characteristics</v>
+      </c>
+      <c r="F36" t="str">
+        <v>IEEE Transactions on Magnetics, vol. 62, no. 7, Jul. 2026</v>
+      </c>
+      <c r="G36" t="str">
+        <v>IF 2.1 · Q3</v>
+      </c>
+      <c r="H36" t="str">
+        <v>https://doi.org/10.1109/TMAG.2025.3624623</v>
+      </c>
+    </row>
+    <row r="37" xml:space="preserve">
+      <c r="A37" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="B37" t="str">
+        <v>20</v>
+      </c>
+      <c r="C37" t="str">
+        <v>2026</v>
+      </c>
+      <c r="D37" t="str">
+        <v>J. H. Lee, H. S. Kim, S. H. Park, J. C. Park, and M. S. Lim*</v>
+      </c>
+      <c r="E37" t="str">
+        <v>Iron Loss Calculation Method Considering Slot Harmonic Components for Induction Motor Using Virtual Blocked Rotor and Transfer Learning</v>
+      </c>
+      <c r="F37" t="str">
+        <v>IEEE Transactions on Industry Applications, Early Access, 2026</v>
+      </c>
+      <c r="G37" t="str">
+        <v>IF 4.5 · Q1 · JCR 14.8%</v>
+      </c>
+      <c r="H37" t="str" xml:space="preserve">
+        <v xml:space="preserve">https://doi.org/10.1109/TIA.2026.3721841_x000d_
+</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="B38" t="str">
+        <v>10</v>
+      </c>
+      <c r="C38" t="str">
+        <v>2026</v>
+      </c>
+      <c r="D38" t="str">
+        <v>H. S. Kim**, S. H. Park**, Y. M. Lee, and M. R. Park*</v>
+      </c>
+      <c r="E38" t="str">
+        <v>Transfer Learning-Assisted Analytical Quasi-3D Surrogate Modeling for Electromagnetic Performance Prediction of AFPMs Considering Eccentricity</v>
+      </c>
+      <c r="F38" t="str">
+        <v>IEEE Transactions on Magnetics, Early Access, 2026</v>
+      </c>
+      <c r="G38" t="str">
+        <v>IF 1.9 · Q3</v>
+      </c>
+      <c r="H38" t="str">
+        <v>https://doi.org/10.1109/TMAG.2026.3701418</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
         <v>FALSE</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I35"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H39"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I44"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -5378,30 +5408,31 @@
         <v>notes</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" xml:space="preserve">
       <c r="A2" t="str">
-        <v>FALSE</v>
+        <v>TRUE</v>
       </c>
       <c r="B2" t="str">
-        <v>10</v>
+        <v>430</v>
       </c>
       <c r="C2" t="str">
-        <v>2025</v>
+        <v>2019</v>
       </c>
       <c r="D2" t="str">
-        <v>(예: 홍길동, 박수환)</v>
+        <v>J. H. Lee, H. S. Kim, S. H. Park, J. C. Park, and M. S. Lim*</v>
       </c>
       <c r="E2" t="str">
-        <v>(발표 논문 제목)</v>
-      </c>
-      <c r="F2" t="str">
-        <v>(학술대회명, 예: KSAE 춘계학술대회)</v>
+        <v>Design of High Bandwidth Motor System Considering Electrical and Mechanical Time Constants</v>
+      </c>
+      <c r="F2" t="str" xml:space="preserve">
+        <v xml:space="preserve">IEEE Energy Conversion Congress &amp;
+ Expo 2019 (ECCE 2019)</v>
       </c>
       <c r="G2" t="str">
-        <v>(예: 제주)</v>
+        <v>Baltimore, USA</v>
       </c>
       <c r="H2" t="str">
-        <v>2025.05</v>
+        <v>2019.09</v>
       </c>
       <c r="I2" t="str">
         <v>발표 목록 데이터 입력 필요 — 원본 디자인은 placeholder</v>
@@ -5409,28 +5440,28 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>FALSE</v>
+        <v>TRUE</v>
       </c>
       <c r="B3" t="str">
-        <v>20</v>
+        <v>420</v>
       </c>
       <c r="C3" t="str">
-        <v>2025</v>
+        <v>2019</v>
       </c>
       <c r="D3" t="str">
-        <v>김찬우, 박수환</v>
+        <v>J. H. Lee, H. S. Kim, S. H. Park, J. C. Park, and M. S. Lim*</v>
       </c>
       <c r="E3" t="str">
-        <v>[샘플] IPMSM의 PWM 고조파를 고려한 철손 예측 기법</v>
+        <v>Design of PMSM for EV Traction using MSO Coil Considering AC Resistance According to Current Density and Parallel Circuit</v>
       </c>
       <c r="F3" t="str">
-        <v>한국자동차공학회 춘계학술대회</v>
+        <v>IEEE Vehicular Power and Propulsion Conference 2019 (VPPC 2019)</v>
       </c>
       <c r="G3" t="str">
-        <v>제주</v>
+        <v>Hanoi, Vietnam</v>
       </c>
       <c r="H3" t="str">
-        <v>2025.05</v>
+        <v>2019.1</v>
       </c>
       <c r="I3" t="str">
         <v>샘플 행 — 실제 발표로 교체할 것</v>
@@ -5438,43 +5469,1084 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>FALSE</v>
+        <v>TRUE</v>
       </c>
       <c r="B4" t="str">
-        <v>30</v>
+        <v>410</v>
       </c>
       <c r="C4" t="str">
-        <v>2024</v>
+        <v>2019</v>
       </c>
       <c r="D4" t="str">
-        <v>유재경, 박수환</v>
+        <v>J. H. Lee, H. S. Kim, S. H. Park, J. C. Park, and M. S. Lim*</v>
       </c>
       <c r="E4" t="str">
-        <v>[샘플] 드론용 축방향 자속 전동기의 다중충실도 최적설계</v>
+        <v>AC Resistance Reduction Design of Traction Motor for High Energy Efficiency of Electric Vehicle</v>
       </c>
       <c r="F4" t="str">
-        <v>대한전기학회 하계학술대회</v>
+        <v>IEEE Vehicular Power and Propulsion Conference 2019 (VPPC 2019)</v>
       </c>
       <c r="G4" t="str">
-        <v>부산</v>
+        <v>Hanoi, Vietnam</v>
       </c>
       <c r="H4" t="str">
-        <v>2024.07</v>
+        <v>2019.1</v>
       </c>
       <c r="I4" t="str">
         <v>샘플 행 — 실제 발표로 교체할 것</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="B5" t="str">
+        <v>400</v>
+      </c>
+      <c r="C5" t="str">
+        <v>2020</v>
+      </c>
+      <c r="D5" t="str">
+        <v>J. H. Lee, H. S. Kim, S. H. Park, J. C. Park, and M. S. Lim*</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Suppression of Torque Ripple Caused by Misalignment of the Gearbox by Using Harmonic Current Injection Method</v>
+      </c>
+      <c r="F5" t="str">
+        <v>2020 IEEE/ASME International Conference on Advanced Intelligent Mechatronics (AIM 2020)</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Boston, USA</v>
+      </c>
+      <c r="H5" t="str">
+        <v>2020.07</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="B6" t="str">
+        <v>390</v>
+      </c>
+      <c r="C6" t="str">
+        <v>2020</v>
+      </c>
+      <c r="D6" t="str">
+        <v>J. H. Lee, H. S. Kim, S. H. Park, J. C. Park, and M. S. Lim*</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Effect of Pole and Slot Combination on the AC Joule Loss of Open-Slot PMSM using MSO Coil</v>
+      </c>
+      <c r="F6" t="str">
+        <v>2020 Conference on Electromagnetic Field Computation (CEFC 2020)</v>
+      </c>
+      <c r="G6" t="str">
+        <v>Pisa, Italy</v>
+      </c>
+      <c r="H6" t="str">
+        <v>2020.11</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="B7" t="str">
+        <v>380</v>
+      </c>
+      <c r="C7" t="str">
+        <v>2020</v>
+      </c>
+      <c r="D7" t="str">
+        <v>J. H. Lee, H. S. Kim, S. H. Park, J. C. Park, and M. S. Lim*</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Analysis of 1kW Drone Drive Motor Characteristics with Cu and Al MSO Coil</v>
+      </c>
+      <c r="F7" t="str">
+        <v>2020 Conference on Electromagnetic Field Computation (CEFC 2020)</v>
+      </c>
+      <c r="G7" t="str">
+        <v>Pisa, Italy</v>
+      </c>
+      <c r="H7" t="str">
+        <v>2020.11</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="B8" t="str">
+        <v>370</v>
+      </c>
+      <c r="C8" t="str">
+        <v>2020</v>
+      </c>
+      <c r="D8" t="str">
+        <v>J. H. Lee, H. S. Kim, S. H. Park, J. C. Park, and M. S. Lim*</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Analytic Method for Magnetic Field Computation of Surface Mounted Permanent Magnet Synchronous Machines with Cycloid Shaped Magnet</v>
+      </c>
+      <c r="F8" t="str">
+        <v>2020 Conference on Electromagnetic Field Computation (CEFC 2020)</v>
+      </c>
+      <c r="G8" t="str">
+        <v>Pisa, Italy</v>
+      </c>
+      <c r="H8" t="str">
+        <v>2020.11</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="B9" t="str">
+        <v>360</v>
+      </c>
+      <c r="C9" t="str">
+        <v>2021</v>
+      </c>
+      <c r="D9" t="str">
+        <v>J. H. Lee, H. S. Kim, S. H. Park, J. C. Park, and M. S. Lim*</v>
+      </c>
+      <c r="E9" t="str">
+        <v>Design Optimization for Torque Ripple Reduction using an Asymmetric Rotor in IPMSM Considering the Forward and Reverse Directions</v>
+      </c>
+      <c r="F9" t="str">
+        <v>2021 International Conference on Magnetics (INTERMAG 2021)</v>
+      </c>
+      <c r="G9" t="str">
+        <v>Lyon, France</v>
+      </c>
+      <c r="H9" t="str">
+        <v>2021.04</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="B10" t="str">
+        <v>350</v>
+      </c>
+      <c r="C10" t="str">
+        <v>2021</v>
+      </c>
+      <c r="D10" t="str">
+        <v>J. H. Lee, H. S. Kim, S. H. Park, J. C. Park, and M. S. Lim*</v>
+      </c>
+      <c r="E10" t="str">
+        <v>Reduction of IPMSM with Asymmetric Rotor Shape under Certain Load Condition</v>
+      </c>
+      <c r="F10" t="str">
+        <v>2021 International Conference on Magnetics (INTERMAG 2021)</v>
+      </c>
+      <c r="G10" t="str">
+        <v>Lyon, France</v>
+      </c>
+      <c r="H10" t="str">
+        <v>2021.04</v>
+      </c>
+    </row>
+    <row r="11" xml:space="preserve">
+      <c r="A11" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="B11" t="str">
+        <v>340</v>
+      </c>
+      <c r="C11" t="str">
+        <v>2021</v>
+      </c>
+      <c r="D11" t="str">
+        <v>J. H. Lee, H. S. Kim, S. H. Park, J. C. Park, and M. S. Lim*</v>
+      </c>
+      <c r="E11" t="str">
+        <v>Characteristics Analysis of IPMSM for EV Traction Considering the Effect of Field and Armature Excitations on AC Copper Loss</v>
+      </c>
+      <c r="F11" t="str" xml:space="preserve">
+        <v xml:space="preserve">IEEE Energy Conversion Congress &amp;
+ Expo 2021 (ECCE 2021)</v>
+      </c>
+      <c r="G11" t="str">
+        <v>Vancouver, Canada</v>
+      </c>
+      <c r="H11" t="str">
+        <v>2021.10</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="B12" t="str">
+        <v>330</v>
+      </c>
+      <c r="C12" t="str">
+        <v>2021</v>
+      </c>
+      <c r="D12" t="str">
+        <v>J. H. Lee, H. S. Kim, S. H. Park, J. C. Park, and M. S. Lim*</v>
+      </c>
+      <c r="E12" t="str">
+        <v>Temperature Prediction of Ultra-High-Speed SPMSM for FCEV Air Compressor Considering PWM Current Harmonics</v>
+      </c>
+      <c r="F12" t="str">
+        <v>IEEE Vehicular Power and Propulsion Conference 2021 (VPPC 2021)</v>
+      </c>
+      <c r="G12" t="str">
+        <v>Gijon, Spain</v>
+      </c>
+      <c r="H12" t="str">
+        <v>2021.10</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="B13" t="str">
+        <v>320</v>
+      </c>
+      <c r="C13" t="str">
+        <v>2021</v>
+      </c>
+      <c r="D13" t="str">
+        <v>J. H. Lee, H. S. Kim, S. H. Park, J. C. Park, and M. S. Lim*</v>
+      </c>
+      <c r="E13" t="str">
+        <v>Open-End Winding Permanent Magnet Synchronous Machine With Winding Connection Change Method for High Efficiency EV Traction</v>
+      </c>
+      <c r="F13" t="str">
+        <v>IEEE Vehicular Power and Propulsion Conference 2021 (VPPC 2021)</v>
+      </c>
+      <c r="G13" t="str">
+        <v>Gijon, Spain</v>
+      </c>
+      <c r="H13" t="str">
+        <v>2021.10</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="B14" t="str">
+        <v>310</v>
+      </c>
+      <c r="C14" t="str">
+        <v>2022</v>
+      </c>
+      <c r="D14" t="str">
+        <v>J. H. Lee, H. S. Kim, S. H. Park, J. C. Park, and M. S. Lim*</v>
+      </c>
+      <c r="E14" t="str">
+        <v>Deep Learning-Based Sizing Method of SPMSM Considering Axial Leakage Flux</v>
+      </c>
+      <c r="F14" t="str">
+        <v>2021 International Conference on the Computation of Electromagnetic Fields (COMPUMAG 2021)</v>
+      </c>
+      <c r="G14" t="str">
+        <v>Cancun, Mexico</v>
+      </c>
+      <c r="H14" t="str">
+        <v>2022.01</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="B15" t="str">
+        <v>300</v>
+      </c>
+      <c r="C15" t="str">
+        <v>2023</v>
+      </c>
+      <c r="D15" t="str">
+        <v>J. H. Lee, H. S. Kim, S. H. Park, J. C. Park, and M. S. Lim*</v>
+      </c>
+      <c r="E15" t="str">
+        <v>Computationally Efficient Estimation of PWM-induced Iron Loss of PMSM using Deep Transfer Learning</v>
+      </c>
+      <c r="F15" t="str">
+        <v>2023 International Conference on Magnetics (INTERMAG 2023)</v>
+      </c>
+      <c r="G15" t="str">
+        <v>Sendai, Japan</v>
+      </c>
+      <c r="H15" t="str">
+        <v>2023.05</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="B16" t="str">
+        <v>290</v>
+      </c>
+      <c r="C16" t="str">
+        <v>2023</v>
+      </c>
+      <c r="D16" t="str">
+        <v>J. H. Lee, H. S. Kim, S. H. Park, J. C. Park, and M. S. Lim*</v>
+      </c>
+      <c r="E16" t="str">
+        <v>Transfer Learning-Based Design Method for Cogging Torque Reduction in PMSM with Step-Skew Considering 3-D Leakage Flux</v>
+      </c>
+      <c r="F16" t="str">
+        <v>2023 International Conference on Magnetics (INTERMAG 2023)</v>
+      </c>
+      <c r="G16" t="str">
+        <v>Sendai, Japan</v>
+      </c>
+      <c r="H16" t="str">
+        <v>2023.05</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="B17" t="str">
+        <v>280</v>
+      </c>
+      <c r="C17" t="str">
+        <v>2023</v>
+      </c>
+      <c r="D17" t="str">
+        <v>J. H. Lee, H. S. Kim, S. H. Park, J. C. Park, and M. S. Lim*</v>
+      </c>
+      <c r="E17" t="str">
+        <v>2-D FEA-Based Iron Loss Calculation Method for Linear Oscillating Actuator Considering the Circumferential Segmented Structure</v>
+      </c>
+      <c r="F17" t="str">
+        <v>2023 International Conference on Magnetics (INTERMAG 2023)</v>
+      </c>
+      <c r="G17" t="str">
+        <v>Sendai, Japan</v>
+      </c>
+      <c r="H17" t="str">
+        <v>2023.05</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="B18" t="str">
+        <v>270</v>
+      </c>
+      <c r="C18" t="str">
+        <v>2024</v>
+      </c>
+      <c r="D18" t="str">
+        <v>J. H. Lee, H. S. Kim, S. H. Park, J. C. Park, and M. S. Lim*</v>
+      </c>
+      <c r="E18" t="str">
+        <v>Suppression of Vibration in PMSM Caused by Time-Varying Load for Reciprocating Compressor</v>
+      </c>
+      <c r="F18" t="str">
+        <v>26th International Conference on Electrical Machines 2024 (ICEM 2024)</v>
+      </c>
+      <c r="G18" t="str">
+        <v>Torino, Italy</v>
+      </c>
+      <c r="H18" t="str">
+        <v>2024.09</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="B19" t="str">
+        <v>260</v>
+      </c>
+      <c r="C19" t="str">
+        <v>2025</v>
+      </c>
+      <c r="D19" t="str">
+        <v>J. H. Lee, H. S. Kim, S. H. Park, J. C. Park, and M. S. Lim*</v>
+      </c>
+      <c r="E19" t="str">
+        <v>Design Optimization of Single-Phase Linear Oscillating Actuator Considering Effect of Detent Force on Mechanical Resonance in Linear Compressor</v>
+      </c>
+      <c r="F19" t="str">
+        <v>The 15th International Symposium on Linear Drives for Industry Applications (LDIA 2025)</v>
+      </c>
+      <c r="G19" t="str">
+        <v>Daejeon, Republic of Korea</v>
+      </c>
+      <c r="H19" t="str">
+        <v>2025.05</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="B20" t="str">
+        <v>250</v>
+      </c>
+      <c r="C20" t="str">
+        <v>2025</v>
+      </c>
+      <c r="D20" t="str">
+        <v>J. H. Lee, H. S. Kim, S. H. Park, J. C. Park, and M. S. Lim*</v>
+      </c>
+      <c r="E20" t="str">
+        <v>A Comparative Study of Dual Mover and Dual Stator Linear Oscillating Actuator Considering Mechanical Resonance in Linear Compressor</v>
+      </c>
+      <c r="F20" t="str">
+        <v>The 15th International Symposium on Linear Drives for Industry Applications (LDIA 2025)</v>
+      </c>
+      <c r="G20" t="str">
+        <v>Daejeon, Republic of Korea</v>
+      </c>
+      <c r="H20" t="str">
+        <v>2025.05</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="B21" t="str">
+        <v>240</v>
+      </c>
+      <c r="C21" t="str">
+        <v>2025</v>
+      </c>
+      <c r="D21" t="str">
+        <v>J. H. Lee, H. S. Kim, S. H. Park, J. C. Park, and M. S. Lim*</v>
+      </c>
+      <c r="E21" t="str">
+        <v>Analysis of 2-D FEA Methods for Linear Oscillating Actuators Considering the Segmented Structure</v>
+      </c>
+      <c r="F21" t="str">
+        <v>The 15th International Symposium on Linear Drives for Industry Applications (LDIA 2025)</v>
+      </c>
+      <c r="G21" t="str">
+        <v>Daejeon, Republic of Korea</v>
+      </c>
+      <c r="H21" t="str">
+        <v>2025.05</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="B22" t="str">
+        <v>230</v>
+      </c>
+      <c r="C22" t="str">
+        <v>2025</v>
+      </c>
+      <c r="D22" t="str">
+        <v>J. H. Lee, H. S. Kim, S. H. Park, J. C. Park, and M. S. Lim*</v>
+      </c>
+      <c r="E22" t="str">
+        <v>Integration of Coil Winding Process into Linear Oscillating Actuators Design</v>
+      </c>
+      <c r="F22" t="str">
+        <v>The 15th International Symposium on Linear Drives for Industry Applications (LDIA 2025)</v>
+      </c>
+      <c r="G22" t="str">
+        <v>Daejeon, Republic of Korea</v>
+      </c>
+      <c r="H22" t="str">
+        <v>2025.05</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="B23" t="str">
+        <v>220</v>
+      </c>
+      <c r="C23" t="str">
+        <v>2025</v>
+      </c>
+      <c r="D23" t="str">
+        <v>J. H. Lee, H. S. Kim, S. H. Park, J. C. Park, and M. S. Lim*</v>
+      </c>
+      <c r="E23" t="str">
+        <v>A Comparative Study of Multi-Objective Optimization in Linear Oscillating Actuators</v>
+      </c>
+      <c r="F23" t="str">
+        <v>The 15th International Symposium on Linear Drives for Industry Applications (LDIA 2025)</v>
+      </c>
+      <c r="G23" t="str">
+        <v>Daejeon, Republic of Korea</v>
+      </c>
+      <c r="H23" t="str">
+        <v>2025.05</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="B24" t="str">
+        <v>210</v>
+      </c>
+      <c r="C24" t="str">
+        <v>2025</v>
+      </c>
+      <c r="D24" t="str">
+        <v>J. H. Lee, H. S. Kim, S. H. Park, J. C. Park, and M. S. Lim*</v>
+      </c>
+      <c r="E24" t="str">
+        <v>Performances Analysis of Linear Oscillating Actuator with Dual Stator Topology</v>
+      </c>
+      <c r="F24" t="str">
+        <v>The 15th International Symposium on Linear Drives for Industry Applications (LDIA 2025)</v>
+      </c>
+      <c r="G24" t="str">
+        <v>Daejeon, Republic of Korea</v>
+      </c>
+      <c r="H24" t="str">
+        <v>2025.05</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="B25" t="str">
+        <v>200</v>
+      </c>
+      <c r="C25" t="str">
+        <v>2025</v>
+      </c>
+      <c r="D25" t="str">
+        <v>J. H. Lee, H. S. Kim, S. H. Park, J. C. Park, and M. S. Lim*</v>
+      </c>
+      <c r="E25" t="str">
+        <v>Improved Loss Analysis Method Considering Core Anisotropy and AC Copper Loss in Linear Oscillating Actuator</v>
+      </c>
+      <c r="F25" t="str">
+        <v>The 15th International Symposium on Linear Drives for Industry Applications (LDIA 2025)</v>
+      </c>
+      <c r="G25" t="str">
+        <v>Daejeon, Republic of Korea</v>
+      </c>
+      <c r="H25" t="str">
+        <v>2025.05</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="B26" t="str">
+        <v>190</v>
+      </c>
+      <c r="C26" t="str">
+        <v>2025</v>
+      </c>
+      <c r="D26" t="str">
+        <v>J. H. Lee, H. S. Kim, S. H. Park, J. C. Park, and M. S. Lim*</v>
+      </c>
+      <c r="E26" t="str">
+        <v>Comparison of Prediction Accuracy between Kriging and Deep Neural Network Surrogate Models for Design Optimization of Linear Oscillating Actuators</v>
+      </c>
+      <c r="F26" t="str">
+        <v>The 15th International Symposium on Linear Drives for Industry Applications (LDIA 2025)</v>
+      </c>
+      <c r="G26" t="str">
+        <v>Daejeon, Republic of Korea</v>
+      </c>
+      <c r="H26" t="str">
+        <v>2025.05</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="B27" t="str">
+        <v>180</v>
+      </c>
+      <c r="C27" t="str">
+        <v>2025</v>
+      </c>
+      <c r="D27" t="str">
+        <v>J. H. Lee, H. S. Kim, S. H. Park, J. C. Park, and M. S. Lim*</v>
+      </c>
+      <c r="E27" t="str">
+        <v>Computationally Efficient Conductor Design for WFSM with Hairpin Windings Considering AC Ohmic Loss</v>
+      </c>
+      <c r="F27" t="str">
+        <v>25th International Conference on the Computation of Electromagnetic Fields (COMPUMAG 2025)</v>
+      </c>
+      <c r="G27" t="str">
+        <v>Naples, Italy</v>
+      </c>
+      <c r="H27" t="str">
+        <v>2025.06</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="B28" t="str">
+        <v>170</v>
+      </c>
+      <c r="C28" t="str">
+        <v>2025</v>
+      </c>
+      <c r="D28" t="str">
+        <v>J. H. Lee, H. S. Kim, S. H. Park, J. C. Park, and M. S. Lim*</v>
+      </c>
+      <c r="E28" t="str">
+        <v>Design of WFSM using Sizing Method Combining 2D Equivalent Magnetic Circuit considering Nonlinear Characteristics</v>
+      </c>
+      <c r="F28" t="str">
+        <v>25th International Conference on the Computation of Electromagnetic Fields (COMPUMAG 2025)</v>
+      </c>
+      <c r="G28" t="str">
+        <v>Naples, Italy</v>
+      </c>
+      <c r="H28" t="str">
+        <v>2025.06</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="B29" t="str">
+        <v>160</v>
+      </c>
+      <c r="C29" t="str">
+        <v>2025</v>
+      </c>
+      <c r="D29" t="str">
+        <v>J. H. Lee, H. S. Kim, S. H. Park, J. C. Park, and M. S. Lim*</v>
+      </c>
+      <c r="E29" t="str">
+        <v>Robust Design Optimization of SPMSM based on Manufacturing Uncertainty Analysis of Prototype</v>
+      </c>
+      <c r="F29" t="str">
+        <v>25th International Conference on the Computation of Electromagnetic Fields (COMPUMAG 2025)</v>
+      </c>
+      <c r="G29" t="str">
+        <v>Naples, Italy</v>
+      </c>
+      <c r="H29" t="str">
+        <v>2025.06</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="B30" t="str">
+        <v>150</v>
+      </c>
+      <c r="C30" t="str">
+        <v>2025</v>
+      </c>
+      <c r="D30" t="str">
+        <v>J. H. Lee, H. S. Kim, S. H. Park, J. C. Park, and M. S. Lim*</v>
+      </c>
+      <c r="E30" t="str">
+        <v>Computationally Efficient Surrogate Modeling of PWM-Induced Iron Loss for Axial Flux Permanent Magnet Synchronous Motors Using Deep Transfer Learning</v>
+      </c>
+      <c r="F30" t="str">
+        <v>25th International Conference on the Computation of Electromagnetic Fields (COMPUMAG 2025)</v>
+      </c>
+      <c r="G30" t="str">
+        <v>Naples, Italy</v>
+      </c>
+      <c r="H30" t="str">
+        <v>2025.06</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="B31" t="str">
+        <v>140</v>
+      </c>
+      <c r="C31" t="str">
+        <v>2025</v>
+      </c>
+      <c r="D31" t="str">
+        <v>J. H. Lee, H. S. Kim, S. H. Park, J. C. Park, and M. S. Lim*</v>
+      </c>
+      <c r="E31" t="str">
+        <v>Efficient Prediction of Electromagnetic Excitation Force for SPMSM Using Analytical Model-Based Deep Transfer Learning Considering Axial Leakage Flux</v>
+      </c>
+      <c r="F31" t="str">
+        <v>25th International Conference on the Computation of Electromagnetic Fields (COMPUMAG 2025)</v>
+      </c>
+      <c r="G31" t="str">
+        <v>Naples, Italy</v>
+      </c>
+      <c r="H31" t="str">
+        <v>2025.06</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="B32" t="str">
+        <v>130</v>
+      </c>
+      <c r="C32" t="str">
+        <v>2025</v>
+      </c>
+      <c r="D32" t="str">
+        <v>J. H. Lee, H. S. Kim, S. H. Park, J. C. Park, and M. S. Lim*</v>
+      </c>
+      <c r="E32" t="str">
+        <v>Efficient Analysis of Efficiency Map for Externally Excited Synchronous Motors Using Equivalent Magnetic Circuit-Based Deep Transfer Learning</v>
+      </c>
+      <c r="F32" t="str">
+        <v>25th International Conference on the Computation of Electromagnetic Fields (COMPUMAG 2025)</v>
+      </c>
+      <c r="G32" t="str">
+        <v>Naples, Italy</v>
+      </c>
+      <c r="H32" t="str">
+        <v>2025.06</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="B33" t="str">
+        <v>120</v>
+      </c>
+      <c r="C33" t="str">
+        <v>2025</v>
+      </c>
+      <c r="D33" t="str">
+        <v>J. H. Lee, H. S. Kim, S. H. Park, J. C. Park, and M. S. Lim*</v>
+      </c>
+      <c r="E33" t="str">
+        <v>Characteristics Estimation and Design of SPMSM using Analytic Method-based Transfer Learning</v>
+      </c>
+      <c r="F33" t="str">
+        <v>25th International Conference on the Computation of Electromagnetic Fields (COMPUMAG 2025)</v>
+      </c>
+      <c r="G33" t="str">
+        <v>Naples, Italy</v>
+      </c>
+      <c r="H33" t="str">
+        <v>2025.06</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="B34" t="str">
+        <v>110</v>
+      </c>
+      <c r="C34" t="str">
+        <v>2025</v>
+      </c>
+      <c r="D34" t="str">
+        <v>J. H. Lee, H. S. Kim, S. H. Park, J. C. Park, and M. S. Lim*</v>
+      </c>
+      <c r="E34" t="str">
+        <v>Effect of Magnetic Anisotropy Property of Non-Oriented Electrical Steel on SPMSM Cogging Torque</v>
+      </c>
+      <c r="F34" t="str">
+        <v>25th International Conference on the Computation of Electromagnetic Fields (COMPUMAG 2025)</v>
+      </c>
+      <c r="G34" t="str">
+        <v>Naples, Italy</v>
+      </c>
+      <c r="H34" t="str">
+        <v>2025.06</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="B35" t="str">
+        <v>100</v>
+      </c>
+      <c r="C35" t="str">
+        <v>2025</v>
+      </c>
+      <c r="D35" t="str">
+        <v>J. H. Lee, H. S. Kim, S. H. Park, J. C. Park, and M. S. Lim*</v>
+      </c>
+      <c r="E35" t="str">
+        <v>Analytic Estimation and Verification of Cogging Torque in SPMSM with Manufacturing Tolerance of Segmented Core</v>
+      </c>
+      <c r="F35" t="str">
+        <v>25th International Conference on the Computation of Electromagnetic Fields (COMPUMAG 2025)</v>
+      </c>
+      <c r="G35" t="str">
+        <v>Naples, Italy</v>
+      </c>
+      <c r="H35" t="str">
+        <v>2025.06</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="B36" t="str">
+        <v>90</v>
+      </c>
+      <c r="C36" t="str">
+        <v>2025</v>
+      </c>
+      <c r="D36" t="str">
+        <v>J. H. Lee, H. S. Kim, S. H. Park, J. C. Park, and M. S. Lim*</v>
+      </c>
+      <c r="E36" t="str">
+        <v>Comparative Study of Kriging and Deep Neural Network as Surrogate Models for Performance Prediction of PMSM</v>
+      </c>
+      <c r="F36" t="str">
+        <v>25th International Conference on the Computation of Electromagnetic Fields (COMPUMAG 2025)</v>
+      </c>
+      <c r="G36" t="str">
+        <v>Naples, Italy</v>
+      </c>
+      <c r="H36" t="str">
+        <v>2025.06</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="B37" t="str">
+        <v>80</v>
+      </c>
+      <c r="C37" t="str">
+        <v>2025</v>
+      </c>
+      <c r="D37" t="str">
+        <v>J. H. Lee, H. S. Kim, S. H. Park, J. C. Park, and M. S. Lim*</v>
+      </c>
+      <c r="E37" t="str">
+        <v>Computationally Efficient Sensitivity Analysis for robustness of Electric Motor considering Manufacturing Uncertainty</v>
+      </c>
+      <c r="F37" t="str">
+        <v>25th International Conference on the Computation of Electromagnetic Fields (COMPUMAG 2025)</v>
+      </c>
+      <c r="G37" t="str">
+        <v>Naples, Italy</v>
+      </c>
+      <c r="H37" t="str">
+        <v>2025.06</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="B38" t="str">
+        <v>70</v>
+      </c>
+      <c r="C38" t="str">
+        <v>2025</v>
+      </c>
+      <c r="D38" t="str">
+        <v>J. H. Lee, H. S. Kim, S. H. Park, J. C. Park, and M. S. Lim*</v>
+      </c>
+      <c r="E38" t="str">
+        <v>Virtual Vibration Sensor Calibration Based on VAE-Based Transfer Learning for Predicting Low Frequency Vibration on Permanent Magnet Synchronous Motors</v>
+      </c>
+      <c r="F38" t="str">
+        <v>31st International Congress on Sound and Vibration (ICSV 31)</v>
+      </c>
+      <c r="G38" t="str">
+        <v>Incheon, Republic of Korea</v>
+      </c>
+      <c r="H38" t="str">
+        <v>2025.07</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="B39" t="str">
+        <v>60</v>
+      </c>
+      <c r="C39" t="str">
+        <v>2026</v>
+      </c>
+      <c r="D39" t="str">
+        <v>J. H. Lee, H. S. Kim, S. H. Park, J. C. Park, and M. S. Lim*</v>
+      </c>
+      <c r="E39" t="str">
+        <v>Computationally Efficient Prediction of Electromagnetic Excitation Force in SPMSM Considering Axial Leakage Flux via Space Harmonic Analysis-Based Deep Transfer Learning</v>
+      </c>
+      <c r="F39" t="str">
+        <v>27th International Conference on Electrical Machines 2024 (ICEM 2026)</v>
+      </c>
+      <c r="G39" t="str">
+        <v>Funchal, Portugal</v>
+      </c>
+      <c r="H39" t="str">
+        <v>2026.09</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="B40" t="str">
+        <v>50</v>
+      </c>
+      <c r="C40" t="str">
+        <v>2026</v>
+      </c>
+      <c r="D40" t="str">
+        <v>J. H. Lee, H. S. Kim, S. H. Park, J. C. Park, and M. S. Lim*</v>
+      </c>
+      <c r="E40" t="str">
+        <v>Data-Driven Multi-State Flux Model for Enhanced Static Eccentricity Diagnosis of IPMSMs</v>
+      </c>
+      <c r="F40" t="str">
+        <v>27th International Conference on Electrical Machines 2024 (ICEM 2026)</v>
+      </c>
+      <c r="G40" t="str">
+        <v>Funchal, Portugal</v>
+      </c>
+      <c r="H40" t="str">
+        <v>2026.09</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="B41" t="str">
+        <v>40</v>
+      </c>
+      <c r="C41" t="str">
+        <v>2026</v>
+      </c>
+      <c r="D41" t="str">
+        <v>J. H. Lee, H. S. Kim, S. H. Park, J. C. Park, and M. S. Lim*</v>
+      </c>
+      <c r="E41" t="str">
+        <v>Analysis of IPMSM for Direct-Drive Compander Considering Temperature-Gradient in Axial Direction</v>
+      </c>
+      <c r="F41" t="str">
+        <v>27th International Conference on Electrical Machines 2024 (ICEM 2026)</v>
+      </c>
+      <c r="G41" t="str">
+        <v>Funchal, Portugal</v>
+      </c>
+      <c r="H41" t="str">
+        <v>2026.09</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="B42" t="str">
+        <v>30</v>
+      </c>
+      <c r="C42" t="str">
+        <v>2026</v>
+      </c>
+      <c r="D42" t="str">
+        <v>J. H. Lee, H. S. Kim, S. H. Park, J. C. Park, and M. S. Lim*</v>
+      </c>
+      <c r="E42" t="str">
+        <v>EMC-Based Geometric Scaling Method for Axial Flux Permanent Magnet Motors</v>
+      </c>
+      <c r="F42" t="str">
+        <v>27th International Conference on Electrical Machines 2024 (ICEM 2026)</v>
+      </c>
+      <c r="G42" t="str">
+        <v>Funchal, Portugal</v>
+      </c>
+      <c r="H42" t="str">
+        <v>2026.09</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="B43" t="str">
+        <v>20</v>
+      </c>
+      <c r="C43" t="str">
+        <v>2026</v>
+      </c>
+      <c r="D43" t="str">
+        <v>J. H. Lee, H. S. Kim, S. H. Park, J. C. Park, and M. S. Lim*</v>
+      </c>
+      <c r="E43" t="str">
+        <v>A Scaling Framework for Efficient Design Optimization of IPMSM for EV Traction</v>
+      </c>
+      <c r="F43" t="str">
+        <v>27th International Conference on Electrical Machines 2024 (ICEM 2026)</v>
+      </c>
+      <c r="G43" t="str">
+        <v>Funchal, Portugal</v>
+      </c>
+      <c r="H43" t="str">
+        <v>2026.09</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="B44" t="str">
+        <v>10</v>
+      </c>
+      <c r="C44" t="str">
+        <v>2026</v>
+      </c>
+      <c r="D44" t="str">
+        <v>J. H. Lee, H. S. Kim, S. H. Park, J. C. Park, and M. S. Lim*</v>
+      </c>
+      <c r="E44" t="str">
+        <v>Deep Transfer Learning-Assisted Fast Performance Prediction for AFPM considering PM Overhang Effects and Radial Leakage Flux</v>
+      </c>
+      <c r="F44" t="str">
+        <v>2026 International Conference on Magnetics (INTERMAG 2026)</v>
+      </c>
+      <c r="G44" t="str">
+        <v>Manchester, United Kingdom</v>
+      </c>
+      <c r="H44" t="str">
+        <v>2026.04</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I44"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -5510,7 +6582,7 @@
         <v>TRUE</v>
       </c>
       <c r="B2" t="str">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C2" t="str">
         <v>US</v>
@@ -5551,9 +6623,32 @@
         <v>US 11,757,383 B2</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="B4" t="str">
+        <v>10</v>
+      </c>
+      <c r="C4" t="str">
+        <v>KOR</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Filed</v>
+      </c>
+      <c r="E4" t="str">
+        <v>매입형 영구자석 모터의 회전자(Rotor for Interior Permanent Magnet Motor)</v>
+      </c>
+      <c r="F4" t="str">
+        <v>2026</v>
+      </c>
+      <c r="G4" t="str">
+        <v>10-2026-0034283</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:I4"/>
   </ignoredErrors>
 </worksheet>
 </file>